--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1519,7 +1519,7 @@
         <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>397.81</v>
+        <v>397.82</v>
       </c>
       <c r="K14" t="n">
         <v>390.68</v>
@@ -10272,7 +10272,7 @@
         <v>7.4</v>
       </c>
       <c r="J129" t="n">
-        <v>314.95</v>
+        <v>314.94</v>
       </c>
       <c r="K129" t="n">
         <v>321</v>
@@ -10730,7 +10730,7 @@
         <v>7.4</v>
       </c>
       <c r="J135" t="n">
-        <v>316.35</v>
+        <v>316.34</v>
       </c>
       <c r="K135" t="n">
         <v>324.08</v>
@@ -13213,7 +13213,7 @@
         <v>7.4</v>
       </c>
       <c r="J168" t="n">
-        <v>371.05</v>
+        <v>371.06</v>
       </c>
       <c r="K168" t="n">
         <v>336.97</v>
@@ -31651,6 +31651,79 @@
         <v>154.5</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="D413" t="n">
+        <v>367.73</v>
+      </c>
+      <c r="E413" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="F413" t="n">
+        <v>361.14</v>
+      </c>
+      <c r="G413" t="n">
+        <v>23605913</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>356.07</v>
+      </c>
+      <c r="K413" t="n">
+        <v>361.02</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.33</v>
+      </c>
+      <c r="M413" t="n">
+        <v>398.64</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="O413" t="n">
+        <v>31</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -1519,7 +1519,7 @@
         <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>397.82</v>
+        <v>397.81</v>
       </c>
       <c r="K14" t="n">
         <v>390.68</v>
@@ -10730,7 +10730,7 @@
         <v>7.4</v>
       </c>
       <c r="J135" t="n">
-        <v>316.34</v>
+        <v>316.35</v>
       </c>
       <c r="K135" t="n">
         <v>324.08</v>
@@ -13213,7 +13213,7 @@
         <v>7.4</v>
       </c>
       <c r="J168" t="n">
-        <v>371.06</v>
+        <v>371.05</v>
       </c>
       <c r="K168" t="n">
         <v>336.97</v>
@@ -31672,31 +31672,31 @@
         <v>357.04</v>
       </c>
       <c r="F413" t="n">
-        <v>361.14</v>
+        <v>358.97</v>
       </c>
       <c r="G413" t="n">
-        <v>23605913</v>
+        <v>32337601</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-1.18</v>
+        <v>-1.77</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
       <c r="J413" t="n">
-        <v>356.07</v>
+        <v>355.96</v>
       </c>
       <c r="K413" t="n">
-        <v>361.02</v>
+        <v>360.99</v>
       </c>
       <c r="L413" t="n">
-        <v>378.33</v>
+        <v>378.31</v>
       </c>
       <c r="M413" t="n">
-        <v>398.64</v>
+        <v>398.63</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>55.11</v>
+        <v>54.13</v>
       </c>
       <c r="O413" t="n">
         <v>31</v>
@@ -31711,18 +31711,24 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>152.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31527,7 +31527,7 @@
         <v>365.44</v>
       </c>
       <c r="G411" t="n">
-        <v>30091300</v>
+        <v>30153000</v>
       </c>
       <c r="H411" s="3" t="n">
         <v>0.52</v>
@@ -31587,28 +31587,44 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>359.78</v>
+      </c>
+      <c r="D412" t="n">
+        <v>367.73</v>
+      </c>
+      <c r="E412" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="F412" t="n">
+        <v>358.97</v>
+      </c>
       <c r="G412" t="n">
-        <v>32337601</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>32401500</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>-1.77</v>
       </c>
       <c r="I412" t="n">
         <v>7.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>355.96</v>
+      </c>
+      <c r="K412" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="L412" t="n">
+        <v>378.31</v>
+      </c>
+      <c r="M412" t="n">
+        <v>398.63</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>57.17</v>
+        <v>54.13</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31620,16 +31636,18 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R412" t="inlineStr"/>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S412" t="n">
         <v>4.96</v>
       </c>
       <c r="T412" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>152.1</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31624,7 +31624,7 @@
         <v>54.13</v>
       </c>
       <c r="O412" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31653,6 +31653,79 @@
         <v>152.1</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>358.73</v>
+      </c>
+      <c r="D413" t="n">
+        <v>362.39</v>
+      </c>
+      <c r="E413" t="n">
+        <v>354.63</v>
+      </c>
+      <c r="F413" t="n">
+        <v>356.89</v>
+      </c>
+      <c r="G413" t="n">
+        <v>21872752</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>356.84</v>
+      </c>
+      <c r="K413" t="n">
+        <v>360.26</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.09</v>
+      </c>
+      <c r="M413" t="n">
+        <v>398.32</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -645,9 +645,7 @@
       <c r="T2" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>173.2</v>
@@ -720,9 +718,7 @@
       <c r="T3" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U3" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="1" t="n">
         <v>168.6</v>
@@ -795,9 +791,7 @@
       <c r="T4" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>163.6</v>
@@ -870,9 +864,7 @@
       <c r="T5" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>157.4</v>
@@ -945,9 +937,7 @@
       <c r="T6" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>156.7</v>
@@ -1020,9 +1010,7 @@
       <c r="T7" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>158.5</v>
@@ -1099,9 +1087,7 @@
       <c r="T8" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>155.4</v>
@@ -1174,9 +1160,7 @@
       <c r="T9" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>159.4</v>
@@ -1253,9 +1237,7 @@
       <c r="T10" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>162.6</v>
@@ -1328,9 +1310,7 @@
       <c r="T11" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>163.6</v>
@@ -1403,9 +1383,7 @@
       <c r="T12" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.5</v>
@@ -1478,9 +1456,7 @@
       <c r="T13" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>166.9</v>
@@ -1553,9 +1529,7 @@
       <c r="T14" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U14" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>168.8</v>
@@ -1628,9 +1602,7 @@
       <c r="T15" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>166.1</v>
@@ -1703,9 +1675,7 @@
       <c r="T16" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>163.4</v>
@@ -1778,9 +1748,7 @@
       <c r="T17" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>168</v>
@@ -1853,9 +1821,7 @@
       <c r="T18" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U18" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>183.1</v>
@@ -1928,9 +1894,7 @@
       <c r="T19" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U19" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>175.8</v>
@@ -2003,9 +1967,7 @@
       <c r="T20" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U20" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>178.6</v>
@@ -2078,9 +2040,7 @@
       <c r="T21" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U21" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>165</v>
@@ -2153,9 +2113,7 @@
       <c r="T22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U22" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>156.9</v>
@@ -2232,9 +2190,7 @@
       <c r="T23" s="7" t="n">
         <v>19.4</v>
       </c>
-      <c r="U23" s="7" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U23" s="7" t="inlineStr"/>
       <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="5" t="n">
         <v>157.6</v>
@@ -2307,9 +2263,7 @@
       <c r="T24" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U24" s="2" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>153.4</v>
@@ -2382,9 +2336,7 @@
       <c r="T25" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U25" s="2" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="2" t="n">
         <v>149.3</v>
@@ -2457,9 +2409,7 @@
       <c r="T26" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U26" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="1" t="n">
         <v>157.9</v>
@@ -2532,9 +2482,7 @@
       <c r="T27" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U27" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>154.3</v>
@@ -2607,9 +2555,7 @@
       <c r="T28" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U28" s="2" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>151.4</v>
@@ -2682,9 +2628,7 @@
       <c r="T29" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U29" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>138.9</v>
@@ -2761,9 +2705,7 @@
       <c r="T30" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U30" s="3" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
         <v>137.6</v>
@@ -2840,9 +2782,7 @@
       <c r="T31" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U31" s="2" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="2" t="n">
         <v>139.9</v>
@@ -2919,14 +2859,8 @@
       <c r="T32" s="6" t="n">
         <v>27.9</v>
       </c>
-      <c r="U32" s="6" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U32" s="7" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="7" t="n">
         <v>146</v>
       </c>
@@ -3002,14 +2936,8 @@
       <c r="T33" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="U33" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -3085,9 +3013,7 @@
       <c r="T34" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U34" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.7</v>
@@ -3164,9 +3090,7 @@
       <c r="T35" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U35" s="2" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>128.9</v>
@@ -3243,9 +3167,7 @@
       <c r="T36" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U36" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>130.3</v>
@@ -3318,9 +3240,7 @@
       <c r="T37" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U37" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>133.9</v>
@@ -3393,9 +3313,7 @@
       <c r="T38" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U38" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.8</v>
@@ -3468,9 +3386,7 @@
       <c r="T39" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U39" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>136.4</v>
@@ -3543,9 +3459,7 @@
       <c r="T40" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U40" s="2" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>140.8</v>
@@ -3618,9 +3532,7 @@
       <c r="T41" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U41" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>141.7</v>
@@ -3693,9 +3605,7 @@
       <c r="T42" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U42" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>144</v>
@@ -3768,9 +3678,7 @@
       <c r="T43" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U43" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>148.7</v>
@@ -3843,9 +3751,7 @@
       <c r="T44" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U44" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>144.8</v>
@@ -3918,9 +3824,7 @@
       <c r="T45" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U45" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>140.9</v>
@@ -3993,9 +3897,7 @@
       <c r="T46" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>139</v>
@@ -4068,9 +3970,7 @@
       <c r="T47" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U47" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>148.6</v>
@@ -4143,9 +4043,7 @@
       <c r="T48" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U48" s="2" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>143</v>
@@ -4218,9 +4116,7 @@
       <c r="T49" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U49" s="3" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="2" t="n">
         <v>144.3</v>
@@ -4293,14 +4189,8 @@
       <c r="T50" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="U50" s="3" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="V50" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" s="2" t="n">
         <v>139.2</v>
       </c>
@@ -4376,14 +4266,8 @@
       <c r="T51" s="6" t="n">
         <v>45.3</v>
       </c>
-      <c r="U51" s="6" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="V51" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U51" s="7" t="inlineStr"/>
+      <c r="V51" s="4" t="inlineStr"/>
       <c r="W51" s="7" t="n">
         <v>136.5</v>
       </c>
@@ -4455,14 +4339,8 @@
       <c r="T52" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U52" s="3" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="V52" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4534,14 +4412,8 @@
       <c r="T53" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="U53" s="3" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="V53" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4613,14 +4485,8 @@
       <c r="T54" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="U54" s="3" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="V54" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4696,14 +4562,8 @@
       <c r="T55" s="3" t="n">
         <v>40.7</v>
       </c>
-      <c r="U55" s="3" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="V55" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" s="2" t="n">
         <v>127.5</v>
       </c>
@@ -4775,14 +4635,8 @@
       <c r="T56" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="U56" s="3" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="V56" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4854,9 +4708,7 @@
       <c r="T57" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U57" s="3" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.7</v>
@@ -4929,9 +4781,7 @@
       <c r="T58" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="U58" s="3" t="n">
-        <v>26</v>
-      </c>
+      <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="2" t="n">
         <v>135.8</v>
@@ -5004,14 +4854,8 @@
       <c r="T59" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="U59" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="V59" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" s="2" t="n">
         <v>131.3</v>
       </c>
@@ -5083,14 +4927,8 @@
       <c r="T60" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="U60" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="V60" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" s="2" t="n">
         <v>130</v>
       </c>
@@ -5162,9 +5000,7 @@
       <c r="T61" s="3" t="n">
         <v>33.8</v>
       </c>
-      <c r="U61" s="3" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="3" t="n">
         <v>125.8</v>
@@ -5237,9 +5073,7 @@
       <c r="T62" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U62" s="3" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="3" t="n">
         <v>125.9</v>
@@ -5312,14 +5146,8 @@
       <c r="T63" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="U63" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="V63" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" s="3" t="n">
         <v>126.7</v>
       </c>
@@ -5391,9 +5219,7 @@
       <c r="T64" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="U64" s="3" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>129</v>
@@ -5466,9 +5292,7 @@
       <c r="T65" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U65" s="2" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>132.4</v>
@@ -5541,9 +5365,7 @@
       <c r="T66" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U66" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>131.3</v>
@@ -5616,9 +5438,7 @@
       <c r="T67" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U67" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>134.3</v>
@@ -5691,9 +5511,7 @@
       <c r="T68" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U68" s="2" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>132.7</v>
@@ -5766,9 +5584,7 @@
       <c r="T69" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U69" s="3" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.1</v>
@@ -5841,9 +5657,7 @@
       <c r="T70" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U70" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.8</v>
@@ -5916,9 +5730,7 @@
       <c r="T71" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U71" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>134.1</v>
@@ -5995,9 +5807,7 @@
       <c r="T72" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U72" s="2" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>133.2</v>
@@ -6070,9 +5880,7 @@
       <c r="T73" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U73" s="2" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>132.2</v>
@@ -6145,9 +5953,7 @@
       <c r="T74" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U74" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>131.5</v>
@@ -6220,9 +6026,7 @@
       <c r="T75" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U75" s="3" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>128.4</v>
@@ -6295,9 +6099,7 @@
       <c r="T76" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U76" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>137.7</v>
@@ -6370,9 +6172,7 @@
       <c r="T77" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U77" s="2" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>140.5</v>
@@ -6445,9 +6245,7 @@
       <c r="T78" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U78" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>138.9</v>
@@ -6520,9 +6318,7 @@
       <c r="T79" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U79" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>140.9</v>
@@ -6595,9 +6391,7 @@
       <c r="T80" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U80" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>136</v>
@@ -6670,9 +6464,7 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>135.9</v>
@@ -6745,9 +6537,7 @@
       <c r="T82" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U82" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6820,9 +6610,7 @@
       <c r="T83" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U83" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>137.3</v>
@@ -6895,9 +6683,7 @@
       <c r="T84" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U84" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139</v>
@@ -6970,9 +6756,7 @@
       <c r="T85" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U85" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>139.3</v>
@@ -7045,9 +6829,7 @@
       <c r="T86" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U86" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>140.9</v>
@@ -7120,9 +6902,7 @@
       <c r="T87" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U87" s="2" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.6</v>
@@ -7195,9 +6975,7 @@
       <c r="T88" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U88" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>137.3</v>
@@ -7270,9 +7048,7 @@
       <c r="T89" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U89" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>138.2</v>
@@ -7345,9 +7121,7 @@
       <c r="T90" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U90" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141</v>
@@ -7420,9 +7194,7 @@
       <c r="T91" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U91" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>141.6</v>
@@ -7499,9 +7271,7 @@
       <c r="T92" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U92" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>137.5</v>
@@ -7578,9 +7348,7 @@
       <c r="T93" s="7" t="n">
         <v>18.5</v>
       </c>
-      <c r="U93" s="7" t="n">
-        <v>19</v>
-      </c>
+      <c r="U93" s="7" t="inlineStr"/>
       <c r="V93" s="4" t="inlineStr"/>
       <c r="W93" s="7" t="n">
         <v>140.1</v>
@@ -7653,9 +7421,7 @@
       <c r="T94" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U94" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>138.9</v>
@@ -7728,9 +7494,7 @@
       <c r="T95" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U95" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>139.2</v>
@@ -7803,9 +7567,7 @@
       <c r="T96" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U96" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.2</v>
@@ -7878,9 +7640,7 @@
       <c r="T97" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U97" s="2" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>141.4</v>
@@ -7957,9 +7717,7 @@
       <c r="T98" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U98" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>145.6</v>
@@ -8032,9 +7790,7 @@
       <c r="T99" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U99" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="2" t="n">
         <v>149.6</v>
@@ -8107,9 +7863,7 @@
       <c r="T100" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U100" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="1" t="n">
         <v>156.6</v>
@@ -8186,9 +7940,7 @@
       <c r="T101" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U101" s="2" t="n">
-        <v>21</v>
-      </c>
+      <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>154.4</v>
@@ -8261,9 +8013,7 @@
       <c r="T102" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U102" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>148.4</v>
@@ -8336,9 +8086,7 @@
       <c r="T103" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U103" s="2" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>149.2</v>
@@ -8411,9 +8159,7 @@
       <c r="T104" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U104" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="2" t="n">
         <v>154.8</v>
@@ -8486,9 +8232,7 @@
       <c r="T105" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U105" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="1" t="n">
         <v>155</v>
@@ -8565,9 +8309,7 @@
       <c r="T106" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U106" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>152.2</v>
@@ -8640,9 +8382,7 @@
       <c r="T107" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U107" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>147.5</v>
@@ -8715,9 +8455,7 @@
       <c r="T108" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U108" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>143.4</v>
@@ -8790,9 +8528,7 @@
       <c r="T109" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U109" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>139.6</v>
@@ -8869,9 +8605,7 @@
       <c r="T110" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U110" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>140.1</v>
@@ -8944,9 +8678,7 @@
       <c r="T111" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U111" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>139.3</v>
@@ -9019,9 +8751,7 @@
       <c r="T112" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U112" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>141.4</v>
@@ -9098,9 +8828,7 @@
       <c r="T113" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U113" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>138</v>
@@ -9173,9 +8901,7 @@
       <c r="T114" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U114" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>140.8</v>
@@ -9248,9 +8974,7 @@
       <c r="T115" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U115" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>141.8</v>
@@ -9323,9 +9047,7 @@
       <c r="T116" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U116" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>143.3</v>
@@ -9398,9 +9120,7 @@
       <c r="T117" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U117" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>145</v>
@@ -9473,9 +9193,7 @@
       <c r="T118" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U118" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>147</v>
@@ -9552,9 +9270,7 @@
       <c r="T119" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U119" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>143.7</v>
@@ -9627,9 +9343,7 @@
       <c r="T120" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U120" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>146.7</v>
@@ -9702,9 +9416,7 @@
       <c r="T121" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U121" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>151.1</v>
@@ -9777,9 +9489,7 @@
       <c r="T122" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U122" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>150.4</v>
@@ -9852,9 +9562,7 @@
       <c r="T123" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U123" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>154.8</v>
@@ -9927,9 +9635,7 @@
       <c r="T124" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U124" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="2" t="n">
         <v>153.4</v>
@@ -10002,9 +9708,7 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>159.3</v>
@@ -10081,9 +9785,7 @@
       <c r="T126" s="7" t="n">
         <v>15.4</v>
       </c>
-      <c r="U126" s="7" t="n">
-        <v>10</v>
-      </c>
+      <c r="U126" s="7" t="inlineStr"/>
       <c r="V126" s="4" t="inlineStr"/>
       <c r="W126" s="5" t="n">
         <v>159.4</v>
@@ -10156,9 +9858,7 @@
       <c r="T127" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U127" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>145.6</v>
@@ -10231,9 +9931,7 @@
       <c r="T128" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U128" s="2" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>147.6</v>
@@ -10310,9 +10008,7 @@
       <c r="T129" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U129" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>149.1</v>
@@ -10385,9 +10081,7 @@
       <c r="T130" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U130" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>154.1</v>
@@ -10464,9 +10158,7 @@
       <c r="T131" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U131" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="2" t="n">
         <v>152.3</v>
@@ -10539,9 +10231,7 @@
       <c r="T132" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U132" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>155.5</v>
@@ -10614,9 +10304,7 @@
       <c r="T133" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U133" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="1" t="n">
         <v>159.3</v>
@@ -10689,9 +10377,7 @@
       <c r="T134" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U134" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.9</v>
@@ -10764,9 +10450,7 @@
       <c r="T135" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U135" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>149.7</v>
@@ -10839,9 +10523,7 @@
       <c r="T136" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U136" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147</v>
@@ -10914,9 +10596,7 @@
       <c r="T137" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U137" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>147.5</v>
@@ -10989,9 +10669,7 @@
       <c r="T138" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U138" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>148.6</v>
@@ -11064,9 +10742,7 @@
       <c r="T139" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U139" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>151.4</v>
@@ -11139,9 +10815,7 @@
       <c r="T140" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U140" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>153.1</v>
@@ -11214,9 +10888,7 @@
       <c r="T141" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U141" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>150.6</v>
@@ -11289,9 +10961,7 @@
       <c r="T142" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U142" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.8</v>
@@ -11364,9 +11034,7 @@
       <c r="T143" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U143" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.9</v>
@@ -11439,9 +11107,7 @@
       <c r="T144" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U144" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>153.2</v>
@@ -11514,9 +11180,7 @@
       <c r="T145" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U145" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.6</v>
@@ -11593,9 +11257,7 @@
       <c r="T146" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U146" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>144.3</v>
@@ -11668,9 +11330,7 @@
       <c r="T147" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U147" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>146.4</v>
@@ -11743,9 +11403,7 @@
       <c r="T148" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U148" s="2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="2" t="n">
         <v>150</v>
@@ -11818,9 +11476,7 @@
       <c r="T149" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U149" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="1" t="n">
         <v>156.5</v>
@@ -11893,9 +11549,7 @@
       <c r="T150" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U150" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>150.9</v>
@@ -11968,9 +11622,7 @@
       <c r="T151" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U151" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.5</v>
@@ -12043,9 +11695,7 @@
       <c r="T152" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U152" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>152.1</v>
@@ -12122,9 +11772,7 @@
       <c r="T153" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U153" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>151.5</v>
@@ -12197,9 +11845,7 @@
       <c r="T154" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U154" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>150.2</v>
@@ -12272,9 +11918,7 @@
       <c r="T155" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U155" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>154</v>
@@ -12347,9 +11991,7 @@
       <c r="T156" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U156" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.2</v>
@@ -12422,9 +12064,7 @@
       <c r="T157" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U157" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>148.8</v>
@@ -12497,9 +12137,7 @@
       <c r="T158" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U158" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>150.9</v>
@@ -12572,9 +12210,7 @@
       <c r="T159" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U159" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>151.9</v>
@@ -12647,9 +12283,7 @@
       <c r="T160" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U160" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>147.6</v>
@@ -12722,9 +12356,7 @@
       <c r="T161" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U161" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>149.5</v>
@@ -12797,9 +12429,7 @@
       <c r="T162" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U162" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>152.1</v>
@@ -12872,9 +12502,7 @@
       <c r="T163" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U163" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>148.2</v>
@@ -12947,9 +12575,7 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>146.4</v>
@@ -13022,9 +12648,7 @@
       <c r="T165" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U165" s="2" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>148.2</v>
@@ -13097,9 +12721,7 @@
       <c r="T166" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U166" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>147</v>
@@ -13172,9 +12794,7 @@
       <c r="T167" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U167" s="2" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>145.5</v>
@@ -13247,9 +12867,7 @@
       <c r="T168" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U168" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U168" s="2" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>146.5</v>
@@ -13322,9 +12940,7 @@
       <c r="T169" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U169" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -13397,9 +13013,7 @@
       <c r="T170" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U170" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U170" s="2" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>145.9</v>
@@ -13472,9 +13086,7 @@
       <c r="T171" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U171" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>141.5</v>
@@ -13547,9 +13159,7 @@
       <c r="T172" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U172" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U172" s="2" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143</v>
@@ -13622,9 +13232,7 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U173" s="2" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.4</v>
@@ -13697,9 +13305,7 @@
       <c r="T174" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U174" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U174" s="2" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>143.7</v>
@@ -13772,9 +13378,7 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U175" s="2" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>145.9</v>
@@ -13847,9 +13451,7 @@
       <c r="T176" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U176" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U176" s="2" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>144.6</v>
@@ -13922,9 +13524,7 @@
       <c r="T177" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U177" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U177" s="2" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>142.5</v>
@@ -13997,9 +13597,7 @@
       <c r="T178" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U178" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U178" s="2" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.2</v>
@@ -14072,9 +13670,7 @@
       <c r="T179" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U179" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U179" s="2" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.8</v>
@@ -14147,9 +13743,7 @@
       <c r="T180" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U180" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U180" s="2" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>145.3</v>
@@ -14226,9 +13820,7 @@
       <c r="T181" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U181" s="3" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U181" s="2" t="inlineStr"/>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="2" t="n">
         <v>138.9</v>
@@ -14301,9 +13893,7 @@
       <c r="T182" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U182" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U182" s="2" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>142.8</v>
@@ -14380,9 +13970,7 @@
       <c r="T183" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U183" s="2" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="U183" s="2" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>146.5</v>
@@ -14455,9 +14043,7 @@
       <c r="T184" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U184" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U184" s="2" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>145</v>
@@ -14534,9 +14120,7 @@
       <c r="T185" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U185" s="2" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="U185" s="2" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.1</v>
@@ -14609,9 +14193,7 @@
       <c r="T186" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U186" s="2" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="U186" s="2" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>147.6</v>
@@ -14684,9 +14266,7 @@
       <c r="T187" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U187" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U187" s="2" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="2" t="n">
         <v>151.3</v>
@@ -14759,9 +14339,7 @@
       <c r="T188" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U188" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U188" s="2" t="inlineStr"/>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>149.9</v>
@@ -14834,9 +14412,7 @@
       <c r="T189" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U189" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U189" s="2" t="inlineStr"/>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>152.9</v>
@@ -14909,9 +14485,7 @@
       <c r="T190" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U190" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U190" s="2" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>154.3</v>
@@ -14988,9 +14562,7 @@
       <c r="T191" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U191" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U191" s="2" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>153.5</v>
@@ -15063,9 +14635,7 @@
       <c r="T192" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U192" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U192" s="2" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>148.5</v>
@@ -15138,9 +14708,7 @@
       <c r="T193" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U193" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U193" s="2" t="inlineStr"/>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>140.4</v>
@@ -15213,9 +14781,7 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U194" s="2" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>139.4</v>
@@ -15288,9 +14854,7 @@
       <c r="T195" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U195" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U195" s="2" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>141.1</v>
@@ -15363,9 +14927,7 @@
       <c r="T196" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U196" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U196" s="2" t="inlineStr"/>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142.8</v>
@@ -15438,9 +15000,7 @@
       <c r="T197" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U197" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U197" s="2" t="inlineStr"/>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>142</v>
@@ -15513,9 +15073,7 @@
       <c r="T198" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U198" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U198" s="2" t="inlineStr"/>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>144</v>
@@ -15588,9 +15146,7 @@
       <c r="T199" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U199" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U199" s="2" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.6</v>
@@ -15663,9 +15219,7 @@
       <c r="T200" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U200" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U200" s="2" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>143.5</v>
@@ -15742,9 +15296,7 @@
       <c r="T201" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U201" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U201" s="2" t="inlineStr"/>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>141.3</v>
@@ -15817,9 +15369,7 @@
       <c r="T202" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U202" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U202" s="2" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>142.9</v>
@@ -15892,9 +15442,7 @@
       <c r="T203" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U203" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U203" s="2" t="inlineStr"/>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>143.4</v>
@@ -15967,9 +15515,7 @@
       <c r="T204" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U204" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U204" s="2" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>138.6</v>
@@ -16046,9 +15592,7 @@
       <c r="T205" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U205" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U205" s="2" t="inlineStr"/>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>142.5</v>
@@ -16121,9 +15665,7 @@
       <c r="T206" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U206" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U206" s="2" t="inlineStr"/>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>137.9</v>
@@ -16196,9 +15738,7 @@
       <c r="T207" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U207" s="2" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="U207" s="2" t="inlineStr"/>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>140.9</v>
@@ -16271,9 +15811,7 @@
       <c r="T208" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U208" s="2" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="U208" s="2" t="inlineStr"/>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143</v>
@@ -16346,9 +15884,7 @@
       <c r="T209" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U209" s="3" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U209" s="2" t="inlineStr"/>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="2" t="n">
         <v>143.1</v>
@@ -16421,14 +15957,8 @@
       <c r="T210" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="U210" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V210" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>145</v>
       </c>
@@ -16500,9 +16030,7 @@
       <c r="T211" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U211" s="2" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U211" s="2" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.3</v>
@@ -16575,9 +16103,7 @@
       <c r="T212" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U212" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U212" s="2" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>148.6</v>
@@ -16650,9 +16176,7 @@
       <c r="T213" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U213" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U213" s="2" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>151.7</v>
@@ -16725,9 +16249,7 @@
       <c r="T214" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U214" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U214" s="2" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>145</v>
@@ -16800,9 +16322,7 @@
       <c r="T215" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U215" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U215" s="2" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>143</v>
@@ -16875,9 +16395,7 @@
       <c r="T216" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U216" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U216" s="2" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16950,9 +16468,7 @@
       <c r="T217" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U217" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U217" s="2" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>144.9</v>
@@ -17025,9 +16541,7 @@
       <c r="T218" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U218" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="U218" s="2" t="inlineStr"/>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>149.2</v>
@@ -17100,9 +16614,7 @@
       <c r="T219" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U219" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U219" s="2" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.9</v>
@@ -17175,9 +16687,7 @@
       <c r="T220" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U220" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U220" s="2" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>148.8</v>
@@ -17250,9 +16760,7 @@
       <c r="T221" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U221" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U221" s="2" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.6</v>
@@ -17325,9 +16833,7 @@
       <c r="T222" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U222" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U222" s="2" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>150.3</v>
@@ -17400,9 +16906,7 @@
       <c r="T223" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U223" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U223" s="2" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>147.6</v>
@@ -17475,9 +16979,7 @@
       <c r="T224" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U224" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U224" s="2" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>148.3</v>
@@ -17550,9 +17052,7 @@
       <c r="T225" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U225" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U225" s="2" t="inlineStr"/>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="2" t="n">
         <v>153.6</v>
@@ -17625,9 +17125,7 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U226" s="2" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>161.9</v>
@@ -17700,9 +17198,7 @@
       <c r="T227" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U227" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U227" s="2" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="1" t="n">
         <v>157</v>
@@ -17775,9 +17271,7 @@
       <c r="T228" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U228" s="2" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U228" s="2" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="2" t="n">
         <v>153.5</v>
@@ -17850,9 +17344,7 @@
       <c r="T229" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U229" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U229" s="2" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.4</v>
@@ -17925,9 +17417,7 @@
       <c r="T230" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U230" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U230" s="2" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>155.9</v>
@@ -18000,9 +17490,7 @@
       <c r="T231" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U231" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U231" s="2" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>159.9</v>
@@ -18075,9 +17563,7 @@
       <c r="T232" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U232" s="2" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U232" s="2" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -18150,9 +17636,7 @@
       <c r="T233" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U233" s="2" t="n">
-        <v>7.4</v>
-      </c>
+      <c r="U233" s="2" t="inlineStr"/>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="1" t="n">
         <v>160.5</v>
@@ -18225,9 +17709,7 @@
       <c r="T234" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U234" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U234" s="2" t="inlineStr"/>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="2" t="n">
         <v>151.4</v>
@@ -18304,9 +17786,7 @@
       <c r="T235" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U235" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="U235" s="2" t="inlineStr"/>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>150.5</v>
@@ -18379,9 +17859,7 @@
       <c r="T236" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U236" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U236" s="2" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.3</v>
@@ -18454,9 +17932,7 @@
       <c r="T237" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U237" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U237" s="2" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>148.7</v>
@@ -18533,9 +18009,7 @@
       <c r="T238" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U238" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U238" s="2" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>141.9</v>
@@ -18608,9 +18082,7 @@
       <c r="T239" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U239" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U239" s="2" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>142.4</v>
@@ -18687,9 +18159,7 @@
       <c r="T240" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U240" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="U240" s="2" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>146.2</v>
@@ -18762,9 +18232,7 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="U241" s="2" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>143.6</v>
@@ -18837,9 +18305,7 @@
       <c r="T242" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U242" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U242" s="2" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>147.1</v>
@@ -18912,9 +18378,7 @@
       <c r="T243" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U243" s="2" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="U243" s="2" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>146</v>
@@ -18987,9 +18451,7 @@
       <c r="T244" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U244" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U244" s="2" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>149.8</v>
@@ -19062,9 +18524,7 @@
       <c r="T245" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U245" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U245" s="2" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>151.6</v>
@@ -19141,9 +18601,7 @@
       <c r="T246" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U246" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U246" s="2" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>152.5</v>
@@ -19216,9 +18674,7 @@
       <c r="T247" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U247" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U247" s="2" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>151.6</v>
@@ -19291,9 +18747,7 @@
       <c r="T248" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U248" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U248" s="2" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="2" t="n">
         <v>153.6</v>
@@ -19366,9 +18820,7 @@
       <c r="T249" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U249" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U249" s="2" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="1" t="n">
         <v>155</v>
@@ -19441,9 +18893,7 @@
       <c r="T250" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U250" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U250" s="2" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>144.4</v>
@@ -19516,9 +18966,7 @@
       <c r="T251" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U251" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U251" s="2" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>141.3</v>
@@ -19591,9 +19039,7 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U252" s="2" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>144</v>
@@ -19670,9 +19116,7 @@
       <c r="T253" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U253" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U253" s="2" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>148.1</v>
@@ -19745,9 +19189,7 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U254" s="2" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>147.2</v>
@@ -19820,9 +19262,7 @@
       <c r="T255" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U255" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U255" s="2" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>145</v>
@@ -19899,9 +19339,7 @@
       <c r="T256" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U256" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U256" s="2" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="2" t="n">
         <v>143.7</v>
@@ -19974,9 +19412,7 @@
       <c r="T257" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U257" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U257" s="2" t="inlineStr"/>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="2" t="n">
         <v>143.6</v>
@@ -20049,9 +19485,7 @@
       <c r="T258" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U258" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U258" s="2" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>146.6</v>
@@ -20128,9 +19562,7 @@
       <c r="T259" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U259" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U259" s="2" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.9</v>
@@ -20203,9 +19635,7 @@
       <c r="T260" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U260" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U260" s="2" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="2" t="n">
         <v>143.2</v>
@@ -20278,9 +19708,7 @@
       <c r="T261" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U261" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U261" s="2" t="inlineStr"/>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>137.2</v>
@@ -20353,9 +19781,7 @@
       <c r="T262" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U262" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U262" s="2" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>140.3</v>
@@ -20428,9 +19854,7 @@
       <c r="T263" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U263" s="2" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.2</v>
@@ -20503,9 +19927,7 @@
       <c r="T264" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U264" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U264" s="2" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>145.7</v>
@@ -20578,9 +20000,7 @@
       <c r="T265" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U265" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U265" s="2" t="inlineStr"/>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="2" t="n">
         <v>143.8</v>
@@ -20657,9 +20077,7 @@
       <c r="T266" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U266" s="2" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="U266" s="2" t="inlineStr"/>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>142.5</v>
@@ -20732,9 +20150,7 @@
       <c r="T267" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U267" s="2" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="U267" s="2" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>139.4</v>
@@ -20807,9 +20223,7 @@
       <c r="T268" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U268" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U268" s="2" t="inlineStr"/>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>140.3</v>
@@ -20882,9 +20296,7 @@
       <c r="T269" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U269" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U269" s="2" t="inlineStr"/>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>139.2</v>
@@ -20957,9 +20369,7 @@
       <c r="T270" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U270" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U270" s="2" t="inlineStr"/>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>141.2</v>
@@ -21032,9 +20442,7 @@
       <c r="T271" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U271" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U271" s="2" t="inlineStr"/>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>145.5</v>
@@ -21107,9 +20515,7 @@
       <c r="T272" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U272" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U272" s="2" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.4</v>
@@ -21182,9 +20588,7 @@
       <c r="T273" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U273" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U273" s="2" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>141.9</v>
@@ -21257,9 +20661,7 @@
       <c r="T274" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U274" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U274" s="2" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.1</v>
@@ -21336,9 +20738,7 @@
       <c r="T275" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U275" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U275" s="2" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.6</v>
@@ -21411,9 +20811,7 @@
       <c r="T276" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U276" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U276" s="2" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>146.7</v>
@@ -21486,9 +20884,7 @@
       <c r="T277" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U277" s="2" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U277" s="2" t="inlineStr"/>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="2" t="n">
         <v>151.8</v>
@@ -21561,9 +20957,7 @@
       <c r="T278" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U278" s="2" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="U278" s="2" t="inlineStr"/>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="2" t="n">
         <v>152.8</v>
@@ -21636,9 +21030,7 @@
       <c r="T279" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U279" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U279" s="2" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>152.9</v>
@@ -21711,9 +21103,7 @@
       <c r="T280" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U280" s="2" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="U280" s="2" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
       <c r="W280" s="2" t="n">
         <v>153.9</v>
@@ -21786,14 +21176,8 @@
       <c r="T281" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="U281" s="3" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="V281" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
       <c r="W281" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21865,9 +21249,7 @@
       <c r="T282" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="U282" s="2" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="U282" s="2" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="1" t="n">
         <v>158</v>
@@ -21940,9 +21322,7 @@
       <c r="T283" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U283" s="2" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="U283" s="2" t="inlineStr"/>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>154.5</v>
@@ -22015,9 +21395,7 @@
       <c r="T284" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U284" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U284" s="2" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>152.4</v>
@@ -22088,9 +21466,7 @@
       <c r="T285" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="U285" s="2" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="U285" s="2" t="inlineStr"/>
       <c r="V285" t="inlineStr"/>
       <c r="W285" s="2" t="n">
         <v>139.9</v>
@@ -22163,14 +21539,8 @@
       <c r="T286" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="U286" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V286" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -22242,9 +21612,7 @@
       <c r="T287" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U287" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U287" s="2" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>141.5</v>
@@ -22317,9 +21685,7 @@
       <c r="T288" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U288" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U288" s="2" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>145</v>
@@ -22392,9 +21758,7 @@
       <c r="T289" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U289" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U289" s="2" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>136.5</v>
@@ -22467,9 +21831,7 @@
       <c r="T290" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U290" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U290" s="2" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
       <c r="W290" s="2" t="n">
         <v>138.3</v>
@@ -22542,14 +21904,8 @@
       <c r="T291" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="U291" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="V291" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>139.1</v>
       </c>
@@ -22621,9 +21977,7 @@
       <c r="T292" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="U292" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U292" s="2" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142</v>
@@ -22696,9 +22050,7 @@
       <c r="T293" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="U293" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U293" s="2" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>142.6</v>
@@ -22771,9 +22123,7 @@
       <c r="T294" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U294" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U294" s="2" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>140.9</v>
@@ -22846,9 +22196,7 @@
       <c r="T295" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="U295" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U295" s="2" t="inlineStr"/>
       <c r="V295" t="inlineStr"/>
       <c r="W295" s="2" t="n">
         <v>144</v>
@@ -22921,14 +22269,8 @@
       <c r="T296" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="U296" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="V296" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>139</v>
       </c>
@@ -23000,9 +22342,7 @@
       <c r="T297" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U297" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U297" s="2" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>142.2</v>
@@ -23075,9 +22415,7 @@
       <c r="T298" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="U298" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U298" s="2" t="inlineStr"/>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>145.4</v>
@@ -23150,9 +22488,7 @@
       <c r="T299" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U299" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U299" s="2" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>143.8</v>
@@ -23225,9 +22561,7 @@
       <c r="T300" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U300" s="3" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="U300" s="2" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>146.9</v>
@@ -23300,9 +22634,7 @@
       <c r="T301" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U301" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U301" s="2" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="2" t="n">
         <v>147.6</v>
@@ -23375,14 +22707,8 @@
       <c r="T302" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="U302" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V302" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -23454,9 +22780,7 @@
       <c r="T303" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U303" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U303" s="2" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>150.4</v>
@@ -23529,9 +22853,7 @@
       <c r="T304" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U304" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U304" s="2" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>143.3</v>
@@ -23604,9 +22926,7 @@
       <c r="T305" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U305" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U305" s="2" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="2" t="n">
         <v>144.2</v>
@@ -23679,9 +22999,7 @@
       <c r="T306" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U306" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U306" s="2" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="1" t="n">
         <v>156.9</v>
@@ -23754,9 +23072,7 @@
       <c r="T307" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U307" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U307" s="2" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>149.9</v>
@@ -23829,9 +23145,7 @@
       <c r="T308" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U308" s="2" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="U308" s="2" t="inlineStr"/>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>139.2</v>
@@ -23904,9 +23218,7 @@
       <c r="T309" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U309" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U309" s="2" t="inlineStr"/>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>140.7</v>
@@ -23979,9 +23291,7 @@
       <c r="T310" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U310" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U310" s="2" t="inlineStr"/>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.8</v>
@@ -24058,9 +23368,7 @@
       <c r="T311" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U311" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U311" s="2" t="inlineStr"/>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>141.9</v>
@@ -24133,9 +23441,7 @@
       <c r="T312" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U312" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U312" s="2" t="inlineStr"/>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.9</v>
@@ -24208,9 +23514,7 @@
       <c r="T313" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U313" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U313" s="2" t="inlineStr"/>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>140.8</v>
@@ -24283,9 +23587,7 @@
       <c r="T314" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U314" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U314" s="2" t="inlineStr"/>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.6</v>
@@ -24358,9 +23660,7 @@
       <c r="T315" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U315" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U315" s="2" t="inlineStr"/>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.1</v>
@@ -24433,9 +23733,7 @@
       <c r="T316" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U316" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U316" s="2" t="inlineStr"/>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>139.6</v>
@@ -24508,9 +23806,7 @@
       <c r="T317" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U317" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U317" s="2" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>138.2</v>
@@ -24583,9 +23879,7 @@
       <c r="T318" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U318" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U318" s="2" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>141.9</v>
@@ -24658,9 +23952,7 @@
       <c r="T319" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U319" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U319" s="2" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>143.3</v>
@@ -24733,9 +24025,7 @@
       <c r="T320" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U320" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U320" s="2" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.4</v>
@@ -24808,9 +24098,7 @@
       <c r="T321" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U321" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U321" s="2" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>141.7</v>
@@ -24883,9 +24171,7 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U322" s="2" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>138.7</v>
@@ -24958,9 +24244,7 @@
       <c r="T323" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U323" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U323" s="2" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>135.4</v>
@@ -25033,9 +24317,7 @@
       <c r="T324" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U324" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U324" s="2" t="inlineStr"/>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>136.1</v>
@@ -25108,9 +24390,7 @@
       <c r="T325" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U325" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U325" s="2" t="inlineStr"/>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>138.2</v>
@@ -25183,9 +24463,7 @@
       <c r="T326" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U326" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U326" s="2" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>140.2</v>
@@ -25258,9 +24536,7 @@
       <c r="T327" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U327" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U327" s="2" t="inlineStr"/>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>139.4</v>
@@ -25333,9 +24609,7 @@
       <c r="T328" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U328" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U328" s="2" t="inlineStr"/>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>141.5</v>
@@ -25408,9 +24682,7 @@
       <c r="T329" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U329" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U329" s="2" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="2" t="n">
         <v>139.3</v>
@@ -25483,9 +24755,7 @@
       <c r="T330" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U330" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U330" s="2" t="inlineStr"/>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>145.8</v>
@@ -25562,9 +24832,7 @@
       <c r="T331" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U331" s="2" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>138.4</v>
@@ -25637,9 +24905,7 @@
       <c r="T332" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U332" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U332" s="2" t="inlineStr"/>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>135.5</v>
@@ -25712,9 +24978,7 @@
       <c r="T333" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U333" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U333" s="2" t="inlineStr"/>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>132.3</v>
@@ -25787,9 +25051,7 @@
       <c r="T334" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U334" s="2" t="n">
-        <v>14</v>
-      </c>
+      <c r="U334" s="2" t="inlineStr"/>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137</v>
@@ -25862,9 +25124,7 @@
       <c r="T335" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U335" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U335" s="2" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>137.4</v>
@@ -25937,9 +25197,7 @@
       <c r="T336" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U336" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U336" s="2" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>139</v>
@@ -26012,9 +25270,7 @@
       <c r="T337" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U337" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U337" s="2" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>138.6</v>
@@ -26087,9 +25343,7 @@
       <c r="T338" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U338" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U338" s="2" t="inlineStr"/>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>139.5</v>
@@ -26162,9 +25416,7 @@
       <c r="T339" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U339" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U339" s="2" t="inlineStr"/>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>144.2</v>
@@ -26241,9 +25493,7 @@
       <c r="T340" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U340" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U340" s="2" t="inlineStr"/>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>142.5</v>
@@ -26316,9 +25566,7 @@
       <c r="T341" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U341" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U341" s="2" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>143.2</v>
@@ -26391,9 +25639,7 @@
       <c r="T342" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U342" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U342" s="2" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>136.9</v>
@@ -26466,9 +25712,7 @@
       <c r="T343" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U343" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U343" s="2" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="2" t="n">
         <v>142.1</v>
@@ -26545,9 +25789,7 @@
       <c r="T344" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U344" s="3" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="U344" s="2" t="inlineStr"/>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="2" t="n">
         <v>152.2</v>
@@ -26620,9 +25862,7 @@
       <c r="T345" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U345" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U345" s="2" t="inlineStr"/>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>145</v>
@@ -26695,9 +25935,7 @@
       <c r="T346" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U346" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="U346" s="2" t="inlineStr"/>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>142</v>
@@ -26774,9 +26012,7 @@
       <c r="T347" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U347" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U347" s="2" t="inlineStr"/>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143.1</v>
@@ -26849,9 +26085,7 @@
       <c r="T348" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U348" s="2" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="U348" s="2" t="inlineStr"/>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>143</v>
@@ -26924,9 +26158,7 @@
       <c r="T349" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U349" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U349" s="2" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>142.6</v>
@@ -26999,9 +26231,7 @@
       <c r="T350" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U350" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U350" s="2" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>144.3</v>
@@ -27078,9 +26308,7 @@
       <c r="T351" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U351" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U351" s="2" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.7</v>
@@ -27153,9 +26381,7 @@
       <c r="T352" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U352" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U352" s="2" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>142.6</v>
@@ -27228,9 +26454,7 @@
       <c r="T353" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U353" s="2" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="U353" s="2" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>146.7</v>
@@ -27303,9 +26527,7 @@
       <c r="T354" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U354" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U354" s="2" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="2" t="n">
         <v>141.9</v>
@@ -27382,9 +26604,7 @@
       <c r="T355" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U355" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U355" s="2" t="inlineStr"/>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="2" t="n">
         <v>143.1</v>
@@ -27457,9 +26677,7 @@
       <c r="T356" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U356" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U356" s="2" t="inlineStr"/>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>145.3</v>
@@ -27532,9 +26750,7 @@
       <c r="T357" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U357" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U357" s="2" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.9</v>
@@ -27607,9 +26823,7 @@
       <c r="T358" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U358" s="2" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="U358" s="2" t="inlineStr"/>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>139.4</v>
@@ -27682,9 +26896,7 @@
       <c r="T359" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U359" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U359" s="2" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>144.5</v>
@@ -27757,9 +26969,7 @@
       <c r="T360" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U360" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U360" s="2" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>149.6</v>
@@ -27832,9 +27042,7 @@
       <c r="T361" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U361" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U361" s="2" t="inlineStr"/>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="2" t="n">
         <v>154.8</v>
@@ -27911,9 +27119,7 @@
       <c r="T362" s="7" t="n">
         <v>16.1</v>
       </c>
-      <c r="U362" s="7" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U362" s="7" t="inlineStr"/>
       <c r="V362" s="4" t="inlineStr"/>
       <c r="W362" s="7" t="n">
         <v>150</v>
@@ -27986,9 +27192,7 @@
       <c r="T363" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U363" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U363" s="2" t="inlineStr"/>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.4</v>
@@ -28061,9 +27265,7 @@
       <c r="T364" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U364" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U364" s="2" t="inlineStr"/>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>145.7</v>
@@ -28140,9 +27342,7 @@
       <c r="T365" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U365" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U365" s="2" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>149.8</v>
@@ -28215,9 +27415,7 @@
       <c r="T366" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U366" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U366" s="2" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.7</v>
@@ -28290,9 +27488,7 @@
       <c r="T367" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U367" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U367" s="2" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="2" t="n">
         <v>144.3</v>
@@ -28369,9 +27565,7 @@
       <c r="T368" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U368" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U368" s="2" t="inlineStr"/>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.7</v>
@@ -28444,9 +27638,7 @@
       <c r="T369" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U369" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U369" s="2" t="inlineStr"/>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>145.1</v>
@@ -28519,9 +27711,7 @@
       <c r="T370" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U370" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U370" s="2" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>148.5</v>
@@ -28594,9 +27784,7 @@
       <c r="T371" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U371" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U371" s="2" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>145.7</v>
@@ -28669,9 +27857,7 @@
       <c r="T372" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U372" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U372" s="2" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>147.3</v>
@@ -31600,7 +30786,7 @@
         <v>358.97</v>
       </c>
       <c r="G412" t="n">
-        <v>32401500</v>
+        <v>32477200</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-1.77</v>
@@ -31671,25 +30857,25 @@
         <v>362.39</v>
       </c>
       <c r="E413" t="n">
-        <v>354.63</v>
+        <v>354.05</v>
       </c>
       <c r="F413" t="n">
-        <v>356.89</v>
+        <v>356.58</v>
       </c>
       <c r="G413" t="n">
-        <v>21872752</v>
+        <v>30215079</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-0.58</v>
+        <v>-0.67</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
       <c r="J413" t="n">
-        <v>356.84</v>
+        <v>356.83</v>
       </c>
       <c r="K413" t="n">
-        <v>360.26</v>
+        <v>360.25</v>
       </c>
       <c r="L413" t="n">
         <v>378.09</v>
@@ -31698,7 +30884,7 @@
         <v>398.32</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>52.72</v>
+        <v>52.58</v>
       </c>
       <c r="O413" t="n">
         <v>29</v>
@@ -31713,18 +30899,24 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S413" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>14.8</v>
+        <v>17.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -30777,28 +30777,44 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="D412" t="n">
+        <v>362.39</v>
+      </c>
+      <c r="E412" t="n">
+        <v>354.05</v>
+      </c>
+      <c r="F412" t="n">
+        <v>356.58</v>
+      </c>
       <c r="G412" t="n">
-        <v>30215079</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>30272800</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>-0.67</v>
       </c>
       <c r="I412" t="n">
         <v>7.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="K412" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="L412" t="n">
+        <v>378.09</v>
+      </c>
+      <c r="M412" t="n">
+        <v>398.32</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>53.63</v>
+        <v>52.58</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -30810,7 +30826,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R412" t="inlineStr"/>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S412" t="n">
         <v>5</v>
       </c>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30837,13 +30837,84 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>357.71</v>
+      </c>
+      <c r="D413" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="E413" t="n">
+        <v>354.89</v>
+      </c>
+      <c r="F413" t="n">
+        <v>361</v>
+      </c>
+      <c r="G413" t="n">
+        <v>16012392</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="K413" t="n">
+        <v>359.52</v>
+      </c>
+      <c r="L413" t="n">
+        <v>377.88</v>
+      </c>
+      <c r="M413" t="n">
+        <v>397.99</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -30790,7 +30790,7 @@
         <v>356.58</v>
       </c>
       <c r="G412" t="n">
-        <v>30272800</v>
+        <v>30317700</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.67</v>
@@ -30864,34 +30864,34 @@
         <v>354.89</v>
       </c>
       <c r="F413" t="n">
-        <v>361</v>
+        <v>358.25</v>
       </c>
       <c r="G413" t="n">
-        <v>16012392</v>
+        <v>28619906</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>1.24</v>
+        <v>0.47</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
       <c r="J413" t="n">
-        <v>358.04</v>
+        <v>357.9</v>
       </c>
       <c r="K413" t="n">
-        <v>359.52</v>
+        <v>359.47</v>
       </c>
       <c r="L413" t="n">
-        <v>377.88</v>
+        <v>377.86</v>
       </c>
       <c r="M413" t="n">
-        <v>397.99</v>
+        <v>397.98</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>56.19</v>
+        <v>55.19</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30905,13 +30905,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -1349,7 +1349,7 @@
         <v>7.4</v>
       </c>
       <c r="J12" t="n">
-        <v>397.81</v>
+        <v>397.82</v>
       </c>
       <c r="K12" t="n">
         <v>390.68</v>
@@ -10270,7 +10270,7 @@
         <v>7.4</v>
       </c>
       <c r="J133" t="n">
-        <v>316.35</v>
+        <v>316.34</v>
       </c>
       <c r="K133" t="n">
         <v>324.08</v>
@@ -12687,7 +12687,7 @@
         <v>7.4</v>
       </c>
       <c r="J166" t="n">
-        <v>371.05</v>
+        <v>371.06</v>
       </c>
       <c r="K166" t="n">
         <v>336.97</v>
@@ -30864,19 +30864,19 @@
         <v>354.89</v>
       </c>
       <c r="F413" t="n">
-        <v>358.25</v>
+        <v>358.08</v>
       </c>
       <c r="G413" t="n">
-        <v>28619906</v>
+        <v>32039274</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
       <c r="J413" t="n">
-        <v>357.9</v>
+        <v>357.89</v>
       </c>
       <c r="K413" t="n">
         <v>359.47</v>
@@ -30885,10 +30885,10 @@
         <v>377.86</v>
       </c>
       <c r="M413" t="n">
-        <v>397.98</v>
+        <v>397.97</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>55.19</v>
+        <v>55.13</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>
@@ -30908,13 +30908,15 @@
         <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>145.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -30855,10 +30855,10 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>357.71</v>
+        <v>357.93</v>
       </c>
       <c r="D413" t="n">
-        <v>365.05</v>
+        <v>365.1</v>
       </c>
       <c r="E413" t="n">
         <v>354.89</v>
@@ -30867,7 +30867,7 @@
         <v>358.08</v>
       </c>
       <c r="G413" t="n">
-        <v>32039274</v>
+        <v>32031100</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>0.42</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30891,7 +30891,7 @@
         <v>55.13</v>
       </c>
       <c r="O413" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30910,13 +30910,84 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U413" s="2" t="inlineStr"/>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>367.59</v>
+      </c>
+      <c r="D414" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="E414" t="n">
+        <v>363.22</v>
+      </c>
+      <c r="F414" t="n">
+        <v>367.99</v>
+      </c>
+      <c r="G414" t="n">
+        <v>28298999</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J414" t="n">
+        <v>358.73</v>
+      </c>
+      <c r="K414" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="L414" t="n">
+        <v>377.83</v>
+      </c>
+      <c r="M414" t="n">
+        <v>397.66</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -30867,7 +30867,7 @@
         <v>358.08</v>
       </c>
       <c r="G413" t="n">
-        <v>32031100</v>
+        <v>32177400</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>0.42</v>
@@ -30937,31 +30937,31 @@
         <v>363.22</v>
       </c>
       <c r="F414" t="n">
-        <v>367.99</v>
+        <v>366.2</v>
       </c>
       <c r="G414" t="n">
-        <v>28298999</v>
+        <v>38770658</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>2.77</v>
+        <v>2.27</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
       <c r="J414" t="n">
-        <v>358.73</v>
+        <v>358.64</v>
       </c>
       <c r="K414" t="n">
-        <v>359.24</v>
+        <v>359.21</v>
       </c>
       <c r="L414" t="n">
-        <v>377.83</v>
+        <v>377.81</v>
       </c>
       <c r="M414" t="n">
         <v>397.66</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>55.47</v>
+        <v>54.8</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>
@@ -30981,13 +30981,15 @@
         <v>4.95</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>145.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -30927,41 +30927,25 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>367.59</v>
-      </c>
-      <c r="D414" t="n">
-        <v>374.12</v>
-      </c>
-      <c r="E414" t="n">
-        <v>363.22</v>
-      </c>
-      <c r="F414" t="n">
-        <v>366.2</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>38770658</v>
       </c>
-      <c r="H414" s="3" t="n">
-        <v>2.27</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
-      <c r="J414" t="n">
-        <v>358.64</v>
-      </c>
-      <c r="K414" t="n">
-        <v>359.21</v>
-      </c>
-      <c r="L414" t="n">
-        <v>377.81</v>
-      </c>
-      <c r="M414" t="n">
-        <v>397.66</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>54.8</v>
+        <v>51.48</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -30927,25 +30927,41 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>367.48</v>
+      </c>
+      <c r="D414" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="E414" t="n">
+        <v>363.22</v>
+      </c>
+      <c r="F414" t="n">
+        <v>366.2</v>
+      </c>
       <c r="G414" t="n">
-        <v>38770658</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>38828500</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>2.27</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>358.64</v>
+      </c>
+      <c r="K414" t="n">
+        <v>359.21</v>
+      </c>
+      <c r="L414" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="M414" t="n">
+        <v>397.66</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>51.48</v>
+        <v>54.8</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30964,7 +30964,7 @@
         <v>54.8</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -30983,13 +30983,84 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>369.28</v>
+      </c>
+      <c r="D415" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="E415" t="n">
+        <v>361.13</v>
+      </c>
+      <c r="F415" t="n">
+        <v>361.29</v>
+      </c>
+      <c r="G415" t="n">
+        <v>11596157</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="I415" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J415" t="n">
+        <v>359.45</v>
+      </c>
+      <c r="K415" t="n">
+        <v>358.98</v>
+      </c>
+      <c r="L415" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="M415" t="n">
+        <v>397.31</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>55.33</v>
+      </c>
+      <c r="O415" t="n">
+        <v>29</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -645,7 +645,9 @@
       <c r="T2" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>168.6</v>
@@ -718,7 +720,9 @@
       <c r="T3" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="1" t="n">
         <v>163.6</v>
@@ -791,7 +795,9 @@
       <c r="T4" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>157.4</v>
@@ -864,7 +870,9 @@
       <c r="T5" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>156.7</v>
@@ -937,7 +945,9 @@
       <c r="T6" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>158.5</v>
@@ -1014,7 +1024,9 @@
       <c r="T7" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>155.4</v>
@@ -1087,7 +1099,9 @@
       <c r="T8" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>159.4</v>
@@ -1164,7 +1178,9 @@
       <c r="T9" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>162.6</v>
@@ -1237,7 +1253,9 @@
       <c r="T10" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>163.6</v>
@@ -1310,7 +1328,9 @@
       <c r="T11" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>166.5</v>
@@ -1383,7 +1403,9 @@
       <c r="T12" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.9</v>
@@ -1456,7 +1478,9 @@
       <c r="T13" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>168.8</v>
@@ -1529,7 +1553,9 @@
       <c r="T14" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>166.1</v>
@@ -1602,7 +1628,9 @@
       <c r="T15" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>163.4</v>
@@ -1675,7 +1703,9 @@
       <c r="T16" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>168</v>
@@ -1748,7 +1778,9 @@
       <c r="T17" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>183.1</v>
@@ -1821,7 +1853,9 @@
       <c r="T18" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>175.8</v>
@@ -1894,7 +1928,9 @@
       <c r="T19" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>178.6</v>
@@ -1967,7 +2003,9 @@
       <c r="T20" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>165</v>
@@ -2040,7 +2078,9 @@
       <c r="T21" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>156.9</v>
@@ -2117,7 +2157,9 @@
       <c r="T22" s="7" t="n">
         <v>19.4</v>
       </c>
-      <c r="U22" s="7" t="inlineStr"/>
+      <c r="U22" s="7" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="5" t="n">
         <v>157.6</v>
@@ -2190,7 +2232,9 @@
       <c r="T23" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="n">
+        <v>20.5</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="2" t="n">
         <v>153.4</v>
@@ -2263,7 +2307,9 @@
       <c r="T24" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>149.3</v>
@@ -2336,7 +2382,9 @@
       <c r="T25" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="1" t="n">
         <v>157.9</v>
@@ -2409,7 +2457,9 @@
       <c r="T26" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="2" t="n">
         <v>154.3</v>
@@ -2482,7 +2532,9 @@
       <c r="T27" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="n">
+        <v>24.6</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>151.4</v>
@@ -2555,7 +2607,9 @@
       <c r="T28" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>138.9</v>
@@ -2632,7 +2686,9 @@
       <c r="T29" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="3" t="n">
+        <v>31.1</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>137.6</v>
@@ -2709,7 +2765,9 @@
       <c r="T30" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="n">
+        <v>24.7</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
         <v>139.9</v>
@@ -2786,8 +2844,14 @@
       <c r="T31" s="6" t="n">
         <v>27.9</v>
       </c>
-      <c r="U31" s="7" t="inlineStr"/>
-      <c r="V31" s="4" t="inlineStr"/>
+      <c r="U31" s="6" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V31" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W31" s="7" t="n">
         <v>146</v>
       </c>
@@ -2863,8 +2927,14 @@
       <c r="T32" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="U32" s="2" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W32" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -2940,7 +3010,9 @@
       <c r="T33" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>128.7</v>
@@ -3017,7 +3089,9 @@
       <c r="T34" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="n">
+        <v>23.4</v>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.9</v>
@@ -3094,7 +3168,9 @@
       <c r="T35" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>130.3</v>
@@ -3167,7 +3243,9 @@
       <c r="T36" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>133.9</v>
@@ -3240,7 +3318,9 @@
       <c r="T37" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>136.8</v>
@@ -3313,7 +3393,9 @@
       <c r="T38" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.4</v>
@@ -3386,7 +3468,9 @@
       <c r="T39" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>140.8</v>
@@ -3459,7 +3543,9 @@
       <c r="T40" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>141.7</v>
@@ -3532,7 +3618,9 @@
       <c r="T41" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>144</v>
@@ -3605,7 +3693,9 @@
       <c r="T42" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>148.7</v>
@@ -3678,7 +3768,9 @@
       <c r="T43" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>144.8</v>
@@ -3751,7 +3843,9 @@
       <c r="T44" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>140.9</v>
@@ -3824,7 +3918,9 @@
       <c r="T45" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="3" t="n">
+        <v>25.4</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>139</v>
@@ -3897,7 +3993,9 @@
       <c r="T46" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>148.6</v>
@@ -3970,7 +4068,9 @@
       <c r="T47" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="n">
+        <v>20.1</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>143</v>
@@ -4043,7 +4143,9 @@
       <c r="T48" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U48" s="2" t="inlineStr"/>
+      <c r="U48" s="3" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>144.3</v>
@@ -4116,8 +4218,14 @@
       <c r="T49" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="U49" s="2" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="U49" s="3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W49" s="2" t="n">
         <v>139.2</v>
       </c>
@@ -4193,8 +4301,14 @@
       <c r="T50" s="6" t="n">
         <v>45.3</v>
       </c>
-      <c r="U50" s="7" t="inlineStr"/>
-      <c r="V50" s="4" t="inlineStr"/>
+      <c r="U50" s="6" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V50" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W50" s="7" t="n">
         <v>136.5</v>
       </c>
@@ -4266,8 +4380,14 @@
       <c r="T51" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U51" s="2" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" s="3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W51" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4339,8 +4459,14 @@
       <c r="T52" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="U52" s="2" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W52" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4412,8 +4538,14 @@
       <c r="T53" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="U53" s="2" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="U53" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W53" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4489,8 +4621,14 @@
       <c r="T54" s="3" t="n">
         <v>40.7</v>
       </c>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="U54" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W54" s="2" t="n">
         <v>127.5</v>
       </c>
@@ -4562,8 +4700,14 @@
       <c r="T55" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="U55" s="2" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" s="3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W55" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4635,7 +4779,9 @@
       <c r="T56" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U56" s="2" t="inlineStr"/>
+      <c r="U56" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>135.7</v>
@@ -4708,7 +4854,9 @@
       <c r="T57" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="U57" s="2" t="inlineStr"/>
+      <c r="U57" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.8</v>
@@ -4781,8 +4929,14 @@
       <c r="T58" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="U58" s="2" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="U58" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W58" s="2" t="n">
         <v>131.3</v>
       </c>
@@ -4854,8 +5008,14 @@
       <c r="T59" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="U59" s="2" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W59" s="2" t="n">
         <v>130</v>
       </c>
@@ -4927,7 +5087,9 @@
       <c r="T60" s="3" t="n">
         <v>33.8</v>
       </c>
-      <c r="U60" s="2" t="inlineStr"/>
+      <c r="U60" s="3" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" s="3" t="n">
         <v>125.8</v>
@@ -5000,7 +5162,9 @@
       <c r="T61" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U61" s="2" t="inlineStr"/>
+      <c r="U61" s="3" t="n">
+        <v>29.1</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="3" t="n">
         <v>125.9</v>
@@ -5073,8 +5237,14 @@
       <c r="T62" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="U62" s="2" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W62" s="3" t="n">
         <v>126.7</v>
       </c>
@@ -5146,7 +5316,9 @@
       <c r="T63" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="U63" s="2" t="inlineStr"/>
+      <c r="U63" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="2" t="n">
         <v>129</v>
@@ -5219,7 +5391,9 @@
       <c r="T64" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="n">
+        <v>23.6</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>132.4</v>
@@ -5292,7 +5466,9 @@
       <c r="T65" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>131.3</v>
@@ -5365,7 +5541,9 @@
       <c r="T66" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>134.3</v>
@@ -5438,7 +5616,9 @@
       <c r="T67" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="n">
+        <v>22.9</v>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>132.7</v>
@@ -5511,7 +5691,9 @@
       <c r="T68" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U68" s="2" t="inlineStr"/>
+      <c r="U68" s="3" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>134.1</v>
@@ -5584,7 +5766,9 @@
       <c r="T69" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.8</v>
@@ -5657,7 +5841,9 @@
       <c r="T70" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.1</v>
@@ -5734,7 +5920,9 @@
       <c r="T71" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>133.2</v>
@@ -5807,7 +5995,9 @@
       <c r="T72" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="n">
+        <v>19.8</v>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>132.2</v>
@@ -5880,7 +6070,9 @@
       <c r="T73" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>131.5</v>
@@ -5953,7 +6145,9 @@
       <c r="T74" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U74" s="2" t="inlineStr"/>
+      <c r="U74" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>128.4</v>
@@ -6026,7 +6220,9 @@
       <c r="T75" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>137.7</v>
@@ -6099,7 +6295,9 @@
       <c r="T76" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>140.5</v>
@@ -6172,7 +6370,9 @@
       <c r="T77" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>138.9</v>
@@ -6245,7 +6445,9 @@
       <c r="T78" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>140.9</v>
@@ -6318,7 +6520,9 @@
       <c r="T79" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>136</v>
@@ -6391,7 +6595,9 @@
       <c r="T80" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>135.9</v>
@@ -6464,7 +6670,9 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>137.3</v>
@@ -6537,7 +6745,9 @@
       <c r="T82" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6610,7 +6820,9 @@
       <c r="T83" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>139</v>
@@ -6683,7 +6895,9 @@
       <c r="T84" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139.3</v>
@@ -6756,7 +6970,9 @@
       <c r="T85" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>140.9</v>
@@ -6829,7 +7045,9 @@
       <c r="T86" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>137.6</v>
@@ -6902,7 +7120,9 @@
       <c r="T87" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.3</v>
@@ -6975,7 +7195,9 @@
       <c r="T88" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>138.2</v>
@@ -7048,7 +7270,9 @@
       <c r="T89" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>141</v>
@@ -7121,7 +7345,9 @@
       <c r="T90" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141.6</v>
@@ -7198,7 +7424,9 @@
       <c r="T91" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>137.5</v>
@@ -7275,7 +7503,9 @@
       <c r="T92" s="7" t="n">
         <v>18.5</v>
       </c>
-      <c r="U92" s="7" t="inlineStr"/>
+      <c r="U92" s="7" t="n">
+        <v>19</v>
+      </c>
       <c r="V92" s="4" t="inlineStr"/>
       <c r="W92" s="7" t="n">
         <v>140.1</v>
@@ -7348,7 +7578,9 @@
       <c r="T93" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>138.9</v>
@@ -7421,7 +7653,9 @@
       <c r="T94" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>139.2</v>
@@ -7494,7 +7728,9 @@
       <c r="T95" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>141.2</v>
@@ -7567,7 +7803,9 @@
       <c r="T96" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.4</v>
@@ -7644,7 +7882,9 @@
       <c r="T97" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>145.6</v>
@@ -7717,7 +7957,9 @@
       <c r="T98" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>149.6</v>
@@ -7790,7 +8032,9 @@
       <c r="T99" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="1" t="n">
         <v>156.6</v>
@@ -7867,7 +8111,9 @@
       <c r="T100" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="n">
+        <v>21</v>
+      </c>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="2" t="n">
         <v>154.4</v>
@@ -7940,7 +8186,9 @@
       <c r="T101" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>148.4</v>
@@ -8013,7 +8261,9 @@
       <c r="T102" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="n">
+        <v>18.4</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>149.2</v>
@@ -8086,7 +8336,9 @@
       <c r="T103" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>154.8</v>
@@ -8159,7 +8411,9 @@
       <c r="T104" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="1" t="n">
         <v>155</v>
@@ -8236,7 +8490,9 @@
       <c r="T105" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="2" t="n">
         <v>152.2</v>
@@ -8309,7 +8565,9 @@
       <c r="T106" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>147.5</v>
@@ -8382,7 +8640,9 @@
       <c r="T107" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>143.4</v>
@@ -8455,7 +8715,9 @@
       <c r="T108" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>139.6</v>
@@ -8532,7 +8794,9 @@
       <c r="T109" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>140.1</v>
@@ -8605,7 +8869,9 @@
       <c r="T110" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>139.3</v>
@@ -8678,7 +8944,9 @@
       <c r="T111" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>141.4</v>
@@ -8755,7 +9023,9 @@
       <c r="T112" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>138</v>
@@ -8828,7 +9098,9 @@
       <c r="T113" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>140.8</v>
@@ -8901,7 +9173,9 @@
       <c r="T114" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>141.8</v>
@@ -8974,7 +9248,9 @@
       <c r="T115" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>143.3</v>
@@ -9047,7 +9323,9 @@
       <c r="T116" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>145</v>
@@ -9120,7 +9398,9 @@
       <c r="T117" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>147</v>
@@ -9197,7 +9477,9 @@
       <c r="T118" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>143.7</v>
@@ -9270,7 +9552,9 @@
       <c r="T119" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>146.7</v>
@@ -9343,7 +9627,9 @@
       <c r="T120" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>151.1</v>
@@ -9416,7 +9702,9 @@
       <c r="T121" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>150.4</v>
@@ -9489,7 +9777,9 @@
       <c r="T122" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>154.8</v>
@@ -9562,7 +9852,9 @@
       <c r="T123" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>153.4</v>
@@ -9635,7 +9927,9 @@
       <c r="T124" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="1" t="n">
         <v>159.3</v>
@@ -9712,7 +10006,9 @@
       <c r="T125" s="7" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="7" t="inlineStr"/>
+      <c r="U125" s="7" t="n">
+        <v>10</v>
+      </c>
       <c r="V125" s="4" t="inlineStr"/>
       <c r="W125" s="5" t="n">
         <v>159.4</v>
@@ -9785,7 +10081,9 @@
       <c r="T126" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="2" t="n">
         <v>145.6</v>
@@ -9858,7 +10156,9 @@
       <c r="T127" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="n">
+        <v>7.9</v>
+      </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>147.6</v>
@@ -9935,7 +10235,9 @@
       <c r="T128" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>149.1</v>
@@ -10008,7 +10310,9 @@
       <c r="T129" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>154.1</v>
@@ -10085,7 +10389,9 @@
       <c r="T130" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>152.3</v>
@@ -10158,7 +10464,9 @@
       <c r="T131" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="1" t="n">
         <v>155.5</v>
@@ -10231,7 +10539,9 @@
       <c r="T132" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>159.3</v>
@@ -10304,7 +10614,9 @@
       <c r="T133" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="2" t="n">
         <v>149.9</v>
@@ -10377,7 +10689,9 @@
       <c r="T134" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.7</v>
@@ -10450,7 +10764,9 @@
       <c r="T135" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>147</v>
@@ -10523,7 +10839,9 @@
       <c r="T136" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147.5</v>
@@ -10596,7 +10914,9 @@
       <c r="T137" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>148.6</v>
@@ -10669,7 +10989,9 @@
       <c r="T138" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>151.4</v>
@@ -10742,7 +11064,9 @@
       <c r="T139" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>153.1</v>
@@ -10815,7 +11139,9 @@
       <c r="T140" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>150.6</v>
@@ -10888,7 +11214,9 @@
       <c r="T141" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>153.8</v>
@@ -10961,7 +11289,9 @@
       <c r="T142" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.9</v>
@@ -11034,7 +11364,9 @@
       <c r="T143" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.2</v>
@@ -11107,7 +11439,9 @@
       <c r="T144" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>144.6</v>
@@ -11184,7 +11518,9 @@
       <c r="T145" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.3</v>
@@ -11257,7 +11593,9 @@
       <c r="T146" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>146.4</v>
@@ -11330,7 +11668,9 @@
       <c r="T147" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>150</v>
@@ -11403,7 +11743,9 @@
       <c r="T148" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="1" t="n">
         <v>156.5</v>
@@ -11476,7 +11818,9 @@
       <c r="T149" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="2" t="n">
         <v>150.9</v>
@@ -11549,7 +11893,9 @@
       <c r="T150" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>152.5</v>
@@ -11622,7 +11968,9 @@
       <c r="T151" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.1</v>
@@ -11699,7 +12047,9 @@
       <c r="T152" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>151.5</v>
@@ -11772,7 +12122,9 @@
       <c r="T153" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>150.2</v>
@@ -11845,7 +12197,9 @@
       <c r="T154" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>154</v>
@@ -11918,7 +12272,9 @@
       <c r="T155" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>148.2</v>
@@ -11991,7 +12347,9 @@
       <c r="T156" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.8</v>
@@ -12064,7 +12422,9 @@
       <c r="T157" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>150.9</v>
@@ -12137,7 +12497,9 @@
       <c r="T158" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>151.9</v>
@@ -12210,7 +12572,9 @@
       <c r="T159" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>147.6</v>
@@ -12283,7 +12647,9 @@
       <c r="T160" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>149.5</v>
@@ -12356,7 +12722,9 @@
       <c r="T161" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>152.1</v>
@@ -12429,7 +12797,9 @@
       <c r="T162" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>148.2</v>
@@ -12502,7 +12872,9 @@
       <c r="T163" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>146.4</v>
@@ -12575,7 +12947,9 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>148.2</v>
@@ -12648,7 +13022,9 @@
       <c r="T165" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>147</v>
@@ -12721,7 +13097,9 @@
       <c r="T166" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>145.5</v>
@@ -12794,7 +13172,9 @@
       <c r="T167" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>146.5</v>
@@ -12867,7 +13247,9 @@
       <c r="T168" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>145.9</v>
@@ -12940,7 +13322,9 @@
       <c r="T169" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -13013,7 +13397,9 @@
       <c r="T170" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>141.5</v>
@@ -13086,7 +13472,9 @@
       <c r="T171" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>143</v>
@@ -13159,7 +13547,9 @@
       <c r="T172" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143.4</v>
@@ -13232,7 +13622,9 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.7</v>
@@ -13305,7 +13697,9 @@
       <c r="T174" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>145.9</v>
@@ -13378,7 +13772,9 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>144.6</v>
@@ -13451,7 +13847,9 @@
       <c r="T176" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>142.5</v>
@@ -13524,7 +13922,9 @@
       <c r="T177" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>145.2</v>
@@ -13597,7 +13997,9 @@
       <c r="T178" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.8</v>
@@ -13670,7 +14072,9 @@
       <c r="T179" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.3</v>
@@ -13747,7 +14151,9 @@
       <c r="T180" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U180" s="2" t="inlineStr"/>
+      <c r="U180" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>138.9</v>
@@ -13820,7 +14226,9 @@
       <c r="T181" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="2" t="n">
         <v>142.8</v>
@@ -13897,7 +14305,9 @@
       <c r="T182" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="n">
+        <v>17.7</v>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>146.5</v>
@@ -13970,7 +14380,9 @@
       <c r="T183" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>145</v>
@@ -14047,7 +14459,9 @@
       <c r="T184" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>147.1</v>
@@ -14120,7 +14534,9 @@
       <c r="T185" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.6</v>
@@ -14193,7 +14609,9 @@
       <c r="T186" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>151.3</v>
@@ -14266,7 +14684,9 @@
       <c r="T187" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="2" t="n">
         <v>149.9</v>
@@ -14339,7 +14759,9 @@
       <c r="T188" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>152.9</v>
@@ -14412,7 +14834,9 @@
       <c r="T189" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>154.3</v>
@@ -14489,7 +14913,9 @@
       <c r="T190" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>153.5</v>
@@ -14562,7 +14988,9 @@
       <c r="T191" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>148.5</v>
@@ -14635,7 +15063,9 @@
       <c r="T192" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>140.4</v>
@@ -14708,7 +15138,9 @@
       <c r="T193" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>139.4</v>
@@ -14781,7 +15213,9 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>141.1</v>
@@ -14854,7 +15288,9 @@
       <c r="T195" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>142.8</v>
@@ -14927,7 +15363,9 @@
       <c r="T196" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142</v>
@@ -15000,7 +15438,9 @@
       <c r="T197" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>144</v>
@@ -15073,7 +15513,9 @@
       <c r="T198" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>143.6</v>
@@ -15146,7 +15588,9 @@
       <c r="T199" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.5</v>
@@ -15223,7 +15667,9 @@
       <c r="T200" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>141.3</v>
@@ -15296,7 +15742,9 @@
       <c r="T201" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>142.9</v>
@@ -15369,7 +15817,9 @@
       <c r="T202" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>143.4</v>
@@ -15442,7 +15892,9 @@
       <c r="T203" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>138.6</v>
@@ -15519,7 +15971,9 @@
       <c r="T204" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>142.5</v>
@@ -15592,7 +16046,9 @@
       <c r="T205" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>137.9</v>
@@ -15665,7 +16121,9 @@
       <c r="T206" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="n">
+        <v>19.4</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>140.9</v>
@@ -15738,7 +16196,9 @@
       <c r="T207" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="n">
+        <v>20.9</v>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>143</v>
@@ -15811,7 +16271,9 @@
       <c r="T208" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U208" s="2" t="inlineStr"/>
+      <c r="U208" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143.1</v>
@@ -15884,8 +16346,14 @@
       <c r="T209" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="U209" s="2" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+      <c r="U209" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V209" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W209" s="2" t="n">
         <v>145</v>
       </c>
@@ -15957,7 +16425,9 @@
       <c r="T210" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>148.3</v>
@@ -16030,7 +16500,9 @@
       <c r="T211" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.6</v>
@@ -16103,7 +16575,9 @@
       <c r="T212" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>151.7</v>
@@ -16176,7 +16650,9 @@
       <c r="T213" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>145</v>
@@ -16249,7 +16725,9 @@
       <c r="T214" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>143</v>
@@ -16322,7 +16800,9 @@
       <c r="T215" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>144.9</v>
@@ -16395,7 +16875,9 @@
       <c r="T216" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16468,7 +16950,9 @@
       <c r="T217" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>149.2</v>
@@ -16541,7 +17025,9 @@
       <c r="T218" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>148.9</v>
@@ -16614,7 +17100,9 @@
       <c r="T219" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.8</v>
@@ -16687,7 +17175,9 @@
       <c r="T220" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>150.6</v>
@@ -16760,7 +17250,9 @@
       <c r="T221" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.3</v>
@@ -16833,7 +17325,9 @@
       <c r="T222" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>147.6</v>
@@ -16906,7 +17400,9 @@
       <c r="T223" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>148.3</v>
@@ -16979,7 +17475,9 @@
       <c r="T224" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>153.6</v>
@@ -17052,7 +17550,9 @@
       <c r="T225" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="1" t="n">
         <v>161.9</v>
@@ -17125,7 +17625,9 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>157</v>
@@ -17198,7 +17700,9 @@
       <c r="T227" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U227" s="2" t="inlineStr"/>
+      <c r="U227" s="2" t="n">
+        <v>16.9</v>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="2" t="n">
         <v>153.5</v>
@@ -17271,7 +17775,9 @@
       <c r="T228" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="1" t="n">
         <v>155.4</v>
@@ -17344,7 +17850,9 @@
       <c r="T229" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U229" s="2" t="inlineStr"/>
+      <c r="U229" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.9</v>
@@ -17417,7 +17925,9 @@
       <c r="T230" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U230" s="2" t="inlineStr"/>
+      <c r="U230" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>159.9</v>
@@ -17490,7 +18000,9 @@
       <c r="T231" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>160.5</v>
@@ -17563,7 +18075,9 @@
       <c r="T232" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U232" s="2" t="inlineStr"/>
+      <c r="U232" s="2" t="n">
+        <v>7.4</v>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -17636,7 +18150,9 @@
       <c r="T233" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U233" s="2" t="inlineStr"/>
+      <c r="U233" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="2" t="n">
         <v>151.4</v>
@@ -17713,7 +18229,9 @@
       <c r="T234" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U234" s="2" t="inlineStr"/>
+      <c r="U234" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="2" t="n">
         <v>150.5</v>
@@ -17786,7 +18304,9 @@
       <c r="T235" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>148.3</v>
@@ -17859,7 +18379,9 @@
       <c r="T236" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U236" s="2" t="inlineStr"/>
+      <c r="U236" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.7</v>
@@ -17936,7 +18458,9 @@
       <c r="T237" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U237" s="2" t="inlineStr"/>
+      <c r="U237" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>141.9</v>
@@ -18009,7 +18533,9 @@
       <c r="T238" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U238" s="2" t="inlineStr"/>
+      <c r="U238" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>142.4</v>
@@ -18086,7 +18612,9 @@
       <c r="T239" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>146.2</v>
@@ -18159,7 +18687,9 @@
       <c r="T240" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U240" s="2" t="inlineStr"/>
+      <c r="U240" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>143.6</v>
@@ -18232,7 +18762,9 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="inlineStr"/>
+      <c r="U241" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>147.1</v>
@@ -18305,7 +18837,9 @@
       <c r="T242" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U242" s="2" t="inlineStr"/>
+      <c r="U242" s="2" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>146</v>
@@ -18378,7 +18912,9 @@
       <c r="T243" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>149.8</v>
@@ -18451,7 +18987,9 @@
       <c r="T244" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>151.6</v>
@@ -18528,7 +19066,9 @@
       <c r="T245" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>152.5</v>
@@ -18601,7 +19141,9 @@
       <c r="T246" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>151.6</v>
@@ -18674,7 +19216,9 @@
       <c r="T247" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U247" s="2" t="inlineStr"/>
+      <c r="U247" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>153.6</v>
@@ -18747,7 +19291,9 @@
       <c r="T248" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U248" s="2" t="inlineStr"/>
+      <c r="U248" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="1" t="n">
         <v>155</v>
@@ -18820,7 +19366,9 @@
       <c r="T249" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U249" s="2" t="inlineStr"/>
+      <c r="U249" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="2" t="n">
         <v>144.4</v>
@@ -18893,7 +19441,9 @@
       <c r="T250" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U250" s="2" t="inlineStr"/>
+      <c r="U250" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>141.3</v>
@@ -18966,7 +19516,9 @@
       <c r="T251" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U251" s="2" t="inlineStr"/>
+      <c r="U251" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>144</v>
@@ -19043,7 +19595,9 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="inlineStr"/>
+      <c r="U252" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>148.1</v>
@@ -19116,7 +19670,9 @@
       <c r="T253" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U253" s="2" t="inlineStr"/>
+      <c r="U253" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>147.2</v>
@@ -19189,7 +19745,9 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="inlineStr"/>
+      <c r="U254" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>145</v>
@@ -19266,7 +19824,9 @@
       <c r="T255" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U255" s="2" t="inlineStr"/>
+      <c r="U255" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>143.7</v>
@@ -19339,7 +19899,9 @@
       <c r="T256" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U256" s="2" t="inlineStr"/>
+      <c r="U256" s="2" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="2" t="n">
         <v>143.6</v>
@@ -19412,7 +19974,9 @@
       <c r="T257" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U257" s="2" t="inlineStr"/>
+      <c r="U257" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="2" t="n">
         <v>146.6</v>
@@ -19489,7 +20053,9 @@
       <c r="T258" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U258" s="2" t="inlineStr"/>
+      <c r="U258" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>143.9</v>
@@ -19562,7 +20128,9 @@
       <c r="T259" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U259" s="2" t="inlineStr"/>
+      <c r="U259" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.2</v>
@@ -19635,7 +20203,9 @@
       <c r="T260" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U260" s="2" t="inlineStr"/>
+      <c r="U260" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="2" t="n">
         <v>137.2</v>
@@ -19708,7 +20278,9 @@
       <c r="T261" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U261" s="2" t="inlineStr"/>
+      <c r="U261" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>140.3</v>
@@ -19781,7 +20353,9 @@
       <c r="T262" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U262" s="2" t="inlineStr"/>
+      <c r="U262" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>145.2</v>
@@ -19854,7 +20428,9 @@
       <c r="T263" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.7</v>
@@ -19927,7 +20503,9 @@
       <c r="T264" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>143.8</v>
@@ -20004,7 +20582,9 @@
       <c r="T265" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U265" s="2" t="inlineStr"/>
+      <c r="U265" s="2" t="n">
+        <v>21.5</v>
+      </c>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="2" t="n">
         <v>142.5</v>
@@ -20077,7 +20657,9 @@
       <c r="T266" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U266" s="2" t="inlineStr"/>
+      <c r="U266" s="2" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>139.4</v>
@@ -20150,7 +20732,9 @@
       <c r="T267" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U267" s="2" t="inlineStr"/>
+      <c r="U267" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>140.3</v>
@@ -20223,7 +20807,9 @@
       <c r="T268" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U268" s="2" t="inlineStr"/>
+      <c r="U268" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>139.2</v>
@@ -20296,7 +20882,9 @@
       <c r="T269" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U269" s="2" t="inlineStr"/>
+      <c r="U269" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>141.2</v>
@@ -20369,7 +20957,9 @@
       <c r="T270" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U270" s="2" t="inlineStr"/>
+      <c r="U270" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>145.5</v>
@@ -20442,7 +21032,9 @@
       <c r="T271" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U271" s="2" t="inlineStr"/>
+      <c r="U271" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>141.4</v>
@@ -20515,7 +21107,9 @@
       <c r="T272" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U272" s="2" t="inlineStr"/>
+      <c r="U272" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.9</v>
@@ -20588,7 +21182,9 @@
       <c r="T273" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U273" s="2" t="inlineStr"/>
+      <c r="U273" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>146.1</v>
@@ -20665,7 +21261,9 @@
       <c r="T274" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.6</v>
@@ -20738,7 +21336,9 @@
       <c r="T275" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.7</v>
@@ -20811,7 +21411,9 @@
       <c r="T276" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>151.8</v>
@@ -20884,7 +21486,9 @@
       <c r="T277" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U277" s="2" t="inlineStr"/>
+      <c r="U277" s="2" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="2" t="n">
         <v>152.8</v>
@@ -20957,7 +21561,9 @@
       <c r="T278" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="2" t="n">
         <v>152.9</v>
@@ -21030,7 +21636,9 @@
       <c r="T279" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U279" s="2" t="inlineStr"/>
+      <c r="U279" s="2" t="n">
+        <v>21.9</v>
+      </c>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>153.9</v>
@@ -21103,8 +21711,14 @@
       <c r="T280" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="U280" s="2" t="inlineStr"/>
-      <c r="V280" t="inlineStr"/>
+      <c r="U280" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V280" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W280" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21176,7 +21790,9 @@
       <c r="T281" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="U281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="n">
+        <v>22.7</v>
+      </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="1" t="n">
         <v>158</v>
@@ -21249,7 +21865,9 @@
       <c r="T282" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="n">
+        <v>21.3</v>
+      </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="2" t="n">
         <v>154.5</v>
@@ -21322,7 +21940,9 @@
       <c r="T283" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U283" s="2" t="inlineStr"/>
+      <c r="U283" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>152.4</v>
@@ -21393,7 +22013,9 @@
       <c r="T284" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="U284" s="2" t="inlineStr"/>
+      <c r="U284" s="2" t="n">
+        <v>24.2</v>
+      </c>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>139.9</v>
@@ -21466,8 +22088,14 @@
       <c r="T285" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="U285" s="2" t="inlineStr"/>
-      <c r="V285" t="inlineStr"/>
+      <c r="U285" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="V285" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W285" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -21539,7 +22167,9 @@
       <c r="T286" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U286" s="2" t="inlineStr"/>
+      <c r="U286" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>141.5</v>
@@ -21612,7 +22242,9 @@
       <c r="T287" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U287" s="2" t="inlineStr"/>
+      <c r="U287" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>145</v>
@@ -21685,7 +22317,9 @@
       <c r="T288" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U288" s="2" t="inlineStr"/>
+      <c r="U288" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>136.5</v>
@@ -21758,7 +22392,9 @@
       <c r="T289" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U289" s="2" t="inlineStr"/>
+      <c r="U289" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>138.3</v>
@@ -21831,8 +22467,14 @@
       <c r="T290" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="U290" s="2" t="inlineStr"/>
-      <c r="V290" t="inlineStr"/>
+      <c r="U290" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V290" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W290" s="2" t="n">
         <v>139.1</v>
       </c>
@@ -21904,7 +22546,9 @@
       <c r="T291" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="U291" s="2" t="inlineStr"/>
+      <c r="U291" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>142</v>
@@ -21977,7 +22621,9 @@
       <c r="T292" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="U292" s="2" t="inlineStr"/>
+      <c r="U292" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142.6</v>
@@ -22050,7 +22696,9 @@
       <c r="T293" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U293" s="2" t="inlineStr"/>
+      <c r="U293" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>140.9</v>
@@ -22123,7 +22771,9 @@
       <c r="T294" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="U294" s="2" t="inlineStr"/>
+      <c r="U294" s="2" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>144</v>
@@ -22196,8 +22846,14 @@
       <c r="T295" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="U295" s="2" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
+      <c r="U295" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="V295" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W295" s="2" t="n">
         <v>139</v>
       </c>
@@ -22269,7 +22925,9 @@
       <c r="T296" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U296" s="2" t="inlineStr"/>
+      <c r="U296" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>142.2</v>
@@ -22342,7 +23000,9 @@
       <c r="T297" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="U297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>145.4</v>
@@ -22415,7 +23075,9 @@
       <c r="T298" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U298" s="2" t="inlineStr"/>
+      <c r="U298" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>143.8</v>
@@ -22488,7 +23150,9 @@
       <c r="T299" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U299" s="2" t="inlineStr"/>
+      <c r="U299" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>146.9</v>
@@ -22561,7 +23225,9 @@
       <c r="T300" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>147.6</v>
@@ -22634,8 +23300,14 @@
       <c r="T301" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="U301" s="2" t="inlineStr"/>
-      <c r="V301" t="inlineStr"/>
+      <c r="U301" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V301" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W301" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -22707,7 +23379,9 @@
       <c r="T302" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>150.4</v>
@@ -22780,7 +23454,9 @@
       <c r="T303" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U303" s="2" t="inlineStr"/>
+      <c r="U303" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>143.3</v>
@@ -22853,7 +23529,9 @@
       <c r="T304" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U304" s="2" t="inlineStr"/>
+      <c r="U304" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>144.2</v>
@@ -22926,7 +23604,9 @@
       <c r="T305" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U305" s="2" t="inlineStr"/>
+      <c r="U305" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="1" t="n">
         <v>156.9</v>
@@ -22999,7 +23679,9 @@
       <c r="T306" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U306" s="2" t="inlineStr"/>
+      <c r="U306" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="2" t="n">
         <v>149.9</v>
@@ -23072,7 +23754,9 @@
       <c r="T307" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>139.2</v>
@@ -23145,7 +23829,9 @@
       <c r="T308" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U308" s="2" t="inlineStr"/>
+      <c r="U308" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>140.7</v>
@@ -23218,7 +23904,9 @@
       <c r="T309" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U309" s="2" t="inlineStr"/>
+      <c r="U309" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>141.8</v>
@@ -23295,7 +23983,9 @@
       <c r="T310" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U310" s="2" t="inlineStr"/>
+      <c r="U310" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.9</v>
@@ -23368,7 +24058,9 @@
       <c r="T311" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U311" s="2" t="inlineStr"/>
+      <c r="U311" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>140.9</v>
@@ -23441,7 +24133,9 @@
       <c r="T312" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U312" s="2" t="inlineStr"/>
+      <c r="U312" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.8</v>
@@ -23514,7 +24208,9 @@
       <c r="T313" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U313" s="2" t="inlineStr"/>
+      <c r="U313" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>139.6</v>
@@ -23587,7 +24283,9 @@
       <c r="T314" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U314" s="2" t="inlineStr"/>
+      <c r="U314" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.1</v>
@@ -23660,7 +24358,9 @@
       <c r="T315" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U315" s="2" t="inlineStr"/>
+      <c r="U315" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.6</v>
@@ -23733,7 +24433,9 @@
       <c r="T316" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U316" s="2" t="inlineStr"/>
+      <c r="U316" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>138.2</v>
@@ -23806,7 +24508,9 @@
       <c r="T317" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U317" s="2" t="inlineStr"/>
+      <c r="U317" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>141.9</v>
@@ -23879,7 +24583,9 @@
       <c r="T318" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U318" s="2" t="inlineStr"/>
+      <c r="U318" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>143.3</v>
@@ -23952,7 +24658,9 @@
       <c r="T319" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U319" s="2" t="inlineStr"/>
+      <c r="U319" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>141.4</v>
@@ -24025,7 +24733,9 @@
       <c r="T320" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U320" s="2" t="inlineStr"/>
+      <c r="U320" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.7</v>
@@ -24098,7 +24808,9 @@
       <c r="T321" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U321" s="2" t="inlineStr"/>
+      <c r="U321" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>138.7</v>
@@ -24171,7 +24883,9 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="inlineStr"/>
+      <c r="U322" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>135.4</v>
@@ -24244,7 +24958,9 @@
       <c r="T323" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U323" s="2" t="inlineStr"/>
+      <c r="U323" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>136.1</v>
@@ -24317,7 +25033,9 @@
       <c r="T324" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U324" s="2" t="inlineStr"/>
+      <c r="U324" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>138.2</v>
@@ -24390,7 +25108,9 @@
       <c r="T325" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U325" s="2" t="inlineStr"/>
+      <c r="U325" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>140.2</v>
@@ -24463,7 +25183,9 @@
       <c r="T326" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="2" t="inlineStr"/>
+      <c r="U326" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>139.4</v>
@@ -24536,7 +25258,9 @@
       <c r="T327" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U327" s="2" t="inlineStr"/>
+      <c r="U327" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>141.5</v>
@@ -24609,7 +25333,9 @@
       <c r="T328" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U328" s="2" t="inlineStr"/>
+      <c r="U328" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>139.3</v>
@@ -24682,7 +25408,9 @@
       <c r="T329" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U329" s="2" t="inlineStr"/>
+      <c r="U329" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="2" t="n">
         <v>145.8</v>
@@ -24759,7 +25487,9 @@
       <c r="T330" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U330" s="2" t="inlineStr"/>
+      <c r="U330" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>138.4</v>
@@ -24832,7 +25562,9 @@
       <c r="T331" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U331" s="2" t="inlineStr"/>
+      <c r="U331" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>135.5</v>
@@ -24905,7 +25637,9 @@
       <c r="T332" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U332" s="2" t="inlineStr"/>
+      <c r="U332" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>132.3</v>
@@ -24978,7 +25712,9 @@
       <c r="T333" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U333" s="2" t="inlineStr"/>
+      <c r="U333" s="2" t="n">
+        <v>14</v>
+      </c>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>137</v>
@@ -25051,7 +25787,9 @@
       <c r="T334" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U334" s="2" t="inlineStr"/>
+      <c r="U334" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137.4</v>
@@ -25124,7 +25862,9 @@
       <c r="T335" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U335" s="2" t="inlineStr"/>
+      <c r="U335" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>139</v>
@@ -25197,7 +25937,9 @@
       <c r="T336" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U336" s="2" t="inlineStr"/>
+      <c r="U336" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>138.6</v>
@@ -25270,7 +26012,9 @@
       <c r="T337" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U337" s="2" t="inlineStr"/>
+      <c r="U337" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>139.5</v>
@@ -25343,7 +26087,9 @@
       <c r="T338" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U338" s="2" t="inlineStr"/>
+      <c r="U338" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>144.2</v>
@@ -25420,7 +26166,9 @@
       <c r="T339" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>142.5</v>
@@ -25493,7 +26241,9 @@
       <c r="T340" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U340" s="2" t="inlineStr"/>
+      <c r="U340" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>143.2</v>
@@ -25566,7 +26316,9 @@
       <c r="T341" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U341" s="2" t="inlineStr"/>
+      <c r="U341" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>136.9</v>
@@ -25639,7 +26391,9 @@
       <c r="T342" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U342" s="2" t="inlineStr"/>
+      <c r="U342" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>142.1</v>
@@ -25716,7 +26470,9 @@
       <c r="T343" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U343" s="2" t="inlineStr"/>
+      <c r="U343" s="3" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="2" t="n">
         <v>152.2</v>
@@ -25789,7 +26545,9 @@
       <c r="T344" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="2" t="n">
         <v>145</v>
@@ -25862,7 +26620,9 @@
       <c r="T345" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U345" s="2" t="inlineStr"/>
+      <c r="U345" s="2" t="n">
+        <v>20.6</v>
+      </c>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>142</v>
@@ -25939,7 +26699,9 @@
       <c r="T346" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U346" s="2" t="inlineStr"/>
+      <c r="U346" s="2" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>143.1</v>
@@ -26012,7 +26774,9 @@
       <c r="T347" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U347" s="2" t="inlineStr"/>
+      <c r="U347" s="2" t="n">
+        <v>21.1</v>
+      </c>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143</v>
@@ -26085,7 +26849,9 @@
       <c r="T348" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U348" s="2" t="inlineStr"/>
+      <c r="U348" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>142.6</v>
@@ -26158,7 +26924,9 @@
       <c r="T349" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U349" s="2" t="inlineStr"/>
+      <c r="U349" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>144.3</v>
@@ -26235,7 +27003,9 @@
       <c r="T350" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U350" s="2" t="inlineStr"/>
+      <c r="U350" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>142.7</v>
@@ -26308,7 +27078,9 @@
       <c r="T351" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U351" s="2" t="inlineStr"/>
+      <c r="U351" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.6</v>
@@ -26381,7 +27153,9 @@
       <c r="T352" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U352" s="2" t="inlineStr"/>
+      <c r="U352" s="2" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>146.7</v>
@@ -26454,7 +27228,9 @@
       <c r="T353" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U353" s="2" t="inlineStr"/>
+      <c r="U353" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>141.9</v>
@@ -26531,7 +27307,9 @@
       <c r="T354" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U354" s="2" t="inlineStr"/>
+      <c r="U354" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="2" t="n">
         <v>143.1</v>
@@ -26604,7 +27382,9 @@
       <c r="T355" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U355" s="2" t="inlineStr"/>
+      <c r="U355" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="2" t="n">
         <v>145.3</v>
@@ -26677,7 +27457,9 @@
       <c r="T356" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>139.9</v>
@@ -26750,7 +27532,9 @@
       <c r="T357" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="n">
+        <v>17.6</v>
+      </c>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.4</v>
@@ -26823,7 +27607,9 @@
       <c r="T358" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U358" s="2" t="inlineStr"/>
+      <c r="U358" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>144.5</v>
@@ -26896,7 +27682,9 @@
       <c r="T359" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U359" s="2" t="inlineStr"/>
+      <c r="U359" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>149.6</v>
@@ -26969,7 +27757,9 @@
       <c r="T360" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U360" s="2" t="inlineStr"/>
+      <c r="U360" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>154.8</v>
@@ -27046,7 +27836,9 @@
       <c r="T361" s="7" t="n">
         <v>16.1</v>
       </c>
-      <c r="U361" s="7" t="inlineStr"/>
+      <c r="U361" s="7" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V361" s="4" t="inlineStr"/>
       <c r="W361" s="7" t="n">
         <v>150</v>
@@ -27119,7 +27911,9 @@
       <c r="T362" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="2" t="n">
         <v>145.4</v>
@@ -27192,7 +27986,9 @@
       <c r="T363" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U363" s="2" t="inlineStr"/>
+      <c r="U363" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.7</v>
@@ -27269,7 +28065,9 @@
       <c r="T364" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U364" s="2" t="inlineStr"/>
+      <c r="U364" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>149.8</v>
@@ -27342,7 +28140,9 @@
       <c r="T365" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U365" s="2" t="inlineStr"/>
+      <c r="U365" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>144.7</v>
@@ -27415,7 +28215,9 @@
       <c r="T366" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.3</v>
@@ -27492,7 +28294,9 @@
       <c r="T367" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U367" s="2" t="inlineStr"/>
+      <c r="U367" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="2" t="n">
         <v>145.7</v>
@@ -27565,7 +28369,9 @@
       <c r="T368" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.1</v>
@@ -27638,7 +28444,9 @@
       <c r="T369" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>148.5</v>
@@ -27711,7 +28519,9 @@
       <c r="T370" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U370" s="2" t="inlineStr"/>
+      <c r="U370" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>145.7</v>
@@ -27784,7 +28594,9 @@
       <c r="T371" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U371" s="2" t="inlineStr"/>
+      <c r="U371" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>147.3</v>
@@ -27857,7 +28669,9 @@
       <c r="T372" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U372" s="2" t="inlineStr"/>
+      <c r="U372" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>146.1</v>
@@ -27930,7 +28744,9 @@
       <c r="T373" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U373" s="2" t="inlineStr"/>
+      <c r="U373" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="2" t="n">
         <v>151.7</v>
@@ -28003,7 +28819,9 @@
       <c r="T374" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U374" s="2" t="inlineStr"/>
+      <c r="U374" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="2" t="n">
         <v>150.2</v>
@@ -28080,7 +28898,9 @@
       <c r="T375" s="7" t="n">
         <v>18.7</v>
       </c>
-      <c r="U375" s="7" t="inlineStr"/>
+      <c r="U375" s="7" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V375" s="4" t="inlineStr"/>
       <c r="W375" s="7" t="n">
         <v>145.9</v>
@@ -28157,7 +28977,9 @@
       <c r="T376" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U376" s="2" t="inlineStr"/>
+      <c r="U376" s="2" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" s="2" t="n">
         <v>147.3</v>
@@ -28234,7 +29056,9 @@
       <c r="T377" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U377" s="2" t="inlineStr"/>
+      <c r="U377" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="2" t="n">
         <v>146.6</v>
@@ -28311,7 +29135,9 @@
       <c r="T378" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U378" s="2" t="inlineStr"/>
+      <c r="U378" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V378" t="inlineStr"/>
       <c r="W378" s="2" t="n">
         <v>143</v>
@@ -28388,7 +29214,9 @@
       <c r="T379" s="2" t="n">
         <v>20.7</v>
       </c>
-      <c r="U379" s="2" t="inlineStr"/>
+      <c r="U379" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V379" t="inlineStr"/>
       <c r="W379" s="2" t="n">
         <v>139.6</v>
@@ -28465,7 +29293,9 @@
       <c r="T380" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U380" s="2" t="inlineStr"/>
+      <c r="U380" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="2" t="n">
         <v>139.9</v>
@@ -28542,7 +29372,9 @@
       <c r="T381" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U381" s="2" t="inlineStr"/>
+      <c r="U381" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="2" t="n">
         <v>141.2</v>
@@ -28619,7 +29451,9 @@
       <c r="T382" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U382" s="2" t="inlineStr"/>
+      <c r="U382" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="2" t="n">
         <v>140</v>
@@ -28696,7 +29530,9 @@
       <c r="T383" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U383" s="2" t="inlineStr"/>
+      <c r="U383" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="3" t="n">
         <v>126.4</v>
@@ -28773,7 +29609,9 @@
       <c r="T384" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U384" s="2" t="inlineStr"/>
+      <c r="U384" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="2" t="n">
         <v>133.3</v>
@@ -28850,7 +29688,9 @@
       <c r="T385" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U385" s="2" t="inlineStr"/>
+      <c r="U385" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="2" t="n">
         <v>134.7</v>
@@ -28923,7 +29763,9 @@
       <c r="T386" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U386" s="2" t="inlineStr"/>
+      <c r="U386" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="2" t="n">
         <v>132.6</v>
@@ -28996,7 +29838,9 @@
       <c r="T387" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U387" s="2" t="inlineStr"/>
+      <c r="U387" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="2" t="n">
         <v>137.1</v>
@@ -29069,7 +29913,9 @@
       <c r="T388" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U388" s="2" t="inlineStr"/>
+      <c r="U388" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="2" t="n">
         <v>135.6</v>
@@ -29142,7 +29988,9 @@
       <c r="T389" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="2" t="n">
         <v>136.5</v>
@@ -29215,7 +30063,9 @@
       <c r="T390" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U390" s="2" t="inlineStr"/>
+      <c r="U390" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="2" t="n">
         <v>134.4</v>
@@ -29288,7 +30138,9 @@
       <c r="T391" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U391" s="2" t="inlineStr"/>
+      <c r="U391" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="2" t="n">
         <v>138.4</v>
@@ -29361,7 +30213,9 @@
       <c r="T392" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="2" t="n">
         <v>142.9</v>
@@ -29434,7 +30288,9 @@
       <c r="T393" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U393" s="2" t="inlineStr"/>
+      <c r="U393" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V393" t="inlineStr"/>
       <c r="W393" s="2" t="n">
         <v>143.6</v>
@@ -29507,7 +30363,9 @@
       <c r="T394" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U394" s="2" t="inlineStr"/>
+      <c r="U394" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="2" t="n">
         <v>142.9</v>
@@ -29580,7 +30438,9 @@
       <c r="T395" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="2" t="n">
         <v>143.2</v>
@@ -29653,7 +30513,9 @@
       <c r="T396" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="2" t="n">
         <v>143.9</v>
@@ -29726,7 +30588,9 @@
       <c r="T397" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U397" s="2" t="inlineStr"/>
+      <c r="U397" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="2" t="n">
         <v>145.6</v>
@@ -29799,7 +30663,9 @@
       <c r="T398" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U398" s="2" t="inlineStr"/>
+      <c r="U398" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="2" t="n">
         <v>143.3</v>
@@ -29872,7 +30738,9 @@
       <c r="T399" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="2" t="n">
         <v>143</v>
@@ -29945,7 +30813,9 @@
       <c r="T400" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="2" t="n">
         <v>144.1</v>
@@ -30018,7 +30888,9 @@
       <c r="T401" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U401" s="2" t="inlineStr"/>
+      <c r="U401" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V401" t="inlineStr"/>
       <c r="W401" s="2" t="n">
         <v>149.8</v>
@@ -30091,7 +30963,9 @@
       <c r="T402" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="2" t="n">
         <v>148.5</v>
@@ -30168,7 +31042,9 @@
       <c r="T403" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U403" s="2" t="inlineStr"/>
+      <c r="U403" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V403" t="inlineStr"/>
       <c r="W403" s="2" t="n">
         <v>149.2</v>
@@ -30241,7 +31117,9 @@
       <c r="T404" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U404" s="2" t="inlineStr"/>
+      <c r="U404" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="2" t="n">
         <v>144.1</v>
@@ -30314,7 +31192,9 @@
       <c r="T405" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U405" s="2" t="inlineStr"/>
+      <c r="U405" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="2" t="n">
         <v>150.6</v>
@@ -30391,7 +31271,9 @@
       <c r="T406" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U406" s="2" t="inlineStr"/>
+      <c r="U406" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="2" t="n">
         <v>151.6</v>
@@ -30464,7 +31346,9 @@
       <c r="T407" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="2" t="n">
         <v>148.9</v>
@@ -30537,7 +31421,9 @@
       <c r="T408" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="2" t="n">
         <v>149.2</v>
@@ -30610,7 +31496,9 @@
       <c r="T409" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U409" s="2" t="inlineStr"/>
+      <c r="U409" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V409" t="inlineStr"/>
       <c r="W409" s="2" t="n">
         <v>147</v>
@@ -30683,7 +31571,9 @@
       <c r="T410" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U410" s="2" t="inlineStr"/>
+      <c r="U410" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="2" t="n">
         <v>154.5</v>
@@ -30760,7 +31650,9 @@
       <c r="T411" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U411" s="2" t="inlineStr"/>
+      <c r="U411" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V411" t="inlineStr"/>
       <c r="W411" s="2" t="n">
         <v>152.1</v>
@@ -30837,7 +31729,9 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
@@ -30910,7 +31804,9 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="inlineStr"/>
+      <c r="U413" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
@@ -30983,7 +31879,9 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
@@ -31007,34 +31905,34 @@
         <v>370.9</v>
       </c>
       <c r="E415" t="n">
-        <v>361.13</v>
+        <v>360.75</v>
       </c>
       <c r="F415" t="n">
-        <v>361.29</v>
+        <v>363.11</v>
       </c>
       <c r="G415" t="n">
-        <v>11596157</v>
+        <v>32235094</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-1.34</v>
+        <v>-0.84</v>
       </c>
       <c r="I415" t="n">
         <v>7.4</v>
       </c>
       <c r="J415" t="n">
-        <v>359.45</v>
+        <v>359.54</v>
       </c>
       <c r="K415" t="n">
-        <v>358.98</v>
+        <v>359.01</v>
       </c>
       <c r="L415" t="n">
-        <v>377.81</v>
+        <v>377.82</v>
       </c>
       <c r="M415" t="n">
-        <v>397.31</v>
+        <v>397.32</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>55.33</v>
+        <v>56.2</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31054,10 +31952,10 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31836,7 +31836,7 @@
         <v>366.2</v>
       </c>
       <c r="G414" t="n">
-        <v>38828500</v>
+        <v>38924100</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>2.27</v>
@@ -31908,31 +31908,31 @@
         <v>360.75</v>
       </c>
       <c r="F415" t="n">
-        <v>363.11</v>
+        <v>364.27</v>
       </c>
       <c r="G415" t="n">
-        <v>32235094</v>
+        <v>51771532</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-0.84</v>
+        <v>-0.53</v>
       </c>
       <c r="I415" t="n">
         <v>7.4</v>
       </c>
       <c r="J415" t="n">
-        <v>359.54</v>
+        <v>359.6</v>
       </c>
       <c r="K415" t="n">
-        <v>359.01</v>
+        <v>359.03</v>
       </c>
       <c r="L415" t="n">
-        <v>377.82</v>
+        <v>377.83</v>
       </c>
       <c r="M415" t="n">
-        <v>397.32</v>
+        <v>397.33</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>56.2</v>
+        <v>56.77</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31952,13 +31952,15 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>148.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1144,7 @@
         <v>7.4</v>
       </c>
       <c r="J9" t="n">
-        <v>397.82</v>
+        <v>397.81</v>
       </c>
       <c r="K9" t="n">
         <v>390.68</v>
@@ -10355,7 +10355,7 @@
         <v>7.4</v>
       </c>
       <c r="J130" t="n">
-        <v>316.34</v>
+        <v>316.35</v>
       </c>
       <c r="K130" t="n">
         <v>324.08</v>
@@ -12838,7 +12838,7 @@
         <v>7.4</v>
       </c>
       <c r="J163" t="n">
-        <v>371.06</v>
+        <v>371.05</v>
       </c>
       <c r="K163" t="n">
         <v>336.97</v>
@@ -21762,7 +21762,7 @@
         <v>431.45</v>
       </c>
       <c r="L281" t="n">
-        <v>433.68</v>
+        <v>433.69</v>
       </c>
       <c r="M281" t="n">
         <v>393.31</v>
@@ -31710,7 +31710,7 @@
         <v>56.77</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31736,6 +31736,79 @@
       <c r="W412" s="2" t="n">
         <v>148.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>371.64</v>
+      </c>
+      <c r="D413" t="n">
+        <v>378.36</v>
+      </c>
+      <c r="E413" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="F413" t="n">
+        <v>373.59</v>
+      </c>
+      <c r="G413" t="n">
+        <v>22180518</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="K413" t="n">
+        <v>359</v>
+      </c>
+      <c r="L413" t="n">
+        <v>377.98</v>
+      </c>
+      <c r="M413" t="n">
+        <v>397.05</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -1144,7 +1144,7 @@
         <v>7.4</v>
       </c>
       <c r="J9" t="n">
-        <v>397.81</v>
+        <v>397.82</v>
       </c>
       <c r="K9" t="n">
         <v>390.68</v>
@@ -9897,7 +9897,7 @@
         <v>7.4</v>
       </c>
       <c r="J124" t="n">
-        <v>314.94</v>
+        <v>314.95</v>
       </c>
       <c r="K124" t="n">
         <v>321</v>
@@ -21762,7 +21762,7 @@
         <v>431.45</v>
       </c>
       <c r="L281" t="n">
-        <v>433.69</v>
+        <v>433.68</v>
       </c>
       <c r="M281" t="n">
         <v>393.31</v>
@@ -25834,7 +25834,7 @@
         <v>392.86</v>
       </c>
       <c r="L335" t="n">
-        <v>414.6</v>
+        <v>414.61</v>
       </c>
       <c r="M335" t="n">
         <v>412.13</v>
@@ -31758,31 +31758,31 @@
         <v>371.1</v>
       </c>
       <c r="F413" t="n">
-        <v>373.59</v>
+        <v>375.3</v>
       </c>
       <c r="G413" t="n">
-        <v>22180518</v>
+        <v>36123485</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>2.56</v>
+        <v>3.03</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
       <c r="J413" t="n">
-        <v>360.14</v>
+        <v>360.22</v>
       </c>
       <c r="K413" t="n">
-        <v>359</v>
+        <v>359.03</v>
       </c>
       <c r="L413" t="n">
-        <v>377.98</v>
+        <v>378</v>
       </c>
       <c r="M413" t="n">
-        <v>397.05</v>
+        <v>397.06</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>52.69</v>
+        <v>53.45</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31799,13 +31799,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31761,7 +31761,7 @@
         <v>375.3</v>
       </c>
       <c r="G413" t="n">
-        <v>36123485</v>
+        <v>36296184</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>3.03</v>
@@ -31808,7 +31808,9 @@
         <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>142.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31737,6 +31737,79 @@
         <v>142.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>379.07</v>
+      </c>
+      <c r="D413" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="E413" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="F413" t="n">
+        <v>377.85</v>
+      </c>
+      <c r="G413" t="n">
+        <v>9098781</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>361.67</v>
+      </c>
+      <c r="K413" t="n">
+        <v>359</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="M413" t="n">
+        <v>396.71</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O413" t="n">
+        <v>37</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31752,40 +31752,40 @@
         <v>379.07</v>
       </c>
       <c r="D413" t="n">
-        <v>379.25</v>
+        <v>379.9</v>
       </c>
       <c r="E413" t="n">
         <v>372.88</v>
       </c>
       <c r="F413" t="n">
-        <v>377.85</v>
+        <v>378.99</v>
       </c>
       <c r="G413" t="n">
-        <v>9098781</v>
+        <v>20569038</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>0.68</v>
+        <v>0.98</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
       <c r="J413" t="n">
-        <v>361.67</v>
+        <v>361.72</v>
       </c>
       <c r="K413" t="n">
-        <v>359</v>
+        <v>359.02</v>
       </c>
       <c r="L413" t="n">
-        <v>378.05</v>
+        <v>378.06</v>
       </c>
       <c r="M413" t="n">
-        <v>396.71</v>
+        <v>396.72</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>61.2</v>
+        <v>61.65</v>
       </c>
       <c r="O413" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31802,10 +31802,10 @@
         <v>4.95</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -9822,7 +9822,7 @@
         <v>7.4</v>
       </c>
       <c r="J123" t="n">
-        <v>314.95</v>
+        <v>314.94</v>
       </c>
       <c r="K123" t="n">
         <v>321</v>
@@ -10280,7 +10280,7 @@
         <v>7.4</v>
       </c>
       <c r="J129" t="n">
-        <v>316.35</v>
+        <v>316.34</v>
       </c>
       <c r="K129" t="n">
         <v>324.08</v>
@@ -12763,7 +12763,7 @@
         <v>7.4</v>
       </c>
       <c r="J162" t="n">
-        <v>371.05</v>
+        <v>371.06</v>
       </c>
       <c r="K162" t="n">
         <v>336.97</v>
@@ -31686,7 +31686,7 @@
         <v>375.3</v>
       </c>
       <c r="G412" t="n">
-        <v>36439300</v>
+        <v>36599600</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>3.03</v>
@@ -31752,19 +31752,19 @@
         <v>379.07</v>
       </c>
       <c r="D413" t="n">
-        <v>379.9</v>
+        <v>380.42</v>
       </c>
       <c r="E413" t="n">
         <v>372.88</v>
       </c>
       <c r="F413" t="n">
-        <v>378.99</v>
+        <v>378.9</v>
       </c>
       <c r="G413" t="n">
-        <v>20569038</v>
+        <v>28089930</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
@@ -31782,10 +31782,10 @@
         <v>396.72</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>61.65</v>
+        <v>61.62</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31799,16 +31799,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31707,19 +31707,11 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="n">
-        <v>144.8</v>
-      </c>
+      <c r="W412" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31670,31 +31670,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="D412" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="E412" t="n">
+        <v>378.56</v>
+      </c>
+      <c r="F412" t="n">
+        <v>379.51</v>
+      </c>
       <c r="G412" t="n">
-        <v>28089930</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>20136159</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>1.12</v>
       </c>
       <c r="I412" t="n">
         <v>7.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>361.75</v>
+      </c>
+      <c r="K412" t="n">
+        <v>359.03</v>
+      </c>
+      <c r="L412" t="n">
+        <v>378.06</v>
+      </c>
+      <c r="M412" t="n">
+        <v>396.72</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>60.16</v>
+        <v>61.85</v>
       </c>
       <c r="O412" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31707,9 +31723,15 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25684,7 +25684,7 @@
         <v>392.86</v>
       </c>
       <c r="L333" t="n">
-        <v>414.61</v>
+        <v>414.6</v>
       </c>
       <c r="M333" t="n">
         <v>412.13</v>
@@ -31670,35 +31670,35 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>379.93</v>
+        <v>379.07</v>
       </c>
       <c r="D412" t="n">
-        <v>386.7</v>
+        <v>380.42</v>
       </c>
       <c r="E412" t="n">
-        <v>378.56</v>
+        <v>372.88</v>
       </c>
       <c r="F412" t="n">
-        <v>379.51</v>
+        <v>378.9</v>
       </c>
       <c r="G412" t="n">
-        <v>20136159</v>
+        <v>28229900</v>
       </c>
       <c r="H412" s="3" t="n">
-        <v>1.12</v>
+        <v>0.96</v>
       </c>
       <c r="I412" t="n">
         <v>7.4</v>
       </c>
       <c r="J412" t="n">
-        <v>361.75</v>
+        <v>361.72</v>
       </c>
       <c r="K412" t="n">
-        <v>359.03</v>
+        <v>359.02</v>
       </c>
       <c r="L412" t="n">
         <v>378.06</v>
@@ -31707,10 +31707,10 @@
         <v>396.72</v>
       </c>
       <c r="N412" s="2" t="n">
-        <v>61.85</v>
+        <v>61.62</v>
       </c>
       <c r="O412" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31723,17 +31723,84 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="D413" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="E413" t="n">
+        <v>377.58</v>
+      </c>
+      <c r="F413" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="G413" t="n">
+        <v>32117694</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>363.21</v>
+      </c>
+      <c r="K413" t="n">
+        <v>358.49</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="M413" t="n">
+        <v>396.34</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="O413" t="n">
+        <v>35</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31753,7 +31753,7 @@
         <v>380.12</v>
       </c>
       <c r="G413" t="n">
-        <v>32117694</v>
+        <v>32914670</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>0.32</v>
@@ -31797,10 +31797,12 @@
         <v>15.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31740,41 +31740,25 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>379.93</v>
-      </c>
-      <c r="D413" t="n">
-        <v>386.7</v>
-      </c>
-      <c r="E413" t="n">
-        <v>377.58</v>
-      </c>
-      <c r="F413" t="n">
-        <v>380.12</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
         <v>32914670</v>
       </c>
-      <c r="H413" s="3" t="n">
-        <v>0.32</v>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
-      <c r="J413" t="n">
-        <v>363.21</v>
-      </c>
-      <c r="K413" t="n">
-        <v>358.49</v>
-      </c>
-      <c r="L413" t="n">
-        <v>378.05</v>
-      </c>
-      <c r="M413" t="n">
-        <v>396.34</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="2" t="n">
-        <v>61.73</v>
+        <v>61.25</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31740,25 +31740,41 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="D413" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="E413" t="n">
+        <v>377.58</v>
+      </c>
+      <c r="F413" t="n">
+        <v>380.12</v>
+      </c>
       <c r="G413" t="n">
-        <v>32914670</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>33427400</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.32</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>363.21</v>
+      </c>
+      <c r="K413" t="n">
+        <v>358.49</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="M413" t="n">
+        <v>396.34</v>
+      </c>
       <c r="N413" s="2" t="n">
-        <v>61.25</v>
+        <v>61.73</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31777,7 +31777,7 @@
         <v>61.73</v>
       </c>
       <c r="O413" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31803,6 +31803,79 @@
       <c r="W413" s="2" t="n">
         <v>146.1</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="D414" t="n">
+        <v>383.33</v>
+      </c>
+      <c r="E414" t="n">
+        <v>375.7</v>
+      </c>
+      <c r="F414" t="n">
+        <v>379.16</v>
+      </c>
+      <c r="G414" t="n">
+        <v>19516912</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J414" t="n">
+        <v>364.88</v>
+      </c>
+      <c r="K414" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="M414" t="n">
+        <v>395.97</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31753,7 +31753,7 @@
         <v>380.12</v>
       </c>
       <c r="G413" t="n">
-        <v>33427400</v>
+        <v>33522500</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>0.32</v>
@@ -31825,34 +31825,34 @@
         <v>375.7</v>
       </c>
       <c r="F414" t="n">
-        <v>379.16</v>
+        <v>377.94</v>
       </c>
       <c r="G414" t="n">
-        <v>19516912</v>
+        <v>25925858</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-0.25</v>
+        <v>-0.57</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
       <c r="J414" t="n">
-        <v>364.88</v>
+        <v>364.82</v>
       </c>
       <c r="K414" t="n">
-        <v>357.8</v>
+        <v>357.78</v>
       </c>
       <c r="L414" t="n">
-        <v>378.2</v>
+        <v>378.19</v>
       </c>
       <c r="M414" t="n">
-        <v>395.97</v>
+        <v>395.96</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>51.74</v>
+        <v>50.97</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31864,18 +31864,24 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr"/>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S414" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31815,41 +31815,25 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>377.35</v>
-      </c>
-      <c r="D414" t="n">
-        <v>383.33</v>
-      </c>
-      <c r="E414" t="n">
-        <v>375.7</v>
-      </c>
-      <c r="F414" t="n">
-        <v>377.94</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>25925858</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>-0.57</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
-      <c r="J414" t="n">
-        <v>364.82</v>
-      </c>
-      <c r="K414" t="n">
-        <v>357.78</v>
-      </c>
-      <c r="L414" t="n">
-        <v>378.19</v>
-      </c>
-      <c r="M414" t="n">
-        <v>395.96</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>50.97</v>
+        <v>52.37</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>
@@ -31864,11 +31848,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>3rd: MA120, 50% cash, 5d</t>
-        </is>
-      </c>
+      <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
         <v>5.16</v>
       </c>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31815,25 +31815,41 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="D414" t="n">
+        <v>383.33</v>
+      </c>
+      <c r="E414" t="n">
+        <v>375.7</v>
+      </c>
+      <c r="F414" t="n">
+        <v>377.94</v>
+      </c>
       <c r="G414" t="n">
-        <v>25925858</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>26088000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.57</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="K414" t="n">
+        <v>357.78</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.19</v>
+      </c>
+      <c r="M414" t="n">
+        <v>395.96</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>52.37</v>
+        <v>50.97</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>
@@ -31848,7 +31864,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr"/>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S414" t="n">
         <v>5.16</v>
       </c>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31723,11 +31723,19 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31891,6 +31891,79 @@
         <v>146</v>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>384.9</v>
+      </c>
+      <c r="D415" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="E415" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="F415" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="G415" t="n">
+        <v>35333794</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I415" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J415" t="n">
+        <v>365.79</v>
+      </c>
+      <c r="K415" t="n">
+        <v>356.92</v>
+      </c>
+      <c r="L415" t="n">
+        <v>378.37</v>
+      </c>
+      <c r="M415" t="n">
+        <v>395.63</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="O415" t="n">
+        <v>38</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31836,7 +31836,7 @@
         <v>377.94</v>
       </c>
       <c r="G414" t="n">
-        <v>26088000</v>
+        <v>26165700</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-0.57</v>
@@ -31912,34 +31912,34 @@
         <v>367.67</v>
       </c>
       <c r="F415" t="n">
-        <v>374.15</v>
+        <v>372.11</v>
       </c>
       <c r="G415" t="n">
-        <v>35333794</v>
+        <v>44753533</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-1</v>
+        <v>-1.54</v>
       </c>
       <c r="I415" t="n">
         <v>7.4</v>
       </c>
       <c r="J415" t="n">
-        <v>365.79</v>
+        <v>365.68</v>
       </c>
       <c r="K415" t="n">
-        <v>356.92</v>
+        <v>356.89</v>
       </c>
       <c r="L415" t="n">
-        <v>378.37</v>
+        <v>378.35</v>
       </c>
       <c r="M415" t="n">
-        <v>395.63</v>
+        <v>395.62</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>65.98</v>
+        <v>63.91</v>
       </c>
       <c r="O415" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31953,16 +31953,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31823,25 +31823,41 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>384.62</v>
+      </c>
+      <c r="D414" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="E414" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="F414" t="n">
+        <v>372.11</v>
+      </c>
       <c r="G414" t="n">
-        <v>44753533</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>45925500</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-1.54</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
-      <c r="N414" s="3" t="n">
-        <v>70.22</v>
+      <c r="J414" t="n">
+        <v>365.68</v>
+      </c>
+      <c r="K414" t="n">
+        <v>356.89</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.35</v>
+      </c>
+      <c r="M414" t="n">
+        <v>395.62</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>63.91</v>
       </c>
       <c r="O414" t="n">
         <v>37</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -761,7 +761,7 @@
         <v>7.4</v>
       </c>
       <c r="J4" t="n">
-        <v>397.82</v>
+        <v>397.81</v>
       </c>
       <c r="K4" t="n">
         <v>390.68</v>
@@ -9514,7 +9514,7 @@
         <v>7.4</v>
       </c>
       <c r="J119" t="n">
-        <v>314.94</v>
+        <v>314.95</v>
       </c>
       <c r="K119" t="n">
         <v>321</v>
@@ -9972,7 +9972,7 @@
         <v>7.4</v>
       </c>
       <c r="J125" t="n">
-        <v>316.34</v>
+        <v>316.35</v>
       </c>
       <c r="K125" t="n">
         <v>324.08</v>
@@ -12455,7 +12455,7 @@
         <v>7.4</v>
       </c>
       <c r="J158" t="n">
-        <v>371.06</v>
+        <v>371.05</v>
       </c>
       <c r="K158" t="n">
         <v>336.97</v>
@@ -31732,6 +31732,83 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>368.06</v>
+      </c>
+      <c r="D413" t="n">
+        <v>369.43</v>
+      </c>
+      <c r="E413" t="n">
+        <v>359.26</v>
+      </c>
+      <c r="F413" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="G413" t="n">
+        <v>13733915</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>366.26</v>
+      </c>
+      <c r="K413" t="n">
+        <v>356.34</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.47</v>
+      </c>
+      <c r="M413" t="n">
+        <v>395.2</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -21379,7 +21379,7 @@
         <v>431.45</v>
       </c>
       <c r="L276" t="n">
-        <v>433.68</v>
+        <v>433.69</v>
       </c>
       <c r="M276" t="n">
         <v>393.31</v>
@@ -31751,34 +31751,34 @@
         <v>369.43</v>
       </c>
       <c r="E413" t="n">
-        <v>359.26</v>
+        <v>356.8</v>
       </c>
       <c r="F413" t="n">
-        <v>360.18</v>
+        <v>357.45</v>
       </c>
       <c r="G413" t="n">
-        <v>13733915</v>
+        <v>38349282</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-3.21</v>
+        <v>-3.94</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
       <c r="J413" t="n">
-        <v>366.26</v>
+        <v>366.12</v>
       </c>
       <c r="K413" t="n">
-        <v>356.34</v>
+        <v>356.29</v>
       </c>
       <c r="L413" t="n">
-        <v>378.47</v>
+        <v>378.44</v>
       </c>
       <c r="M413" t="n">
-        <v>395.2</v>
+        <v>395.18</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>43.63</v>
+        <v>41.81</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31799,16 +31799,18 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31737,6 +31737,83 @@
         <v>146.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>358.42</v>
+      </c>
+      <c r="D413" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="E413" t="n">
+        <v>352.01</v>
+      </c>
+      <c r="F413" t="n">
+        <v>353.55</v>
+      </c>
+      <c r="G413" t="n">
+        <v>13003446</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="K413" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.53</v>
+      </c>
+      <c r="M413" t="n">
+        <v>394.69</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -21304,7 +21304,7 @@
         <v>431.45</v>
       </c>
       <c r="L275" t="n">
-        <v>433.69</v>
+        <v>433.68</v>
       </c>
       <c r="M275" t="n">
         <v>393.31</v>
@@ -31682,7 +31682,7 @@
         <v>357.45</v>
       </c>
       <c r="G412" t="n">
-        <v>39347100</v>
+        <v>39452900</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-3.94</v>
@@ -31749,43 +31749,43 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>358.42</v>
+        <v>358.4</v>
       </c>
       <c r="D413" t="n">
         <v>358.74</v>
       </c>
       <c r="E413" t="n">
-        <v>352.01</v>
+        <v>351.67</v>
       </c>
       <c r="F413" t="n">
-        <v>353.55</v>
+        <v>352.84</v>
       </c>
       <c r="G413" t="n">
-        <v>13003446</v>
+        <v>31598253</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-1.09</v>
+        <v>-1.29</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
       <c r="J413" t="n">
-        <v>365.4</v>
+        <v>365.36</v>
       </c>
       <c r="K413" t="n">
-        <v>355.19</v>
+        <v>355.17</v>
       </c>
       <c r="L413" t="n">
-        <v>378.53</v>
+        <v>378.52</v>
       </c>
       <c r="M413" t="n">
         <v>394.69</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>39.66</v>
+        <v>39.26</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31803,13 +31803,13 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="3" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31673,25 +31673,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>358.4</v>
+      </c>
+      <c r="D412" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="E412" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="F412" t="n">
+        <v>352.84</v>
+      </c>
       <c r="G412" t="n">
-        <v>31676972</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>0</v>
+        <v>32408600</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>-1.29</v>
       </c>
       <c r="I412" t="n">
         <v>7.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>365.36</v>
+      </c>
+      <c r="K412" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="L412" t="n">
+        <v>378.52</v>
+      </c>
+      <c r="M412" t="n">
+        <v>394.69</v>
+      </c>
       <c r="N412" s="3" t="n">
-        <v>42.04</v>
+        <v>39.26</v>
       </c>
       <c r="O412" t="n">
         <v>32</v>
@@ -31706,7 +31722,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R412" t="inlineStr"/>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S412" t="n">
         <v>5.26</v>
       </c>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31710,7 +31710,7 @@
         <v>39.26</v>
       </c>
       <c r="O412" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31741,6 +31741,79 @@
         <v>144.6</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>351.79</v>
+      </c>
+      <c r="D413" t="n">
+        <v>354.43</v>
+      </c>
+      <c r="E413" t="n">
+        <v>345.88</v>
+      </c>
+      <c r="F413" t="n">
+        <v>352.37</v>
+      </c>
+      <c r="G413" t="n">
+        <v>28401981</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="K413" t="n">
+        <v>354.33</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.58</v>
+      </c>
+      <c r="M413" t="n">
+        <v>394.22</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31686,7 +31686,7 @@
         <v>352.84</v>
       </c>
       <c r="G412" t="n">
-        <v>32408600</v>
+        <v>32492400</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-1.29</v>
@@ -31756,40 +31756,40 @@
         <v>351.79</v>
       </c>
       <c r="D413" t="n">
-        <v>354.43</v>
+        <v>355.22</v>
       </c>
       <c r="E413" t="n">
         <v>345.88</v>
       </c>
       <c r="F413" t="n">
-        <v>352.37</v>
+        <v>354.81</v>
       </c>
       <c r="G413" t="n">
-        <v>28401981</v>
-      </c>
-      <c r="H413" s="1" t="n">
-        <v>-0.13</v>
+        <v>38511510</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="I413" t="n">
         <v>7.4</v>
       </c>
       <c r="J413" t="n">
-        <v>365.18</v>
+        <v>365.3</v>
       </c>
       <c r="K413" t="n">
-        <v>354.33</v>
+        <v>354.37</v>
       </c>
       <c r="L413" t="n">
-        <v>378.58</v>
+        <v>378.6</v>
       </c>
       <c r="M413" t="n">
-        <v>394.22</v>
+        <v>394.23</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>41.51</v>
+        <v>43.51</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31803,16 +31803,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="3" t="inlineStr"/>
+      <c r="W413" s="3" t="n">
+        <v>141.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31753,7 +31753,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>351.79</v>
+        <v>352.11</v>
       </c>
       <c r="D413" t="n">
         <v>355.22</v>
@@ -31765,7 +31765,7 @@
         <v>354.81</v>
       </c>
       <c r="G413" t="n">
-        <v>38511510</v>
+        <v>39158100</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>0.5600000000000001</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31789,7 +31789,7 @@
         <v>43.51</v>
       </c>
       <c r="O413" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31816,6 +31816,79 @@
         <v>141.9</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>356.81</v>
+      </c>
+      <c r="D414" t="n">
+        <v>359.79</v>
+      </c>
+      <c r="E414" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="F414" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="G414" t="n">
+        <v>16161157</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J414" t="n">
+        <v>365.34</v>
+      </c>
+      <c r="K414" t="n">
+        <v>353.77</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.67</v>
+      </c>
+      <c r="M414" t="n">
+        <v>393.72</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31765,7 +31765,7 @@
         <v>354.81</v>
       </c>
       <c r="G413" t="n">
-        <v>39158100</v>
+        <v>39235800</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>0.5600000000000001</v>
@@ -31837,34 +31837,34 @@
         <v>353.8</v>
       </c>
       <c r="F414" t="n">
-        <v>357.75</v>
+        <v>354.11</v>
       </c>
       <c r="G414" t="n">
-        <v>16161157</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0.83</v>
+        <v>30302824</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.2</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
       <c r="J414" t="n">
-        <v>365.34</v>
+        <v>365.16</v>
       </c>
       <c r="K414" t="n">
-        <v>353.77</v>
+        <v>353.71</v>
       </c>
       <c r="L414" t="n">
-        <v>378.67</v>
+        <v>378.64</v>
       </c>
       <c r="M414" t="n">
-        <v>393.72</v>
+        <v>393.71</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>44.38</v>
+        <v>41.44</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31878,16 +31878,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>142.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31827,41 +31827,25 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>356.81</v>
-      </c>
-      <c r="D414" t="n">
-        <v>359.79</v>
-      </c>
-      <c r="E414" t="n">
-        <v>353.8</v>
-      </c>
-      <c r="F414" t="n">
-        <v>354.11</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>30302824</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>-0.2</v>
+      <c r="H414" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
-      <c r="J414" t="n">
-        <v>365.16</v>
-      </c>
-      <c r="K414" t="n">
-        <v>353.71</v>
-      </c>
-      <c r="L414" t="n">
-        <v>378.64</v>
-      </c>
-      <c r="M414" t="n">
-        <v>393.71</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="3" t="n">
-        <v>41.44</v>
+        <v>41.89</v>
       </c>
       <c r="O414" t="n">
         <v>28</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31827,28 +31827,44 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>356.81</v>
+      </c>
+      <c r="D414" t="n">
+        <v>359.79</v>
+      </c>
+      <c r="E414" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="F414" t="n">
+        <v>354.11</v>
+      </c>
       <c r="G414" t="n">
-        <v>30302824</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0</v>
+        <v>31004400</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.2</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>365.16</v>
+      </c>
+      <c r="K414" t="n">
+        <v>353.71</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.64</v>
+      </c>
+      <c r="M414" t="n">
+        <v>393.71</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>41.89</v>
+        <v>41.44</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31864,7 +31864,7 @@
         <v>41.44</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31890,6 +31890,79 @@
       <c r="W414" s="3" t="n">
         <v>142.8</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="D415" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="E415" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="F415" t="n">
+        <v>372.56</v>
+      </c>
+      <c r="G415" t="n">
+        <v>28028443</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="I415" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J415" t="n">
+        <v>364.96</v>
+      </c>
+      <c r="K415" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="L415" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="M415" t="n">
+        <v>393.19</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="O415" t="n">
+        <v>31</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U415" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31840,7 +31840,7 @@
         <v>354.11</v>
       </c>
       <c r="G414" t="n">
-        <v>31004400</v>
+        <v>31080800</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-0.2</v>
@@ -31906,37 +31906,37 @@
         <v>360.08</v>
       </c>
       <c r="D415" t="n">
-        <v>374.36</v>
+        <v>374.6</v>
       </c>
       <c r="E415" t="n">
         <v>359.41</v>
       </c>
       <c r="F415" t="n">
-        <v>372.56</v>
+        <v>370.59</v>
       </c>
       <c r="G415" t="n">
-        <v>28028443</v>
+        <v>53897748</v>
       </c>
       <c r="H415" s="2" t="n">
-        <v>5.21</v>
+        <v>4.65</v>
       </c>
       <c r="I415" t="n">
         <v>7.4</v>
       </c>
       <c r="J415" t="n">
-        <v>364.96</v>
+        <v>364.87</v>
       </c>
       <c r="K415" t="n">
-        <v>353.14</v>
+        <v>353.11</v>
       </c>
       <c r="L415" t="n">
-        <v>378.81</v>
+        <v>378.79</v>
       </c>
       <c r="M415" t="n">
-        <v>393.19</v>
+        <v>393.18</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>58.69</v>
+        <v>57.62</v>
       </c>
       <c r="O415" t="n">
         <v>31</v>
@@ -31953,13 +31953,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="3" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31827,25 +31827,41 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="D414" t="n">
+        <v>374.6</v>
+      </c>
+      <c r="E414" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="F414" t="n">
+        <v>370.59</v>
+      </c>
       <c r="G414" t="n">
-        <v>54147498</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0</v>
+        <v>55242800</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>4.65</v>
       </c>
       <c r="I414" t="n">
         <v>7.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>364.87</v>
+      </c>
+      <c r="K414" t="n">
+        <v>353.11</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="M414" t="n">
+        <v>393.18</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>45.93</v>
+        <v>57.62</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31714,7 +31714,7 @@
         <v>57.62</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9139,7 +9139,7 @@
         <v>7.4</v>
       </c>
       <c r="J114" t="n">
-        <v>314.95</v>
+        <v>314.94</v>
       </c>
       <c r="K114" t="n">
         <v>321</v>
@@ -9597,7 +9597,7 @@
         <v>7.4</v>
       </c>
       <c r="J120" t="n">
-        <v>316.35</v>
+        <v>316.34</v>
       </c>
       <c r="K120" t="n">
         <v>324.08</v>
@@ -12080,7 +12080,7 @@
         <v>7.4</v>
       </c>
       <c r="J153" t="n">
-        <v>371.05</v>
+        <v>371.06</v>
       </c>
       <c r="K153" t="n">
         <v>336.97</v>
@@ -30871,7 +30871,7 @@
         <v>377.81</v>
       </c>
       <c r="M401" t="n">
-        <v>397.66</v>
+        <v>397.65</v>
       </c>
       <c r="N401" s="2" t="n">
         <v>54.8</v>
@@ -31714,7 +31714,7 @@
         <v>57.62</v>
       </c>
       <c r="O412" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31740,6 +31740,79 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="D413" t="n">
+        <v>381.14</v>
+      </c>
+      <c r="E413" t="n">
+        <v>364.91</v>
+      </c>
+      <c r="F413" t="n">
+        <v>379.42</v>
+      </c>
+      <c r="G413" t="n">
+        <v>28131662</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>366.13</v>
+      </c>
+      <c r="K413" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.92</v>
+      </c>
+      <c r="M413" t="n">
+        <v>392.63</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>63.82</v>
+      </c>
+      <c r="O413" t="n">
+        <v>44</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31615,7 +31615,7 @@
         <v>370.59</v>
       </c>
       <c r="G411" t="n">
-        <v>55242800</v>
+        <v>55330100</v>
       </c>
       <c r="H411" s="3" t="n">
         <v>4.65</v>
@@ -31677,25 +31677,41 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>369</v>
+      </c>
+      <c r="D412" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="E412" t="n">
+        <v>364.91</v>
+      </c>
+      <c r="F412" t="n">
+        <v>378.73</v>
+      </c>
       <c r="G412" t="n">
-        <v>42006295</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>42112900</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="I412" t="n">
         <v>7.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="K412" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="L412" t="n">
+        <v>378.92</v>
+      </c>
+      <c r="M412" t="n">
+        <v>392.63</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>59.49</v>
+        <v>63.51</v>
       </c>
       <c r="O412" t="n">
         <v>43</v>
@@ -31707,7 +31723,7 @@
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>BUY STOP</t>
         </is>
       </c>
       <c r="R412" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31714,7 +31714,7 @@
         <v>63.51</v>
       </c>
       <c r="O412" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31740,6 +31740,79 @@
       <c r="W412" s="2" t="n">
         <v>143</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>382.04</v>
+      </c>
+      <c r="D413" t="n">
+        <v>383.33</v>
+      </c>
+      <c r="E413" t="n">
+        <v>378.52</v>
+      </c>
+      <c r="F413" t="n">
+        <v>380.98</v>
+      </c>
+      <c r="G413" t="n">
+        <v>10388495</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="K413" t="n">
+        <v>352.39</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="M413" t="n">
+        <v>392.2</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="O413" t="n">
+        <v>48</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -608,7 +608,7 @@
         <v>-0.03</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J2" t="n">
         <v>384.57</v>
@@ -683,7 +683,7 @@
         <v>-0.49</v>
       </c>
       <c r="I3" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J3" t="n">
         <v>380.95</v>
@@ -758,7 +758,7 @@
         <v>1.82</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J4" t="n">
         <v>377.77</v>
@@ -833,7 +833,7 @@
         <v>-1.71</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J5" t="n">
         <v>374.74</v>
@@ -908,7 +908,7 @@
         <v>-4.68</v>
       </c>
       <c r="I6" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J6" t="n">
         <v>371.01</v>
@@ -983,7 +983,7 @@
         <v>-2.15</v>
       </c>
       <c r="I7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J7" t="n">
         <v>367.21</v>
@@ -1058,7 +1058,7 @@
         <v>-8.390000000000001</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>362.49</v>
@@ -1137,7 +1137,7 @@
         <v>-3.96</v>
       </c>
       <c r="I9" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>357.12</v>
@@ -1212,7 +1212,7 @@
         <v>-3.04</v>
       </c>
       <c r="I10" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>351.77</v>
@@ -1287,7 +1287,7 @@
         <v>3.91</v>
       </c>
       <c r="I11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J11" t="n">
         <v>346.4</v>
@@ -1362,7 +1362,7 @@
         <v>-2.84</v>
       </c>
       <c r="I12" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J12" t="n">
         <v>340.4</v>
@@ -1437,7 +1437,7 @@
         <v>-4.43</v>
       </c>
       <c r="I13" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J13" t="n">
         <v>334.82</v>
@@ -1512,7 +1512,7 @@
         <v>2.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J14" t="n">
         <v>329.17</v>
@@ -1587,7 +1587,7 @@
         <v>-5.61</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J15" t="n">
         <v>323.43</v>
@@ -1666,7 +1666,7 @@
         <v>-0.3</v>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J16" t="n">
         <v>317.85</v>
@@ -1745,7 +1745,7 @@
         <v>-15.43</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>310.88</v>
@@ -1828,7 +1828,7 @@
         <v>3.79</v>
       </c>
       <c r="I18" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J18" t="n">
         <v>304.87</v>
@@ -1911,7 +1911,7 @@
         <v>7.59</v>
       </c>
       <c r="I19" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J19" t="n">
         <v>300.85</v>
@@ -1990,7 +1990,7 @@
         <v>-2.99</v>
       </c>
       <c r="I20" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
         <v>296.06</v>
@@ -2069,7 +2069,7 @@
         <v>3.86</v>
       </c>
       <c r="I21" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J21" t="n">
         <v>290.76</v>
@@ -2148,7 +2148,7 @@
         <v>-4.79</v>
       </c>
       <c r="I22" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J22" t="n">
         <v>284.87</v>
@@ -2223,7 +2223,7 @@
         <v>-5.34</v>
       </c>
       <c r="I23" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J23" t="n">
         <v>278.43</v>
@@ -2298,7 +2298,7 @@
         <v>4.68</v>
       </c>
       <c r="I24" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J24" t="n">
         <v>272.19</v>
@@ -2373,7 +2373,7 @@
         <v>0.17</v>
       </c>
       <c r="I25" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J25" t="n">
         <v>266.28</v>
@@ -2448,7 +2448,7 @@
         <v>5.27</v>
       </c>
       <c r="I26" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
         <v>261.83</v>
@@ -2523,7 +2523,7 @@
         <v>11.93</v>
       </c>
       <c r="I27" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J27" t="n">
         <v>259.22</v>
@@ -2598,7 +2598,7 @@
         <v>3.5</v>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J28" t="n">
         <v>258.49</v>
@@ -2673,7 +2673,7 @@
         <v>-5.58</v>
       </c>
       <c r="I29" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J29" t="n">
         <v>257.55</v>
@@ -2748,7 +2748,7 @@
         <v>0.39</v>
       </c>
       <c r="I30" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
         <v>257.11</v>
@@ -2823,7 +2823,7 @@
         <v>-3.51</v>
       </c>
       <c r="I31" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J31" t="n">
         <v>255.64</v>
@@ -2898,7 +2898,7 @@
         <v>-1.67</v>
       </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J32" t="n">
         <v>254.37</v>
@@ -2973,7 +2973,7 @@
         <v>3.59</v>
       </c>
       <c r="I33" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J33" t="n">
         <v>254.19</v>
@@ -3048,7 +3048,7 @@
         <v>5.33</v>
       </c>
       <c r="I34" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J34" t="n">
         <v>254.37</v>
@@ -3123,7 +3123,7 @@
         <v>-5.47</v>
       </c>
       <c r="I35" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J35" t="n">
         <v>254.56</v>
@@ -3202,7 +3202,7 @@
         <v>-10.42</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>253.4</v>
@@ -3285,7 +3285,7 @@
         <v>-2.56</v>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J37" t="n">
         <v>253.96</v>
@@ -3364,7 +3364,7 @@
         <v>-4.9</v>
       </c>
       <c r="I38" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J38" t="n">
         <v>253.52</v>
@@ -3443,7 +3443,7 @@
         <v>22.69</v>
       </c>
       <c r="I39" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J39" t="n">
         <v>254.73</v>
@@ -3522,7 +3522,7 @@
         <v>-7.27</v>
       </c>
       <c r="I40" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J40" t="n">
         <v>255.31</v>
@@ -3605,7 +3605,7 @@
         <v>-0.04</v>
       </c>
       <c r="I41" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J41" t="n">
         <v>255.43</v>
@@ -3684,7 +3684,7 @@
         <v>0.02</v>
       </c>
       <c r="I42" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J42" t="n">
         <v>256.15</v>
@@ -3759,7 +3759,7 @@
         <v>0.7</v>
       </c>
       <c r="I43" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J43" t="n">
         <v>257.59</v>
@@ -3834,7 +3834,7 @@
         <v>-4.94</v>
       </c>
       <c r="I44" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J44" t="n">
         <v>257.87</v>
@@ -3913,7 +3913,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J45" t="n">
         <v>258.13</v>
@@ -3992,7 +3992,7 @@
         <v>-5.75</v>
       </c>
       <c r="I46" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J46" t="n">
         <v>257.06</v>
@@ -4067,7 +4067,7 @@
         <v>4.6</v>
       </c>
       <c r="I47" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J47" t="n">
         <v>255.04</v>
@@ -4142,7 +4142,7 @@
         <v>5.37</v>
       </c>
       <c r="I48" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J48" t="n">
         <v>253.17</v>
@@ -4221,7 +4221,7 @@
         <v>3.5</v>
       </c>
       <c r="I49" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J49" t="n">
         <v>252.55</v>
@@ -4296,7 +4296,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J50" t="n">
         <v>253.14</v>
@@ -4371,7 +4371,7 @@
         <v>0.33</v>
       </c>
       <c r="I51" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J51" t="n">
         <v>254.25</v>
@@ -4446,7 +4446,7 @@
         <v>2.15</v>
       </c>
       <c r="I52" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J52" t="n">
         <v>255.9</v>
@@ -4521,7 +4521,7 @@
         <v>-3.38</v>
       </c>
       <c r="I53" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J53" t="n">
         <v>256.58</v>
@@ -4596,7 +4596,7 @@
         <v>-0.58</v>
       </c>
       <c r="I54" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J54" t="n">
         <v>256.47</v>
@@ -4671,7 +4671,7 @@
         <v>2.38</v>
       </c>
       <c r="I55" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J55" t="n">
         <v>257.47</v>
@@ -4746,7 +4746,7 @@
         <v>-2.42</v>
       </c>
       <c r="I56" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J56" t="n">
         <v>259.51</v>
@@ -4821,7 +4821,7 @@
         <v>-1.75</v>
       </c>
       <c r="I57" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J57" t="n">
         <v>261.61</v>
@@ -4900,7 +4900,7 @@
         <v>0.32</v>
       </c>
       <c r="I58" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J58" t="n">
         <v>264.33</v>
@@ -4975,7 +4975,7 @@
         <v>3.11</v>
       </c>
       <c r="I59" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J59" t="n">
         <v>264.96</v>
@@ -5050,7 +5050,7 @@
         <v>4.72</v>
       </c>
       <c r="I60" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J60" t="n">
         <v>267.25</v>
@@ -5125,7 +5125,7 @@
         <v>6.75</v>
       </c>
       <c r="I61" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J61" t="n">
         <v>270.56</v>
@@ -5200,7 +5200,7 @@
         <v>4.93</v>
       </c>
       <c r="I62" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J62" t="n">
         <v>274.64</v>
@@ -5275,7 +5275,7 @@
         <v>4.07</v>
       </c>
       <c r="I63" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J63" t="n">
         <v>279.32</v>
@@ -5350,7 +5350,7 @@
         <v>-1.4</v>
       </c>
       <c r="I64" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J64" t="n">
         <v>284.38</v>
@@ -5425,7 +5425,7 @@
         <v>2.09</v>
       </c>
       <c r="I65" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J65" t="n">
         <v>289.82</v>
@@ -5500,7 +5500,7 @@
         <v>-2.25</v>
       </c>
       <c r="I66" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J66" t="n">
         <v>295.54</v>
@@ -5575,7 +5575,7 @@
         <v>0.51</v>
       </c>
       <c r="I67" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J67" t="n">
         <v>300.84</v>
@@ -5650,7 +5650,7 @@
         <v>-2.68</v>
       </c>
       <c r="I68" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J68" t="n">
         <v>305.03</v>
@@ -5725,7 +5725,7 @@
         <v>1.92</v>
       </c>
       <c r="I69" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J69" t="n">
         <v>309.11</v>
@@ -5800,7 +5800,7 @@
         <v>-0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J70" t="n">
         <v>311.83</v>
@@ -5875,7 +5875,7 @@
         <v>6.94</v>
       </c>
       <c r="I71" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J71" t="n">
         <v>315.68</v>
@@ -5950,7 +5950,7 @@
         <v>-1.65</v>
       </c>
       <c r="I72" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J72" t="n">
         <v>318.92</v>
@@ -6025,7 +6025,7 @@
         <v>0.43</v>
       </c>
       <c r="I73" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J73" t="n">
         <v>322.74</v>
@@ -6100,7 +6100,7 @@
         <v>-3.34</v>
       </c>
       <c r="I74" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J74" t="n">
         <v>326.03</v>
@@ -6175,7 +6175,7 @@
         <v>-1.09</v>
       </c>
       <c r="I75" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J75" t="n">
         <v>328.81</v>
@@ -6250,7 +6250,7 @@
         <v>0.46</v>
       </c>
       <c r="I76" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J76" t="n">
         <v>332.01</v>
@@ -6325,7 +6325,7 @@
         <v>-3.55</v>
       </c>
       <c r="I77" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J77" t="n">
         <v>334.84</v>
@@ -6404,7 +6404,7 @@
         <v>-14.26</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>335.27</v>
@@ -6483,7 +6483,7 @@
         <v>3.67</v>
       </c>
       <c r="I79" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J79" t="n">
         <v>335.78</v>
@@ -6558,7 +6558,7 @@
         <v>4.55</v>
       </c>
       <c r="I80" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J80" t="n">
         <v>336.3</v>
@@ -6633,7 +6633,7 @@
         <v>5.67</v>
       </c>
       <c r="I81" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J81" t="n">
         <v>336.68</v>
@@ -6708,7 +6708,7 @@
         <v>0.1</v>
       </c>
       <c r="I82" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J82" t="n">
         <v>336.3</v>
@@ -6783,7 +6783,7 @@
         <v>-2.24</v>
       </c>
       <c r="I83" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J83" t="n">
         <v>334.87</v>
@@ -6862,7 +6862,7 @@
         <v>1.94</v>
       </c>
       <c r="I84" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J84" t="n">
         <v>334</v>
@@ -6937,7 +6937,7 @@
         <v>1.17</v>
       </c>
       <c r="I85" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J85" t="n">
         <v>332.95</v>
@@ -7012,7 +7012,7 @@
         <v>-3.88</v>
       </c>
       <c r="I86" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J86" t="n">
         <v>331.67</v>
@@ -7091,7 +7091,7 @@
         <v>1.8</v>
       </c>
       <c r="I87" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J87" t="n">
         <v>330.58</v>
@@ -7166,7 +7166,7 @@
         <v>0.03</v>
       </c>
       <c r="I88" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J88" t="n">
         <v>329.96</v>
@@ -7241,7 +7241,7 @@
         <v>8.23</v>
       </c>
       <c r="I89" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J89" t="n">
         <v>330.34</v>
@@ -7316,7 +7316,7 @@
         <v>-2.35</v>
       </c>
       <c r="I90" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J90" t="n">
         <v>330.39</v>
@@ -7391,7 +7391,7 @@
         <v>-3.79</v>
       </c>
       <c r="I91" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J91" t="n">
         <v>328.63</v>
@@ -7470,7 +7470,7 @@
         <v>-0.54</v>
       </c>
       <c r="I92" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J92" t="n">
         <v>327.07</v>
@@ -7545,7 +7545,7 @@
         <v>-0.66</v>
       </c>
       <c r="I93" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J93" t="n">
         <v>325.33</v>
@@ -7620,7 +7620,7 @@
         <v>-1.84</v>
       </c>
       <c r="I94" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J94" t="n">
         <v>323.89</v>
@@ -7695,7 +7695,7 @@
         <v>-5.34</v>
       </c>
       <c r="I95" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J95" t="n">
         <v>321.79</v>
@@ -7774,7 +7774,7 @@
         <v>4.97</v>
       </c>
       <c r="I96" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J96" t="n">
         <v>320.36</v>
@@ -7849,7 +7849,7 @@
         <v>-0.1</v>
       </c>
       <c r="I97" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J97" t="n">
         <v>319.53</v>
@@ -7924,7 +7924,7 @@
         <v>-6.79</v>
       </c>
       <c r="I98" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J98" t="n">
         <v>319.99</v>
@@ -8003,7 +8003,7 @@
         <v>1.32</v>
       </c>
       <c r="I99" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J99" t="n">
         <v>320.12</v>
@@ -8078,7 +8078,7 @@
         <v>-0.65</v>
       </c>
       <c r="I100" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J100" t="n">
         <v>319.49</v>
@@ -8153,7 +8153,7 @@
         <v>4.73</v>
       </c>
       <c r="I101" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J101" t="n">
         <v>318.68</v>
@@ -8228,7 +8228,7 @@
         <v>1.17</v>
       </c>
       <c r="I102" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J102" t="n">
         <v>318.03</v>
@@ -8303,7 +8303,7 @@
         <v>1.08</v>
       </c>
       <c r="I103" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J103" t="n">
         <v>317.92</v>
@@ -8378,7 +8378,7 @@
         <v>-1.93</v>
       </c>
       <c r="I104" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J104" t="n">
         <v>317.19</v>
@@ -8457,7 +8457,7 @@
         <v>3.5</v>
       </c>
       <c r="I105" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J105" t="n">
         <v>316.82</v>
@@ -8532,7 +8532,7 @@
         <v>-0.7</v>
       </c>
       <c r="I106" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J106" t="n">
         <v>316.97</v>
@@ -8607,7 +8607,7 @@
         <v>3.21</v>
       </c>
       <c r="I107" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J107" t="n">
         <v>317.35</v>
@@ -8682,7 +8682,7 @@
         <v>-0.35</v>
       </c>
       <c r="I108" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J108" t="n">
         <v>317.67</v>
@@ -8757,7 +8757,7 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J109" t="n">
         <v>316.84</v>
@@ -8832,7 +8832,7 @@
         <v>0.14</v>
       </c>
       <c r="I110" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J110" t="n">
         <v>316.45</v>
@@ -8907,7 +8907,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>315.33</v>
@@ -8986,7 +8986,7 @@
         <v>3.52</v>
       </c>
       <c r="I112" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J112" t="n">
         <v>314.85</v>
@@ -9061,10 +9061,10 @@
         <v>3.02</v>
       </c>
       <c r="I113" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J113" t="n">
-        <v>314.95</v>
+        <v>314.94</v>
       </c>
       <c r="K113" t="n">
         <v>321</v>
@@ -9136,7 +9136,7 @@
         <v>-1.35</v>
       </c>
       <c r="I114" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J114" t="n">
         <v>315.12</v>
@@ -9215,7 +9215,7 @@
         <v>-0.67</v>
       </c>
       <c r="I115" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J115" t="n">
         <v>316.04</v>
@@ -9290,7 +9290,7 @@
         <v>-3.38</v>
       </c>
       <c r="I116" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J116" t="n">
         <v>315.67</v>
@@ -9369,7 +9369,7 @@
         <v>-1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J117" t="n">
         <v>315.03</v>
@@ -9444,7 +9444,7 @@
         <v>2.19</v>
       </c>
       <c r="I118" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J118" t="n">
         <v>315.8</v>
@@ -9519,10 +9519,10 @@
         <v>-0.17</v>
       </c>
       <c r="I119" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J119" t="n">
-        <v>316.35</v>
+        <v>316.34</v>
       </c>
       <c r="K119" t="n">
         <v>324.08</v>
@@ -9594,7 +9594,7 @@
         <v>3.62</v>
       </c>
       <c r="I120" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J120" t="n">
         <v>317.55</v>
@@ -9669,7 +9669,7 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J121" t="n">
         <v>318.17</v>
@@ -9744,7 +9744,7 @@
         <v>2.29</v>
       </c>
       <c r="I122" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J122" t="n">
         <v>318.97</v>
@@ -9819,7 +9819,7 @@
         <v>2.85</v>
       </c>
       <c r="I123" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J123" t="n">
         <v>320.08</v>
@@ -9894,7 +9894,7 @@
         <v>0.53</v>
       </c>
       <c r="I124" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J124" t="n">
         <v>321.58</v>
@@ -9969,7 +9969,7 @@
         <v>-0.43</v>
       </c>
       <c r="I125" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J125" t="n">
         <v>322.47</v>
@@ -10044,7 +10044,7 @@
         <v>-1.12</v>
       </c>
       <c r="I126" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J126" t="n">
         <v>323.28</v>
@@ -10119,7 +10119,7 @@
         <v>-1.5</v>
       </c>
       <c r="I127" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J127" t="n">
         <v>323.32</v>
@@ -10194,7 +10194,7 @@
         <v>1.39</v>
       </c>
       <c r="I128" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J128" t="n">
         <v>323.66</v>
@@ -10269,7 +10269,7 @@
         <v>-1.75</v>
       </c>
       <c r="I129" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J129" t="n">
         <v>323.52</v>
@@ -10344,7 +10344,7 @@
         <v>-1.64</v>
       </c>
       <c r="I130" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J130" t="n">
         <v>323.08</v>
@@ -10419,7 +10419,7 @@
         <v>-1.17</v>
       </c>
       <c r="I131" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J131" t="n">
         <v>323.82</v>
@@ -10498,7 +10498,7 @@
         <v>6.22</v>
       </c>
       <c r="I132" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J132" t="n">
         <v>325.02</v>
@@ -10573,7 +10573,7 @@
         <v>1.94</v>
       </c>
       <c r="I133" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J133" t="n">
         <v>326.07</v>
@@ -10648,7 +10648,7 @@
         <v>1.46</v>
       </c>
       <c r="I134" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J134" t="n">
         <v>327.59</v>
@@ -10723,7 +10723,7 @@
         <v>-0.59</v>
       </c>
       <c r="I135" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J135" t="n">
         <v>329.12</v>
@@ -10798,7 +10798,7 @@
         <v>-1.04</v>
       </c>
       <c r="I136" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J136" t="n">
         <v>331.01</v>
@@ -10873,7 +10873,7 @@
         <v>-3.5</v>
       </c>
       <c r="I137" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J137" t="n">
         <v>332.57</v>
@@ -10948,7 +10948,7 @@
         <v>-1.35</v>
       </c>
       <c r="I138" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J138" t="n">
         <v>333.58</v>
@@ -11027,7 +11027,7 @@
         <v>1.44</v>
       </c>
       <c r="I139" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J139" t="n">
         <v>334.84</v>
@@ -11102,7 +11102,7 @@
         <v>1.33</v>
       </c>
       <c r="I140" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J140" t="n">
         <v>335.78</v>
@@ -11177,7 +11177,7 @@
         <v>3.64</v>
       </c>
       <c r="I141" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J141" t="n">
         <v>337.2</v>
@@ -11252,7 +11252,7 @@
         <v>-1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J142" t="n">
         <v>338.04</v>
@@ -11327,7 +11327,7 @@
         <v>0.16</v>
       </c>
       <c r="I143" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J143" t="n">
         <v>338.44</v>
@@ -11402,7 +11402,7 @@
         <v>0.24</v>
       </c>
       <c r="I144" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J144" t="n">
         <v>338.79</v>
@@ -11477,7 +11477,7 @@
         <v>6.04</v>
       </c>
       <c r="I145" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J145" t="n">
         <v>340.26</v>
@@ -11552,7 +11552,7 @@
         <v>7.36</v>
       </c>
       <c r="I146" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J146" t="n">
         <v>343.28</v>
@@ -11627,7 +11627,7 @@
         <v>3.56</v>
       </c>
       <c r="I147" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J147" t="n">
         <v>347.25</v>
@@ -11702,7 +11702,7 @@
         <v>2.82</v>
       </c>
       <c r="I148" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J148" t="n">
         <v>351.57</v>
@@ -11777,7 +11777,7 @@
         <v>1.01</v>
       </c>
       <c r="I149" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J149" t="n">
         <v>356.4</v>
@@ -11852,7 +11852,7 @@
         <v>-2.12</v>
       </c>
       <c r="I150" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J150" t="n">
         <v>361.05</v>
@@ -11927,7 +11927,7 @@
         <v>2.21</v>
       </c>
       <c r="I151" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J151" t="n">
         <v>366.34</v>
@@ -12002,10 +12002,10 @@
         <v>1.91</v>
       </c>
       <c r="I152" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J152" t="n">
-        <v>371.05</v>
+        <v>371.06</v>
       </c>
       <c r="K152" t="n">
         <v>336.97</v>
@@ -12077,7 +12077,7 @@
         <v>-1.93</v>
       </c>
       <c r="I153" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J153" t="n">
         <v>375.02</v>
@@ -12152,7 +12152,7 @@
         <v>3.98</v>
       </c>
       <c r="I154" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J154" t="n">
         <v>379.57</v>
@@ -12227,7 +12227,7 @@
         <v>-4.38</v>
       </c>
       <c r="I155" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J155" t="n">
         <v>383.26</v>
@@ -12302,7 +12302,7 @@
         <v>4.02</v>
       </c>
       <c r="I156" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J156" t="n">
         <v>387.98</v>
@@ -12377,7 +12377,7 @@
         <v>0.64</v>
       </c>
       <c r="I157" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J157" t="n">
         <v>393.45</v>
@@ -12452,7 +12452,7 @@
         <v>0.34</v>
       </c>
       <c r="I158" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J158" t="n">
         <v>399.22</v>
@@ -12527,7 +12527,7 @@
         <v>3.31</v>
       </c>
       <c r="I159" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J159" t="n">
         <v>405.49</v>
@@ -12602,7 +12602,7 @@
         <v>-5.11</v>
       </c>
       <c r="I160" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J160" t="n">
         <v>410.36</v>
@@ -12677,7 +12677,7 @@
         <v>-1.42</v>
       </c>
       <c r="I161" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J161" t="n">
         <v>414.31</v>
@@ -12752,7 +12752,7 @@
         <v>5.45</v>
       </c>
       <c r="I162" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J162" t="n">
         <v>419.65</v>
@@ -12827,7 +12827,7 @@
         <v>-4.45</v>
       </c>
       <c r="I163" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J163" t="n">
         <v>423.96</v>
@@ -12902,7 +12902,7 @@
         <v>1.29</v>
       </c>
       <c r="I164" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J164" t="n">
         <v>428.5</v>
@@ -12977,7 +12977,7 @@
         <v>-0.72</v>
       </c>
       <c r="I165" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J165" t="n">
         <v>431.84</v>
@@ -13052,7 +13052,7 @@
         <v>-5.06</v>
       </c>
       <c r="I166" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J166" t="n">
         <v>432.72</v>
@@ -13131,7 +13131,7 @@
         <v>5.42</v>
       </c>
       <c r="I167" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J167" t="n">
         <v>434.01</v>
@@ -13206,7 +13206,7 @@
         <v>-1.53</v>
       </c>
       <c r="I168" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J168" t="n">
         <v>434.39</v>
@@ -13285,7 +13285,7 @@
         <v>1.38</v>
       </c>
       <c r="I169" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J169" t="n">
         <v>434.86</v>
@@ -13360,7 +13360,7 @@
         <v>-1.47</v>
       </c>
       <c r="I170" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J170" t="n">
         <v>435.45</v>
@@ -13439,7 +13439,7 @@
         <v>2.46</v>
       </c>
       <c r="I171" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J171" t="n">
         <v>436.11</v>
@@ -13514,7 +13514,7 @@
         <v>1.85</v>
       </c>
       <c r="I172" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J172" t="n">
         <v>436.77</v>
@@ -13589,7 +13589,7 @@
         <v>-1.08</v>
       </c>
       <c r="I173" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J173" t="n">
         <v>437.61</v>
@@ -13664,7 +13664,7 @@
         <v>-0.82</v>
       </c>
       <c r="I174" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J174" t="n">
         <v>437.42</v>
@@ -13739,7 +13739,7 @@
         <v>2.28</v>
       </c>
       <c r="I175" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J175" t="n">
         <v>438.7</v>
@@ -13814,7 +13814,7 @@
         <v>-3.4</v>
       </c>
       <c r="I176" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J176" t="n">
         <v>438.37</v>
@@ -13893,7 +13893,7 @@
         <v>4.31</v>
       </c>
       <c r="I177" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J177" t="n">
         <v>438.83</v>
@@ -13968,7 +13968,7 @@
         <v>1.8</v>
       </c>
       <c r="I178" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J178" t="n">
         <v>439.62</v>
@@ -14043,7 +14043,7 @@
         <v>0.21</v>
       </c>
       <c r="I179" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J179" t="n">
         <v>439.72</v>
@@ -14118,7 +14118,7 @@
         <v>-4.64</v>
       </c>
       <c r="I180" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J180" t="n">
         <v>439.93</v>
@@ -14193,7 +14193,7 @@
         <v>3.74</v>
       </c>
       <c r="I181" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J181" t="n">
         <v>441.26</v>
@@ -14268,7 +14268,7 @@
         <v>2.59</v>
       </c>
       <c r="I182" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J182" t="n">
         <v>442.02</v>
@@ -14343,7 +14343,7 @@
         <v>-5.15</v>
       </c>
       <c r="I183" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J183" t="n">
         <v>442.58</v>
@@ -14418,7 +14418,7 @@
         <v>4.01</v>
       </c>
       <c r="I184" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J184" t="n">
         <v>443.75</v>
@@ -14493,7 +14493,7 @@
         <v>-3.5</v>
       </c>
       <c r="I185" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J185" t="n">
         <v>444.26</v>
@@ -14568,7 +14568,7 @@
         <v>-3.68</v>
       </c>
       <c r="I186" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J186" t="n">
         <v>445.07</v>
@@ -14647,7 +14647,7 @@
         <v>3.66</v>
       </c>
       <c r="I187" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J187" t="n">
         <v>445.53</v>
@@ -14722,7 +14722,7 @@
         <v>-1.26</v>
       </c>
       <c r="I188" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J188" t="n">
         <v>446.05</v>
@@ -14797,7 +14797,7 @@
         <v>-2.05</v>
       </c>
       <c r="I189" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J189" t="n">
         <v>445.82</v>
@@ -14872,7 +14872,7 @@
         <v>-6.64</v>
       </c>
       <c r="I190" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J190" t="n">
         <v>444.49</v>
@@ -14951,7 +14951,7 @@
         <v>0.59</v>
       </c>
       <c r="I191" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J191" t="n">
         <v>442.74</v>
@@ -15026,7 +15026,7 @@
         <v>1.13</v>
       </c>
       <c r="I192" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J192" t="n">
         <v>440.81</v>
@@ -15101,7 +15101,7 @@
         <v>-1.88</v>
       </c>
       <c r="I193" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J193" t="n">
         <v>438.74</v>
@@ -15176,7 +15176,7 @@
         <v>0.68</v>
       </c>
       <c r="I194" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J194" t="n">
         <v>437</v>
@@ -15251,7 +15251,7 @@
         <v>-2.17</v>
       </c>
       <c r="I195" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J195" t="n">
         <v>434.31</v>
@@ -15330,7 +15330,7 @@
         <v>-1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J196" t="n">
         <v>432.18</v>
@@ -15405,7 +15405,7 @@
         <v>6.82</v>
       </c>
       <c r="I197" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J197" t="n">
         <v>430.44</v>
@@ -15480,7 +15480,7 @@
         <v>0.39</v>
       </c>
       <c r="I198" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J198" t="n">
         <v>428.39</v>
@@ -15555,7 +15555,7 @@
         <v>1.71</v>
       </c>
       <c r="I199" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J199" t="n">
         <v>426.64</v>
@@ -15630,7 +15630,7 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J200" t="n">
         <v>426.14</v>
@@ -15705,7 +15705,7 @@
         <v>-0.01</v>
       </c>
       <c r="I201" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J201" t="n">
         <v>424.82</v>
@@ -15780,7 +15780,7 @@
         <v>-0.21</v>
       </c>
       <c r="I202" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J202" t="n">
         <v>422.87</v>
@@ -15855,7 +15855,7 @@
         <v>4.08</v>
       </c>
       <c r="I203" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J203" t="n">
         <v>422.99</v>
@@ -15930,7 +15930,7 @@
         <v>1.74</v>
       </c>
       <c r="I204" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J204" t="n">
         <v>422.61</v>
@@ -16005,7 +16005,7 @@
         <v>0.1</v>
       </c>
       <c r="I205" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J205" t="n">
         <v>423.07</v>
@@ -16080,7 +16080,7 @@
         <v>-3.39</v>
       </c>
       <c r="I206" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J206" t="n">
         <v>423.57</v>
@@ -16155,7 +16155,7 @@
         <v>1.27</v>
       </c>
       <c r="I207" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J207" t="n">
         <v>423.57</v>
@@ -16230,7 +16230,7 @@
         <v>1.41</v>
       </c>
       <c r="I208" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J208" t="n">
         <v>424.16</v>
@@ -16305,7 +16305,7 @@
         <v>-1.01</v>
       </c>
       <c r="I209" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J209" t="n">
         <v>424.97</v>
@@ -16380,7 +16380,7 @@
         <v>2.7</v>
       </c>
       <c r="I210" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J210" t="n">
         <v>427.82</v>
@@ -16455,7 +16455,7 @@
         <v>3.56</v>
       </c>
       <c r="I211" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J211" t="n">
         <v>431.37</v>
@@ -16530,7 +16530,7 @@
         <v>3.07</v>
       </c>
       <c r="I212" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J212" t="n">
         <v>435.42</v>
@@ -16605,7 +16605,7 @@
         <v>-4.62</v>
       </c>
       <c r="I213" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J213" t="n">
         <v>438.72</v>
@@ -16680,7 +16680,7 @@
         <v>3.45</v>
       </c>
       <c r="I214" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J214" t="n">
         <v>442.69</v>
@@ -16755,7 +16755,7 @@
         <v>-0.45</v>
       </c>
       <c r="I215" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J215" t="n">
         <v>446.99</v>
@@ -16830,7 +16830,7 @@
         <v>1.56</v>
       </c>
       <c r="I216" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J216" t="n">
         <v>451.87</v>
@@ -16905,7 +16905,7 @@
         <v>-0.65</v>
       </c>
       <c r="I217" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J217" t="n">
         <v>455.26</v>
@@ -16980,7 +16980,7 @@
         <v>-0.03</v>
       </c>
       <c r="I218" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J218" t="n">
         <v>458.56</v>
@@ -17055,7 +17055,7 @@
         <v>-2.1</v>
       </c>
       <c r="I219" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J219" t="n">
         <v>460.99</v>
@@ -17130,7 +17130,7 @@
         <v>-3.27</v>
       </c>
       <c r="I220" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J220" t="n">
         <v>462.46</v>
@@ -17209,7 +17209,7 @@
         <v>-1.13</v>
       </c>
       <c r="I221" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J221" t="n">
         <v>463.68</v>
@@ -17284,7 +17284,7 @@
         <v>-1.04</v>
       </c>
       <c r="I222" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J222" t="n">
         <v>464.7</v>
@@ -17359,7 +17359,7 @@
         <v>-2.59</v>
       </c>
       <c r="I223" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J223" t="n">
         <v>464.27</v>
@@ -17438,7 +17438,7 @@
         <v>3.1</v>
       </c>
       <c r="I224" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J224" t="n">
         <v>464.12</v>
@@ -17513,7 +17513,7 @@
         <v>-4.14</v>
       </c>
       <c r="I225" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J225" t="n">
         <v>463.02</v>
@@ -17592,7 +17592,7 @@
         <v>-0.36</v>
       </c>
       <c r="I226" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J226" t="n">
         <v>462.61</v>
@@ -17667,7 +17667,7 @@
         <v>1.02</v>
       </c>
       <c r="I227" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J227" t="n">
         <v>462.14</v>
@@ -17742,7 +17742,7 @@
         <v>2.11</v>
       </c>
       <c r="I228" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J228" t="n">
         <v>461.82</v>
@@ -17817,7 +17817,7 @@
         <v>0.89</v>
       </c>
       <c r="I229" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J229" t="n">
         <v>461.93</v>
@@ -17892,7 +17892,7 @@
         <v>-0.39</v>
       </c>
       <c r="I230" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J230" t="n">
         <v>461.34</v>
@@ -17967,7 +17967,7 @@
         <v>-1.79</v>
       </c>
       <c r="I231" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J231" t="n">
         <v>459.53</v>
@@ -18046,7 +18046,7 @@
         <v>-0.14</v>
       </c>
       <c r="I232" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J232" t="n">
         <v>456.97</v>
@@ -18121,7 +18121,7 @@
         <v>-0.24</v>
       </c>
       <c r="I233" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J233" t="n">
         <v>455.48</v>
@@ -18196,7 +18196,7 @@
         <v>-4.17</v>
       </c>
       <c r="I234" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J234" t="n">
         <v>452.27</v>
@@ -18271,7 +18271,7 @@
         <v>2.91</v>
       </c>
       <c r="I235" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J235" t="n">
         <v>449.79</v>
@@ -18346,7 +18346,7 @@
         <v>4.15</v>
       </c>
       <c r="I236" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J236" t="n">
         <v>447.82</v>
@@ -18421,7 +18421,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="I237" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J237" t="n">
         <v>445.99</v>
@@ -18496,7 +18496,7 @@
         <v>-3.09</v>
       </c>
       <c r="I238" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J238" t="n">
         <v>443.48</v>
@@ -18575,7 +18575,7 @@
         <v>-0.99</v>
       </c>
       <c r="I239" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J239" t="n">
         <v>441.27</v>
@@ -18650,7 +18650,7 @@
         <v>0.13</v>
       </c>
       <c r="I240" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J240" t="n">
         <v>439.86</v>
@@ -18725,7 +18725,7 @@
         <v>-3.45</v>
       </c>
       <c r="I241" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J241" t="n">
         <v>437.96</v>
@@ -18804,7 +18804,7 @@
         <v>3.32</v>
       </c>
       <c r="I242" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J242" t="n">
         <v>437</v>
@@ -18879,7 +18879,7 @@
         <v>-2</v>
       </c>
       <c r="I243" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J243" t="n">
         <v>436.19</v>
@@ -18954,7 +18954,7 @@
         <v>0.04</v>
       </c>
       <c r="I244" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J244" t="n">
         <v>434.7</v>
@@ -19033,7 +19033,7 @@
         <v>-3.78</v>
       </c>
       <c r="I245" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J245" t="n">
         <v>433.35</v>
@@ -19108,7 +19108,7 @@
         <v>-2.17</v>
       </c>
       <c r="I246" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J246" t="n">
         <v>431.64</v>
@@ -19183,7 +19183,7 @@
         <v>3.5</v>
       </c>
       <c r="I247" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J247" t="n">
         <v>430.41</v>
@@ -19258,7 +19258,7 @@
         <v>1.51</v>
       </c>
       <c r="I248" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J248" t="n">
         <v>429.02</v>
@@ -19333,7 +19333,7 @@
         <v>1.89</v>
       </c>
       <c r="I249" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J249" t="n">
         <v>427.84</v>
@@ -19408,7 +19408,7 @@
         <v>0.72</v>
       </c>
       <c r="I250" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J250" t="n">
         <v>426.89</v>
@@ -19483,7 +19483,7 @@
         <v>-2.62</v>
       </c>
       <c r="I251" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J251" t="n">
         <v>425.78</v>
@@ -19562,7 +19562,7 @@
         <v>0.09</v>
       </c>
       <c r="I252" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J252" t="n">
         <v>424.73</v>
@@ -19637,7 +19637,7 @@
         <v>-1.63</v>
       </c>
       <c r="I253" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J253" t="n">
         <v>423.38</v>
@@ -19712,7 +19712,7 @@
         <v>0.17</v>
       </c>
       <c r="I254" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J254" t="n">
         <v>422.99</v>
@@ -19787,7 +19787,7 @@
         <v>0.09</v>
       </c>
       <c r="I255" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J255" t="n">
         <v>422</v>
@@ -19862,7 +19862,7 @@
         <v>0.03</v>
       </c>
       <c r="I256" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J256" t="n">
         <v>420.12</v>
@@ -19937,7 +19937,7 @@
         <v>-2.91</v>
       </c>
       <c r="I257" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J257" t="n">
         <v>417.66</v>
@@ -20012,7 +20012,7 @@
         <v>2.39</v>
       </c>
       <c r="I258" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J258" t="n">
         <v>416.37</v>
@@ -20087,7 +20087,7 @@
         <v>1.96</v>
       </c>
       <c r="I259" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J259" t="n">
         <v>415.7</v>
@@ -20162,7 +20162,7 @@
         <v>-2.11</v>
       </c>
       <c r="I260" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J260" t="n">
         <v>414.55</v>
@@ -20241,7 +20241,7 @@
         <v>-1.49</v>
       </c>
       <c r="I261" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J261" t="n">
         <v>413.85</v>
@@ -20316,7 +20316,7 @@
         <v>0.2</v>
       </c>
       <c r="I262" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J262" t="n">
         <v>412.5</v>
@@ -20391,7 +20391,7 @@
         <v>-2.7</v>
       </c>
       <c r="I263" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J263" t="n">
         <v>411.03</v>
@@ -20466,7 +20466,7 @@
         <v>3.44</v>
       </c>
       <c r="I264" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J264" t="n">
         <v>410.23</v>
@@ -20541,7 +20541,7 @@
         <v>-0.1</v>
       </c>
       <c r="I265" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J265" t="n">
         <v>410.2</v>
@@ -20616,7 +20616,7 @@
         <v>-2.17</v>
       </c>
       <c r="I266" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J266" t="n">
         <v>410.18</v>
@@ -20695,7 +20695,7 @@
         <v>0.49</v>
       </c>
       <c r="I267" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J267" t="n">
         <v>409.56</v>
@@ -20770,7 +20770,7 @@
         <v>0.14</v>
       </c>
       <c r="I268" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J268" t="n">
         <v>408.65</v>
@@ -20845,7 +20845,7 @@
         <v>2.15</v>
       </c>
       <c r="I269" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J269" t="n">
         <v>407.78</v>
@@ -20920,7 +20920,7 @@
         <v>-3.14</v>
       </c>
       <c r="I270" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J270" t="n">
         <v>406.12</v>
@@ -20929,7 +20929,7 @@
         <v>431.45</v>
       </c>
       <c r="L270" t="n">
-        <v>433.69</v>
+        <v>433.68</v>
       </c>
       <c r="M270" t="n">
         <v>393.31</v>
@@ -20993,7 +20993,7 @@
         <v>-0.96</v>
       </c>
       <c r="I271" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J271" t="n">
         <v>404.83</v>
@@ -21072,7 +21072,7 @@
         <v>1.11</v>
       </c>
       <c r="I272" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J272" t="n">
         <v>403.73</v>
@@ -21147,7 +21147,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I273" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J273" t="n">
         <v>403.16</v>
@@ -21222,7 +21222,7 @@
         <v>-1.63</v>
       </c>
       <c r="I274" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J274" t="n">
         <v>402.24</v>
@@ -21297,7 +21297,7 @@
         <v>-3.18</v>
       </c>
       <c r="I275" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J275" t="n">
         <v>400.67</v>
@@ -21372,7 +21372,7 @@
         <v>-3.24</v>
       </c>
       <c r="I276" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J276" t="n">
         <v>398.47</v>
@@ -21451,7 +21451,7 @@
         <v>3.5</v>
       </c>
       <c r="I277" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J277" t="n">
         <v>397.53</v>
@@ -21526,7 +21526,7 @@
         <v>0.57</v>
       </c>
       <c r="I278" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J278" t="n">
         <v>396.21</v>
@@ -21601,7 +21601,7 @@
         <v>0.76</v>
       </c>
       <c r="I279" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J279" t="n">
         <v>394.64</v>
@@ -21676,7 +21676,7 @@
         <v>-3.59</v>
       </c>
       <c r="I280" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J280" t="n">
         <v>392.81</v>
@@ -21751,7 +21751,7 @@
         <v>-2.76</v>
       </c>
       <c r="I281" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J281" t="n">
         <v>390.78</v>
@@ -21830,7 +21830,7 @@
         <v>-1.81</v>
       </c>
       <c r="I282" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J282" t="n">
         <v>388.38</v>
@@ -21905,7 +21905,7 @@
         <v>4.64</v>
       </c>
       <c r="I283" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J283" t="n">
         <v>387.34</v>
@@ -21980,7 +21980,7 @@
         <v>2.56</v>
       </c>
       <c r="I284" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J284" t="n">
         <v>386.11</v>
@@ -22055,7 +22055,7 @@
         <v>-5.42</v>
       </c>
       <c r="I285" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J285" t="n">
         <v>383.86</v>
@@ -22130,7 +22130,7 @@
         <v>-2.15</v>
       </c>
       <c r="I286" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J286" t="n">
         <v>381.66</v>
@@ -22205,7 +22205,7 @@
         <v>-1.75</v>
       </c>
       <c r="I287" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J287" t="n">
         <v>379.06</v>
@@ -22284,7 +22284,7 @@
         <v>-0.98</v>
       </c>
       <c r="I288" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J288" t="n">
         <v>376.26</v>
@@ -22359,7 +22359,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J289" t="n">
         <v>373.15</v>
@@ -22434,7 +22434,7 @@
         <v>0.96</v>
       </c>
       <c r="I290" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J290" t="n">
         <v>370.85</v>
@@ -22509,7 +22509,7 @@
         <v>0.99</v>
       </c>
       <c r="I291" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J291" t="n">
         <v>368.91</v>
@@ -22584,7 +22584,7 @@
         <v>3.34</v>
       </c>
       <c r="I292" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J292" t="n">
         <v>367.34</v>
@@ -22659,7 +22659,7 @@
         <v>7.62</v>
       </c>
       <c r="I293" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J293" t="n">
         <v>366.98</v>
@@ -22734,7 +22734,7 @@
         <v>-0.78</v>
       </c>
       <c r="I294" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J294" t="n">
         <v>366.78</v>
@@ -22809,7 +22809,7 @@
         <v>3.01</v>
       </c>
       <c r="I295" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J295" t="n">
         <v>367.8</v>
@@ -22884,7 +22884,7 @@
         <v>-2.03</v>
       </c>
       <c r="I296" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J296" t="n">
         <v>369.03</v>
@@ -22963,7 +22963,7 @@
         <v>-1.55</v>
       </c>
       <c r="I297" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J297" t="n">
         <v>369.3</v>
@@ -23038,7 +23038,7 @@
         <v>0.28</v>
       </c>
       <c r="I298" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J298" t="n">
         <v>369.53</v>
@@ -23113,7 +23113,7 @@
         <v>-3.56</v>
       </c>
       <c r="I299" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J299" t="n">
         <v>368.92</v>
@@ -23188,7 +23188,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I300" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J300" t="n">
         <v>369.13</v>
@@ -23263,7 +23263,7 @@
         <v>0.63</v>
       </c>
       <c r="I301" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J301" t="n">
         <v>369.97</v>
@@ -23338,7 +23338,7 @@
         <v>-0.7</v>
       </c>
       <c r="I302" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J302" t="n">
         <v>371.01</v>
@@ -23413,7 +23413,7 @@
         <v>-0.86</v>
       </c>
       <c r="I303" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J303" t="n">
         <v>371.06</v>
@@ -23488,7 +23488,7 @@
         <v>2.37</v>
       </c>
       <c r="I304" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J304" t="n">
         <v>371.08</v>
@@ -23563,7 +23563,7 @@
         <v>2.41</v>
       </c>
       <c r="I305" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J305" t="n">
         <v>372.59</v>
@@ -23638,7 +23638,7 @@
         <v>0.43</v>
       </c>
       <c r="I306" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J306" t="n">
         <v>374.57</v>
@@ -23713,7 +23713,7 @@
         <v>-0.8</v>
       </c>
       <c r="I307" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J307" t="n">
         <v>376.71</v>
@@ -23788,7 +23788,7 @@
         <v>2.4</v>
       </c>
       <c r="I308" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J308" t="n">
         <v>379.48</v>
@@ -23863,7 +23863,7 @@
         <v>3.28</v>
       </c>
       <c r="I309" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J309" t="n">
         <v>382.79</v>
@@ -23938,7 +23938,7 @@
         <v>4.02</v>
       </c>
       <c r="I310" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J310" t="n">
         <v>386.76</v>
@@ -24013,7 +24013,7 @@
         <v>3.89</v>
       </c>
       <c r="I311" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J311" t="n">
         <v>391.39</v>
@@ -24088,7 +24088,7 @@
         <v>-2.6</v>
       </c>
       <c r="I312" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J312" t="n">
         <v>394.85</v>
@@ -24163,7 +24163,7 @@
         <v>2.73</v>
       </c>
       <c r="I313" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J313" t="n">
         <v>397.52</v>
@@ -24238,7 +24238,7 @@
         <v>-0.44</v>
       </c>
       <c r="I314" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J314" t="n">
         <v>400.24</v>
@@ -24313,7 +24313,7 @@
         <v>-4.75</v>
       </c>
       <c r="I315" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J315" t="n">
         <v>401.32</v>
@@ -24388,7 +24388,7 @@
         <v>-2.9</v>
       </c>
       <c r="I316" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J316" t="n">
         <v>402.19</v>
@@ -24467,7 +24467,7 @@
         <v>-1.43</v>
       </c>
       <c r="I317" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J317" t="n">
         <v>403.08</v>
@@ -24542,7 +24542,7 @@
         <v>3.25</v>
       </c>
       <c r="I318" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J318" t="n">
         <v>404.57</v>
@@ -24617,7 +24617,7 @@
         <v>0.14</v>
       </c>
       <c r="I319" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J319" t="n">
         <v>406.77</v>
@@ -24692,7 +24692,7 @@
         <v>1.95</v>
       </c>
       <c r="I320" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J320" t="n">
         <v>409.26</v>
@@ -24767,7 +24767,7 @@
         <v>1.78</v>
       </c>
       <c r="I321" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J321" t="n">
         <v>412</v>
@@ -24842,7 +24842,7 @@
         <v>1.56</v>
       </c>
       <c r="I322" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J322" t="n">
         <v>415.22</v>
@@ -24917,7 +24917,7 @@
         <v>0.4</v>
       </c>
       <c r="I323" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J323" t="n">
         <v>418.69</v>
@@ -24992,7 +24992,7 @@
         <v>-1.43</v>
       </c>
       <c r="I324" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J324" t="n">
         <v>421.39</v>
@@ -25067,7 +25067,7 @@
         <v>-4.57</v>
       </c>
       <c r="I325" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J325" t="n">
         <v>422.65</v>
@@ -25146,7 +25146,7 @@
         <v>1.89</v>
       </c>
       <c r="I326" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J326" t="n">
         <v>424.21</v>
@@ -25221,7 +25221,7 @@
         <v>-0.01</v>
       </c>
       <c r="I327" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J327" t="n">
         <v>425.93</v>
@@ -25296,7 +25296,7 @@
         <v>-1.24</v>
       </c>
       <c r="I328" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J328" t="n">
         <v>426.91</v>
@@ -25371,7 +25371,7 @@
         <v>-6.56</v>
       </c>
       <c r="I329" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J329" t="n">
         <v>425.87</v>
@@ -25450,7 +25450,7 @@
         <v>4.59</v>
       </c>
       <c r="I330" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J330" t="n">
         <v>424.9</v>
@@ -25525,7 +25525,7 @@
         <v>-3</v>
       </c>
       <c r="I331" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J331" t="n">
         <v>422.49</v>
@@ -25600,7 +25600,7 @@
         <v>-3.8</v>
       </c>
       <c r="I332" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J332" t="n">
         <v>419.89</v>
@@ -25679,7 +25679,7 @@
         <v>4.6</v>
       </c>
       <c r="I333" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J333" t="n">
         <v>417.59</v>
@@ -25754,7 +25754,7 @@
         <v>1.82</v>
       </c>
       <c r="I334" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J334" t="n">
         <v>415.74</v>
@@ -25829,7 +25829,7 @@
         <v>1.16</v>
       </c>
       <c r="I335" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J335" t="n">
         <v>415.19</v>
@@ -25904,7 +25904,7 @@
         <v>-1.58</v>
       </c>
       <c r="I336" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J336" t="n">
         <v>414.92</v>
@@ -25983,7 +25983,7 @@
         <v>-2.05</v>
       </c>
       <c r="I337" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J337" t="n">
         <v>414.54</v>
@@ -26058,7 +26058,7 @@
         <v>1.04</v>
       </c>
       <c r="I338" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J338" t="n">
         <v>413.7</v>
@@ -26133,7 +26133,7 @@
         <v>1.14</v>
       </c>
       <c r="I339" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J339" t="n">
         <v>413.06</v>
@@ -26208,7 +26208,7 @@
         <v>-5.79</v>
       </c>
       <c r="I340" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J340" t="n">
         <v>410.84</v>
@@ -26287,7 +26287,7 @@
         <v>-1.59</v>
       </c>
       <c r="I341" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J341" t="n">
         <v>407.93</v>
@@ -26362,7 +26362,7 @@
         <v>-0.11</v>
       </c>
       <c r="I342" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J342" t="n">
         <v>404.67</v>
@@ -26437,7 +26437,7 @@
         <v>1.22</v>
       </c>
       <c r="I343" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J343" t="n">
         <v>401.55</v>
@@ -26512,7 +26512,7 @@
         <v>8.460000000000001</v>
       </c>
       <c r="I344" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J344" t="n">
         <v>400.36</v>
@@ -26587,7 +26587,7 @@
         <v>2.13</v>
       </c>
       <c r="I345" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J345" t="n">
         <v>400.59</v>
@@ -26662,7 +26662,7 @@
         <v>1.12</v>
       </c>
       <c r="I346" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J346" t="n">
         <v>400.67</v>
@@ -26737,7 +26737,7 @@
         <v>-7.49</v>
       </c>
       <c r="I347" s="4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J347" s="4" t="n">
         <v>399.16</v>
@@ -26816,7 +26816,7 @@
         <v>6.69</v>
       </c>
       <c r="I348" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J348" t="n">
         <v>399.22</v>
@@ -26891,7 +26891,7 @@
         <v>-4.02</v>
       </c>
       <c r="I349" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J349" t="n">
         <v>399.82</v>
@@ -26966,7 +26966,7 @@
         <v>-2.19</v>
       </c>
       <c r="I350" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J350" t="n">
         <v>399.07</v>
@@ -27045,7 +27045,7 @@
         <v>3.17</v>
       </c>
       <c r="I351" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J351" t="n">
         <v>399.57</v>
@@ -27120,7 +27120,7 @@
         <v>0.3</v>
       </c>
       <c r="I352" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J352" t="n">
         <v>400.88</v>
@@ -27195,7 +27195,7 @@
         <v>-3.19</v>
       </c>
       <c r="I353" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J353" t="n">
         <v>400.66</v>
@@ -27274,7 +27274,7 @@
         <v>0.36</v>
       </c>
       <c r="I354" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J354" t="n">
         <v>400.14</v>
@@ -27349,7 +27349,7 @@
         <v>-0.43</v>
       </c>
       <c r="I355" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J355" t="n">
         <v>399.31</v>
@@ -27424,7 +27424,7 @@
         <v>-0.86</v>
       </c>
       <c r="I356" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J356" t="n">
         <v>398.63</v>
@@ -27499,7 +27499,7 @@
         <v>-2.61</v>
       </c>
       <c r="I357" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J357" t="n">
         <v>397.85</v>
@@ -27574,7 +27574,7 @@
         <v>-2.96</v>
       </c>
       <c r="I358" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J358" t="n">
         <v>396.31</v>
@@ -27649,7 +27649,7 @@
         <v>2.53</v>
       </c>
       <c r="I359" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J359" t="n">
         <v>395</v>
@@ -27724,7 +27724,7 @@
         <v>-1.3</v>
       </c>
       <c r="I360" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J360" t="n">
         <v>394.62</v>
@@ -27799,7 +27799,7 @@
         <v>-14.52</v>
       </c>
       <c r="I361" s="4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J361" s="4" t="n">
         <v>391.83</v>
@@ -27878,7 +27878,7 @@
         <v>-2.08</v>
       </c>
       <c r="I362" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J362" t="n">
         <v>388.72</v>
@@ -27957,7 +27957,7 @@
         <v>-1.22</v>
       </c>
       <c r="I363" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J363" t="n">
         <v>385.2</v>
@@ -28036,7 +28036,7 @@
         <v>-0.58</v>
       </c>
       <c r="I364" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J364" t="n">
         <v>379.98</v>
@@ -28115,7 +28115,7 @@
         <v>-2.97</v>
       </c>
       <c r="I365" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J365" t="n">
         <v>373.86</v>
@@ -28194,7 +28194,7 @@
         <v>3.53</v>
       </c>
       <c r="I366" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J366" t="n">
         <v>368.04</v>
@@ -28273,7 +28273,7 @@
         <v>0.76</v>
       </c>
       <c r="I367" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J367" t="n">
         <v>363.93</v>
@@ -28352,7 +28352,7 @@
         <v>3.49</v>
       </c>
       <c r="I368" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J368" t="n">
         <v>359.05</v>
@@ -28431,7 +28431,7 @@
         <v>1.64</v>
       </c>
       <c r="I369" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J369" t="n">
         <v>355.27</v>
@@ -28510,7 +28510,7 @@
         <v>-1.77</v>
       </c>
       <c r="I370" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J370" t="n">
         <v>351.64</v>
@@ -28589,7 +28589,7 @@
         <v>-0.63</v>
       </c>
       <c r="I371" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J371" t="n">
         <v>347.29</v>
@@ -28668,7 +28668,7 @@
         <v>2.83</v>
       </c>
       <c r="I372" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J372" t="n">
         <v>343.33</v>
@@ -28743,7 +28743,7 @@
         <v>0.7</v>
       </c>
       <c r="I373" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J373" t="n">
         <v>340.14</v>
@@ -28818,7 +28818,7 @@
         <v>0.58</v>
       </c>
       <c r="I374" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J374" t="n">
         <v>336.97</v>
@@ -28893,7 +28893,7 @@
         <v>-1.59</v>
       </c>
       <c r="I375" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J375" t="n">
         <v>333.62</v>
@@ -28968,7 +28968,7 @@
         <v>3.8</v>
       </c>
       <c r="I376" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J376" t="n">
         <v>331.07</v>
@@ -29043,7 +29043,7 @@
         <v>0.68</v>
       </c>
       <c r="I377" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J377" t="n">
         <v>329.14</v>
@@ -29118,7 +29118,7 @@
         <v>-0.87</v>
       </c>
       <c r="I378" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J378" t="n">
         <v>327.63</v>
@@ -29193,7 +29193,7 @@
         <v>-0.72</v>
       </c>
       <c r="I379" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J379" t="n">
         <v>325.52</v>
@@ -29268,7 +29268,7 @@
         <v>4.23</v>
       </c>
       <c r="I380" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J380" t="n">
         <v>324.38</v>
@@ -29343,7 +29343,7 @@
         <v>-1.71</v>
       </c>
       <c r="I381" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J381" t="n">
         <v>325.65</v>
@@ -29418,7 +29418,7 @@
         <v>5.14</v>
       </c>
       <c r="I382" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J382" t="n">
         <v>328.14</v>
@@ -29493,7 +29493,7 @@
         <v>-3.83</v>
       </c>
       <c r="I383" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J383" t="n">
         <v>330.13</v>
@@ -29568,7 +29568,7 @@
         <v>0.37</v>
       </c>
       <c r="I384" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J384" t="n">
         <v>332.27</v>
@@ -29643,7 +29643,7 @@
         <v>-1.26</v>
       </c>
       <c r="I385" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J385" t="n">
         <v>334.64</v>
@@ -29718,7 +29718,7 @@
         <v>2.6</v>
       </c>
       <c r="I386" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J386" t="n">
         <v>336.94</v>
@@ -29793,7 +29793,7 @@
         <v>-1.71</v>
       </c>
       <c r="I387" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J387" t="n">
         <v>338.82</v>
@@ -29868,7 +29868,7 @@
         <v>5.51</v>
       </c>
       <c r="I388" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J388" t="n">
         <v>341.11</v>
@@ -29943,7 +29943,7 @@
         <v>-3.22</v>
       </c>
       <c r="I389" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J389" t="n">
         <v>342.55</v>
@@ -30022,7 +30022,7 @@
         <v>0.26</v>
       </c>
       <c r="I390" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J390" t="n">
         <v>344.32</v>
@@ -30097,7 +30097,7 @@
         <v>5.42</v>
       </c>
       <c r="I391" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J391" t="n">
         <v>347.16</v>
@@ -30172,7 +30172,7 @@
         <v>-5.92</v>
       </c>
       <c r="I392" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J392" t="n">
         <v>348.44</v>
@@ -30251,7 +30251,7 @@
         <v>3.98</v>
       </c>
       <c r="I393" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J393" t="n">
         <v>350.3</v>
@@ -30326,7 +30326,7 @@
         <v>-0.1</v>
       </c>
       <c r="I394" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J394" t="n">
         <v>352.05</v>
@@ -30401,7 +30401,7 @@
         <v>-1.16</v>
       </c>
       <c r="I395" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J395" t="n">
         <v>353.86</v>
@@ -30476,7 +30476,7 @@
         <v>0.52</v>
       </c>
       <c r="I396" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J396" t="n">
         <v>355.13</v>
@@ -30551,7 +30551,7 @@
         <v>-1.77</v>
       </c>
       <c r="I397" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J397" t="n">
         <v>355.96</v>
@@ -30630,7 +30630,7 @@
         <v>-0.67</v>
       </c>
       <c r="I398" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J398" t="n">
         <v>356.83</v>
@@ -30709,7 +30709,7 @@
         <v>0.42</v>
       </c>
       <c r="I399" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J399" t="n">
         <v>357.89</v>
@@ -30784,7 +30784,7 @@
         <v>2.27</v>
       </c>
       <c r="I400" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J400" t="n">
         <v>358.64</v>
@@ -30859,7 +30859,7 @@
         <v>-0.53</v>
       </c>
       <c r="I401" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J401" t="n">
         <v>359.6</v>
@@ -30934,7 +30934,7 @@
         <v>3.03</v>
       </c>
       <c r="I402" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J402" t="n">
         <v>360.22</v>
@@ -31009,7 +31009,7 @@
         <v>0.96</v>
       </c>
       <c r="I403" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J403" t="n">
         <v>361.72</v>
@@ -31084,7 +31084,7 @@
         <v>0.32</v>
       </c>
       <c r="I404" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J404" t="n">
         <v>363.21</v>
@@ -31159,7 +31159,7 @@
         <v>-0.57</v>
       </c>
       <c r="I405" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J405" t="n">
         <v>364.82</v>
@@ -31238,7 +31238,7 @@
         <v>-1.54</v>
       </c>
       <c r="I406" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J406" t="n">
         <v>365.68</v>
@@ -31313,7 +31313,7 @@
         <v>-3.94</v>
       </c>
       <c r="I407" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J407" t="n">
         <v>366.12</v>
@@ -31392,7 +31392,7 @@
         <v>-1.29</v>
       </c>
       <c r="I408" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J408" t="n">
         <v>365.36</v>
@@ -31471,7 +31471,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I409" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J409" t="n">
         <v>365.3</v>
@@ -31546,7 +31546,7 @@
         <v>-0.2</v>
       </c>
       <c r="I410" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J410" t="n">
         <v>365.16</v>
@@ -31621,7 +31621,7 @@
         <v>4.65</v>
       </c>
       <c r="I411" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J411" t="n">
         <v>364.87</v>
@@ -31690,13 +31690,13 @@
         <v>378.73</v>
       </c>
       <c r="G412" t="n">
-        <v>42112900</v>
+        <v>42232700</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="I412" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J412" t="n">
         <v>366.1</v>
@@ -31762,19 +31762,19 @@
         <v>378.52</v>
       </c>
       <c r="F413" t="n">
-        <v>380.98</v>
+        <v>380.68</v>
       </c>
       <c r="G413" t="n">
-        <v>10388495</v>
+        <v>26746770</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="I413" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J413" t="n">
-        <v>366.74</v>
+        <v>366.72</v>
       </c>
       <c r="K413" t="n">
         <v>352.39</v>
@@ -31783,10 +31783,10 @@
         <v>378.82</v>
       </c>
       <c r="M413" t="n">
-        <v>392.2</v>
+        <v>392.19</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>63.84</v>
+        <v>63.71</v>
       </c>
       <c r="O413" t="n">
         <v>48</v>
@@ -31803,13 +31803,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31677,25 +31677,41 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="D412" t="n">
+        <v>383.33</v>
+      </c>
+      <c r="E412" t="n">
+        <v>378.52</v>
+      </c>
+      <c r="F412" t="n">
+        <v>380.68</v>
+      </c>
       <c r="G412" t="n">
-        <v>27702813</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>27671400</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>0.51</v>
       </c>
       <c r="I412" t="n">
         <v>7.3</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>366.72</v>
+      </c>
+      <c r="K412" t="n">
+        <v>352.39</v>
+      </c>
+      <c r="L412" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="M412" t="n">
+        <v>392.19</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>62.83</v>
+        <v>63.71</v>
       </c>
       <c r="O412" t="n">
         <v>47</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31741,6 +31741,83 @@
         <v>141.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>378.35</v>
+      </c>
+      <c r="D413" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="E413" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="F413" t="n">
+        <v>375.43</v>
+      </c>
+      <c r="G413" t="n">
+        <v>8144309</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="I413" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J413" t="n">
+        <v>367.11</v>
+      </c>
+      <c r="K413" t="n">
+        <v>352.04</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.71</v>
+      </c>
+      <c r="M413" t="n">
+        <v>391.65</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="O413" t="n">
+        <v>42</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -8989,7 +8989,7 @@
         <v>7.3</v>
       </c>
       <c r="J112" t="n">
-        <v>314.94</v>
+        <v>314.95</v>
       </c>
       <c r="K112" t="n">
         <v>321</v>
@@ -9447,7 +9447,7 @@
         <v>7.3</v>
       </c>
       <c r="J118" t="n">
-        <v>316.34</v>
+        <v>316.35</v>
       </c>
       <c r="K118" t="n">
         <v>324.08</v>
@@ -11930,7 +11930,7 @@
         <v>7.3</v>
       </c>
       <c r="J151" t="n">
-        <v>371.06</v>
+        <v>371.05</v>
       </c>
       <c r="K151" t="n">
         <v>336.97</v>
@@ -31690,7 +31690,7 @@
         <v>380.68</v>
       </c>
       <c r="G412" t="n">
-        <v>27671400</v>
+        <v>27735400</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>0.51</v>
@@ -31753,7 +31753,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>378.35</v>
+        <v>378.45</v>
       </c>
       <c r="D413" t="n">
         <v>382.35</v>
@@ -31762,34 +31762,34 @@
         <v>374.43</v>
       </c>
       <c r="F413" t="n">
-        <v>375.43</v>
+        <v>377.81</v>
       </c>
       <c r="G413" t="n">
-        <v>8144309</v>
+        <v>25375061</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-1.38</v>
+        <v>-0.75</v>
       </c>
       <c r="I413" t="n">
         <v>7.3</v>
       </c>
       <c r="J413" t="n">
-        <v>367.11</v>
+        <v>367.22</v>
       </c>
       <c r="K413" t="n">
-        <v>352.04</v>
+        <v>352.08</v>
       </c>
       <c r="L413" t="n">
-        <v>378.71</v>
+        <v>378.73</v>
       </c>
       <c r="M413" t="n">
-        <v>391.65</v>
+        <v>391.67</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>55.8</v>
+        <v>57.52</v>
       </c>
       <c r="O413" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31807,13 +31807,13 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31752,41 +31752,25 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>378.45</v>
-      </c>
-      <c r="D413" t="n">
-        <v>382.35</v>
-      </c>
-      <c r="E413" t="n">
-        <v>374.43</v>
-      </c>
-      <c r="F413" t="n">
-        <v>377.81</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>25375061</v>
-      </c>
-      <c r="H413" s="1" t="n">
-        <v>-0.75</v>
+        <v>25496215</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>7.3</v>
       </c>
-      <c r="J413" t="n">
-        <v>367.22</v>
-      </c>
-      <c r="K413" t="n">
-        <v>352.08</v>
-      </c>
-      <c r="L413" t="n">
-        <v>378.73</v>
-      </c>
-      <c r="M413" t="n">
-        <v>391.67</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="2" t="n">
-        <v>57.52</v>
+        <v>59.74</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>
@@ -31801,11 +31785,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr">
-        <is>
-          <t>3rd: MA120, 50% cash, 5d</t>
-        </is>
-      </c>
+      <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
         <v>5.28</v>
       </c>
@@ -31816,7 +31796,9 @@
         <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31752,25 +31752,41 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>378.45</v>
+      </c>
+      <c r="D413" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="E413" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="F413" t="n">
+        <v>377.81</v>
+      </c>
       <c r="G413" t="n">
-        <v>25496215</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>25529400</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.75</v>
       </c>
       <c r="I413" t="n">
         <v>7.3</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>367.22</v>
+      </c>
+      <c r="K413" t="n">
+        <v>352.08</v>
+      </c>
+      <c r="L413" t="n">
+        <v>378.73</v>
+      </c>
+      <c r="M413" t="n">
+        <v>391.67</v>
+      </c>
       <c r="N413" s="2" t="n">
-        <v>59.74</v>
+        <v>57.52</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>
@@ -31785,7 +31801,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S413" t="n">
         <v>5.28</v>
       </c>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31789,7 +31789,7 @@
         <v>57.52</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31819,6 +31819,79 @@
       <c r="W413" s="2" t="n">
         <v>141.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="D414" t="n">
+        <v>375.96</v>
+      </c>
+      <c r="E414" t="n">
+        <v>371.55</v>
+      </c>
+      <c r="F414" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="G414" t="n">
+        <v>9675507</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="K414" t="n">
+        <v>351.72</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.49</v>
+      </c>
+      <c r="M414" t="n">
+        <v>391.12</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="O414" t="n">
+        <v>41</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31765,7 +31765,7 @@
         <v>377.81</v>
       </c>
       <c r="G413" t="n">
-        <v>25529400</v>
+        <v>25594600</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.75</v>
@@ -31838,37 +31838,37 @@
         <v>375.96</v>
       </c>
       <c r="E414" t="n">
-        <v>371.55</v>
+        <v>368.03</v>
       </c>
       <c r="F414" t="n">
-        <v>372.45</v>
+        <v>375</v>
       </c>
       <c r="G414" t="n">
-        <v>9675507</v>
+        <v>28215427</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-1.42</v>
+        <v>-0.74</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>367.67</v>
+        <v>367.8</v>
       </c>
       <c r="K414" t="n">
-        <v>351.72</v>
+        <v>351.76</v>
       </c>
       <c r="L414" t="n">
-        <v>378.49</v>
+        <v>378.52</v>
       </c>
       <c r="M414" t="n">
-        <v>391.12</v>
+        <v>391.13</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>55.07</v>
+        <v>56.87</v>
       </c>
       <c r="O414" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31882,13 +31882,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31844,7 +31844,7 @@
         <v>375</v>
       </c>
       <c r="G414" t="n">
-        <v>28215427</v>
+        <v>28313500</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-0.74</v>
@@ -31891,7 +31891,9 @@
         <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31868,7 +31868,7 @@
         <v>56.87</v>
       </c>
       <c r="O414" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31894,6 +31894,79 @@
       <c r="W414" s="2" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>382.38</v>
+      </c>
+      <c r="D415" t="n">
+        <v>388.56</v>
+      </c>
+      <c r="E415" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="F415" t="n">
+        <v>382.97</v>
+      </c>
+      <c r="G415" t="n">
+        <v>24153740</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I415" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>368.67</v>
+      </c>
+      <c r="K415" t="n">
+        <v>351.62</v>
+      </c>
+      <c r="L415" t="n">
+        <v>378.44</v>
+      </c>
+      <c r="M415" t="n">
+        <v>390.61</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="O415" t="n">
+        <v>44</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31844,7 +31844,7 @@
         <v>375</v>
       </c>
       <c r="G414" t="n">
-        <v>28313500</v>
+        <v>28394900</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-0.74</v>
@@ -31916,34 +31916,34 @@
         <v>379.71</v>
       </c>
       <c r="F415" t="n">
-        <v>382.97</v>
+        <v>382.7</v>
       </c>
       <c r="G415" t="n">
-        <v>24153740</v>
+        <v>38761404</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
       <c r="J415" t="n">
-        <v>368.67</v>
+        <v>368.66</v>
       </c>
       <c r="K415" t="n">
         <v>351.62</v>
       </c>
       <c r="L415" t="n">
-        <v>378.44</v>
+        <v>378.43</v>
       </c>
       <c r="M415" t="n">
-        <v>390.61</v>
+        <v>390.6</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>55.11</v>
+        <v>54.95</v>
       </c>
       <c r="O415" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31957,13 +31957,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31906,41 +31906,25 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>382.38</v>
-      </c>
-      <c r="D415" t="n">
-        <v>388.56</v>
-      </c>
-      <c r="E415" t="n">
-        <v>379.71</v>
-      </c>
-      <c r="F415" t="n">
-        <v>382.7</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>38761404</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>2.05</v>
+        <v>38834397</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
-      <c r="J415" t="n">
-        <v>368.66</v>
-      </c>
-      <c r="K415" t="n">
-        <v>351.62</v>
-      </c>
-      <c r="L415" t="n">
-        <v>378.43</v>
-      </c>
-      <c r="M415" t="n">
-        <v>390.6</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="2" t="n">
-        <v>54.95</v>
+        <v>49.78</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>
@@ -31966,7 +31950,9 @@
         <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>154.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31906,25 +31906,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>382.38</v>
+      </c>
+      <c r="D415" t="n">
+        <v>388.56</v>
+      </c>
+      <c r="E415" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="F415" t="n">
+        <v>382.7</v>
+      </c>
       <c r="G415" t="n">
-        <v>38834397</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>38897700</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>2.05</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>368.66</v>
+      </c>
+      <c r="K415" t="n">
+        <v>351.62</v>
+      </c>
+      <c r="L415" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="M415" t="n">
+        <v>390.6</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>49.78</v>
+        <v>54.95</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8839,7 +8839,7 @@
         <v>7.3</v>
       </c>
       <c r="J110" t="n">
-        <v>314.95</v>
+        <v>314.94</v>
       </c>
       <c r="K110" t="n">
         <v>321</v>
@@ -9297,7 +9297,7 @@
         <v>7.3</v>
       </c>
       <c r="J116" t="n">
-        <v>316.35</v>
+        <v>316.34</v>
       </c>
       <c r="K116" t="n">
         <v>324.08</v>
@@ -11780,7 +11780,7 @@
         <v>7.3</v>
       </c>
       <c r="J149" t="n">
-        <v>371.05</v>
+        <v>371.06</v>
       </c>
       <c r="K149" t="n">
         <v>336.97</v>
@@ -31793,11 +31793,11 @@
         <v>54.95</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31818,6 +31818,85 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>154.3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="D414" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="E414" t="n">
+        <v>377.58</v>
+      </c>
+      <c r="F414" t="n">
+        <v>378.03</v>
+      </c>
+      <c r="G414" t="n">
+        <v>20131780</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>369.61</v>
+      </c>
+      <c r="K414" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.36</v>
+      </c>
+      <c r="M414" t="n">
+        <v>390.07</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="O414" t="n">
+        <v>46</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>155.1</v>
       </c>
     </row>
   </sheetData>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31824,6 +31824,79 @@
         <v>155.1</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>372.17</v>
+      </c>
+      <c r="D414" t="n">
+        <v>376.98</v>
+      </c>
+      <c r="E414" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="F414" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="G414" t="n">
+        <v>10988904</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="K414" t="n">
+        <v>351.66</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.26</v>
+      </c>
+      <c r="M414" t="n">
+        <v>389.51</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>46.58</v>
+      </c>
+      <c r="O414" t="n">
+        <v>44</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -8764,7 +8764,7 @@
         <v>7.3</v>
       </c>
       <c r="J109" t="n">
-        <v>314.94</v>
+        <v>314.95</v>
       </c>
       <c r="K109" t="n">
         <v>321</v>
@@ -9222,7 +9222,7 @@
         <v>7.3</v>
       </c>
       <c r="J115" t="n">
-        <v>316.34</v>
+        <v>316.35</v>
       </c>
       <c r="K115" t="n">
         <v>324.08</v>
@@ -11705,7 +11705,7 @@
         <v>7.3</v>
       </c>
       <c r="J148" t="n">
-        <v>371.06</v>
+        <v>371.05</v>
       </c>
       <c r="K148" t="n">
         <v>336.97</v>
@@ -24701,7 +24701,7 @@
         <v>392.86</v>
       </c>
       <c r="L320" t="n">
-        <v>414.6</v>
+        <v>414.61</v>
       </c>
       <c r="M320" t="n">
         <v>412.13</v>
@@ -30496,7 +30496,7 @@
         <v>377.81</v>
       </c>
       <c r="M396" t="n">
-        <v>397.66</v>
+        <v>397.65</v>
       </c>
       <c r="N396" s="3" t="n">
         <v>54.8</v>
@@ -31769,7 +31769,7 @@
         <v>378.03</v>
       </c>
       <c r="G413" t="n">
-        <v>20164200</v>
+        <v>20244300</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-1.22</v>
@@ -31839,40 +31839,40 @@
         <v>372.17</v>
       </c>
       <c r="D414" t="n">
-        <v>376.98</v>
+        <v>377.05</v>
       </c>
       <c r="E414" t="n">
         <v>371.3</v>
       </c>
       <c r="F414" t="n">
-        <v>374.8</v>
+        <v>375.23</v>
       </c>
       <c r="G414" t="n">
-        <v>10988904</v>
+        <v>18314332</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-0.85</v>
+        <v>-0.74</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>370.52</v>
+        <v>370.54</v>
       </c>
       <c r="K414" t="n">
-        <v>351.66</v>
+        <v>351.67</v>
       </c>
       <c r="L414" t="n">
         <v>378.26</v>
       </c>
       <c r="M414" t="n">
-        <v>389.51</v>
+        <v>389.52</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>46.58</v>
+        <v>46.84</v>
       </c>
       <c r="O414" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31888,12 +31888,8 @@
       <c r="S414" t="n">
         <v>5.22</v>
       </c>
-      <c r="T414" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U414" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="T414" s="3" t="inlineStr"/>
+      <c r="U414" s="3" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="3" t="inlineStr"/>
     </row>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31801,7 +31801,7 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31797,11 +31797,11 @@
         <v>46.84</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31823,6 +31823,83 @@
       <c r="W413" s="2" t="n">
         <v>154.7</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>371.15</v>
+      </c>
+      <c r="D414" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="E414" t="n">
+        <v>364.44</v>
+      </c>
+      <c r="F414" t="n">
+        <v>368.33</v>
+      </c>
+      <c r="G414" t="n">
+        <v>10924607</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>371.06</v>
+      </c>
+      <c r="K414" t="n">
+        <v>351.49</v>
+      </c>
+      <c r="L414" t="n">
+        <v>378.22</v>
+      </c>
+      <c r="M414" t="n">
+        <v>388.98</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="O414" t="n">
+        <v>37</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31842,37 +31842,37 @@
         <v>371.39</v>
       </c>
       <c r="E414" t="n">
-        <v>364.44</v>
+        <v>363.82</v>
       </c>
       <c r="F414" t="n">
-        <v>368.33</v>
+        <v>364.8</v>
       </c>
       <c r="G414" t="n">
-        <v>10924607</v>
+        <v>22577758</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-1.84</v>
+        <v>-2.78</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>371.06</v>
+        <v>370.88</v>
       </c>
       <c r="K414" t="n">
-        <v>351.49</v>
+        <v>351.43</v>
       </c>
       <c r="L414" t="n">
-        <v>378.22</v>
+        <v>378.19</v>
       </c>
       <c r="M414" t="n">
-        <v>388.98</v>
+        <v>388.96</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>44.15</v>
+        <v>42.33</v>
       </c>
       <c r="O414" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31890,13 +31890,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -8689,7 +8689,7 @@
         <v>7.3</v>
       </c>
       <c r="J108" t="n">
-        <v>314.95</v>
+        <v>314.94</v>
       </c>
       <c r="K108" t="n">
         <v>321</v>
@@ -9147,7 +9147,7 @@
         <v>7.3</v>
       </c>
       <c r="J114" t="n">
-        <v>316.35</v>
+        <v>316.34</v>
       </c>
       <c r="K114" t="n">
         <v>324.08</v>
@@ -11630,7 +11630,7 @@
         <v>7.3</v>
       </c>
       <c r="J147" t="n">
-        <v>371.05</v>
+        <v>371.06</v>
       </c>
       <c r="K147" t="n">
         <v>336.97</v>
@@ -24626,7 +24626,7 @@
         <v>392.86</v>
       </c>
       <c r="L319" t="n">
-        <v>414.61</v>
+        <v>414.6</v>
       </c>
       <c r="M319" t="n">
         <v>412.13</v>
@@ -30421,7 +30421,7 @@
         <v>377.81</v>
       </c>
       <c r="M395" t="n">
-        <v>397.65</v>
+        <v>397.66</v>
       </c>
       <c r="N395" s="2" t="n">
         <v>54.8</v>
@@ -31773,7 +31773,7 @@
         <v>375.23</v>
       </c>
       <c r="G413" t="n">
-        <v>18349700</v>
+        <v>18393000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.74</v>
@@ -31845,34 +31845,34 @@
         <v>363.82</v>
       </c>
       <c r="F414" t="n">
-        <v>364.8</v>
+        <v>367.16</v>
       </c>
       <c r="G414" t="n">
-        <v>22577758</v>
+        <v>30868569</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-2.78</v>
+        <v>-2.15</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>370.88</v>
+        <v>371</v>
       </c>
       <c r="K414" t="n">
-        <v>351.43</v>
+        <v>351.47</v>
       </c>
       <c r="L414" t="n">
-        <v>378.19</v>
+        <v>378.21</v>
       </c>
       <c r="M414" t="n">
-        <v>388.96</v>
+        <v>388.98</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>42.33</v>
+        <v>43.53</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31893,13 +31893,15 @@
         <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>157.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>371.15</v>
+        <v>371.16</v>
       </c>
       <c r="D414" t="n">
         <v>371.39</v>
@@ -31848,7 +31848,7 @@
         <v>367.16</v>
       </c>
       <c r="G414" t="n">
-        <v>30868569</v>
+        <v>30803500</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-2.15</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31872,7 +31872,7 @@
         <v>43.53</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31872,7 +31872,7 @@
         <v>43.53</v>
       </c>
       <c r="O414" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31902,6 +31902,79 @@
       <c r="W414" s="1" t="n">
         <v>157.3</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="D415" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="E415" t="n">
+        <v>355.23</v>
+      </c>
+      <c r="F415" t="n">
+        <v>357.12</v>
+      </c>
+      <c r="G415" t="n">
+        <v>6253937</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="I415" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>370.54</v>
+      </c>
+      <c r="K415" t="n">
+        <v>351.19</v>
+      </c>
+      <c r="L415" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="M415" t="n">
+        <v>388.46</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="O415" t="n">
+        <v>24</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31918,60 +31918,60 @@
         <v>360.58</v>
       </c>
       <c r="D415" t="n">
-        <v>360.58</v>
+        <v>363.69</v>
       </c>
       <c r="E415" t="n">
         <v>355.23</v>
       </c>
       <c r="F415" t="n">
-        <v>357.12</v>
+        <v>361.5</v>
       </c>
       <c r="G415" t="n">
-        <v>6253937</v>
+        <v>20330414</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-2.73</v>
+        <v>-1.54</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
       <c r="J415" t="n">
-        <v>370.54</v>
+        <v>370.76</v>
       </c>
       <c r="K415" t="n">
-        <v>351.19</v>
+        <v>351.26</v>
       </c>
       <c r="L415" t="n">
-        <v>378.05</v>
+        <v>378.08</v>
       </c>
       <c r="M415" t="n">
-        <v>388.46</v>
+        <v>388.49</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>41.43</v>
+        <v>43.62</v>
       </c>
       <c r="O415" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>extreme fear</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>3x BUY</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31848,7 +31848,7 @@
         <v>367.16</v>
       </c>
       <c r="G414" t="n">
-        <v>30803500</v>
+        <v>31001400</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-2.15</v>
@@ -31918,40 +31918,40 @@
         <v>360.58</v>
       </c>
       <c r="D415" t="n">
-        <v>363.69</v>
+        <v>363.75</v>
       </c>
       <c r="E415" t="n">
         <v>355.23</v>
       </c>
       <c r="F415" t="n">
-        <v>361.5</v>
+        <v>362.44</v>
       </c>
       <c r="G415" t="n">
-        <v>20330414</v>
+        <v>26484292</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-1.54</v>
+        <v>-1.29</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
       <c r="J415" t="n">
-        <v>370.76</v>
+        <v>370.81</v>
       </c>
       <c r="K415" t="n">
-        <v>351.26</v>
+        <v>351.28</v>
       </c>
       <c r="L415" t="n">
-        <v>378.08</v>
+        <v>378.09</v>
       </c>
       <c r="M415" t="n">
         <v>388.49</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>43.62</v>
+        <v>44.11</v>
       </c>
       <c r="O415" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31965,16 +31965,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31914,41 +31914,25 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>360.58</v>
-      </c>
-      <c r="D415" t="n">
-        <v>363.75</v>
-      </c>
-      <c r="E415" t="n">
-        <v>355.23</v>
-      </c>
-      <c r="F415" t="n">
-        <v>362.44</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
         <v>26484292</v>
       </c>
-      <c r="H415" s="1" t="n">
-        <v>-1.29</v>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
-      <c r="J415" t="n">
-        <v>370.81</v>
-      </c>
-      <c r="K415" t="n">
-        <v>351.28</v>
-      </c>
-      <c r="L415" t="n">
-        <v>378.09</v>
-      </c>
-      <c r="M415" t="n">
-        <v>388.49</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="2" t="n">
-        <v>44.11</v>
+        <v>46.8</v>
       </c>
       <c r="O415" t="n">
         <v>32</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31914,28 +31914,44 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>360.57</v>
+      </c>
+      <c r="D415" t="n">
+        <v>363.75</v>
+      </c>
+      <c r="E415" t="n">
+        <v>355.23</v>
+      </c>
+      <c r="F415" t="n">
+        <v>362.44</v>
+      </c>
       <c r="G415" t="n">
-        <v>26484292</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>26614300</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-1.29</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="K415" t="n">
+        <v>351.28</v>
+      </c>
+      <c r="L415" t="n">
+        <v>378.09</v>
+      </c>
+      <c r="M415" t="n">
+        <v>388.49</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>46.8</v>
+        <v>44.11</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31951,7 +31951,7 @@
         <v>44.11</v>
       </c>
       <c r="O415" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31951,7 +31951,7 @@
         <v>44.11</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31977,6 +31977,79 @@
       <c r="W415" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="D416" t="n">
+        <v>370.58</v>
+      </c>
+      <c r="E416" t="n">
+        <v>358.37</v>
+      </c>
+      <c r="F416" t="n">
+        <v>358.47</v>
+      </c>
+      <c r="G416" t="n">
+        <v>30231759</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I416" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J416" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="K416" t="n">
+        <v>351.92</v>
+      </c>
+      <c r="L416" t="n">
+        <v>377.92</v>
+      </c>
+      <c r="M416" t="n">
+        <v>388.01</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="O416" t="n">
+        <v>30</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31996,57 +31996,57 @@
         <v>370.58</v>
       </c>
       <c r="E416" t="n">
-        <v>358.37</v>
+        <v>349.33</v>
       </c>
       <c r="F416" t="n">
-        <v>358.47</v>
+        <v>352.24</v>
       </c>
       <c r="G416" t="n">
-        <v>30231759</v>
+        <v>52287694</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-1.1</v>
+        <v>-2.81</v>
       </c>
       <c r="I416" t="n">
         <v>7.3</v>
       </c>
       <c r="J416" t="n">
-        <v>370.52</v>
+        <v>370.21</v>
       </c>
       <c r="K416" t="n">
-        <v>351.92</v>
+        <v>351.82</v>
       </c>
       <c r="L416" t="n">
-        <v>377.92</v>
+        <v>377.87</v>
       </c>
       <c r="M416" t="n">
-        <v>388.01</v>
+        <v>387.98</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>50.71</v>
+        <v>46.65</v>
       </c>
       <c r="O416" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31927,7 +31927,7 @@
         <v>362.44</v>
       </c>
       <c r="G415" t="n">
-        <v>26614300</v>
+        <v>26728300</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-1.29</v>
@@ -31993,37 +31993,37 @@
         <v>369.04</v>
       </c>
       <c r="D416" t="n">
-        <v>370.58</v>
+        <v>370.5</v>
       </c>
       <c r="E416" t="n">
         <v>349.33</v>
       </c>
       <c r="F416" t="n">
-        <v>352.24</v>
+        <v>354.72</v>
       </c>
       <c r="G416" t="n">
-        <v>52287694</v>
+        <v>61706132</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-2.81</v>
+        <v>-2.13</v>
       </c>
       <c r="I416" t="n">
         <v>7.3</v>
       </c>
       <c r="J416" t="n">
-        <v>370.21</v>
+        <v>370.33</v>
       </c>
       <c r="K416" t="n">
-        <v>351.82</v>
+        <v>351.86</v>
       </c>
       <c r="L416" t="n">
-        <v>377.87</v>
+        <v>377.89</v>
       </c>
       <c r="M416" t="n">
-        <v>387.98</v>
+        <v>387.99</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>46.65</v>
+        <v>48.19</v>
       </c>
       <c r="O416" t="n">
         <v>18</v>
@@ -32043,13 +32043,15 @@
         <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="1" t="n">
+        <v>168.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31914,25 +31914,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>369.15</v>
+      </c>
+      <c r="D415" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="E415" t="n">
+        <v>349.33</v>
+      </c>
+      <c r="F415" t="n">
+        <v>354.72</v>
+      </c>
       <c r="G415" t="n">
-        <v>61706132</v>
-      </c>
-      <c r="H415" s="7" t="n">
-        <v>0</v>
+        <v>61855000</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-2.13</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="K415" t="n">
+        <v>351.86</v>
+      </c>
+      <c r="L415" t="n">
+        <v>377.89</v>
+      </c>
+      <c r="M415" t="n">
+        <v>387.99</v>
+      </c>
       <c r="N415" s="7" t="n">
-        <v>53.7</v>
+        <v>48.19</v>
       </c>
       <c r="O415" t="n">
         <v>18</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31797,7 +31797,7 @@
         <v>48.19</v>
       </c>
       <c r="O413" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31797,7 +31797,7 @@
         <v>48.19</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31823,6 +31823,79 @@
       <c r="W413" s="1" t="n">
         <v>168.6</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>357.48</v>
+      </c>
+      <c r="D414" t="n">
+        <v>369.58</v>
+      </c>
+      <c r="E414" t="n">
+        <v>354.47</v>
+      </c>
+      <c r="F414" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="G414" t="n">
+        <v>30183938</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>370</v>
+      </c>
+      <c r="K414" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="L414" t="n">
+        <v>377.83</v>
+      </c>
+      <c r="M414" t="n">
+        <v>387.59</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="O414" t="n">
+        <v>24</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -30192,7 +30192,7 @@
         <v>377.81</v>
       </c>
       <c r="M392" t="n">
-        <v>397.66</v>
+        <v>397.65</v>
       </c>
       <c r="N392" s="3" t="n">
         <v>54.8</v>
@@ -31845,34 +31845,34 @@
         <v>354.47</v>
       </c>
       <c r="F414" t="n">
-        <v>368.56</v>
+        <v>368.06</v>
       </c>
       <c r="G414" t="n">
-        <v>30183938</v>
+        <v>38651173</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>370</v>
+        <v>369.97</v>
       </c>
       <c r="K414" t="n">
-        <v>352.79</v>
+        <v>352.78</v>
       </c>
       <c r="L414" t="n">
         <v>377.83</v>
       </c>
       <c r="M414" t="n">
-        <v>387.59</v>
+        <v>387.58</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>59.31</v>
+        <v>59.07</v>
       </c>
       <c r="O414" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31886,16 +31886,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>161.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31797,7 +31797,7 @@
         <v>59.07</v>
       </c>
       <c r="O413" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31823,6 +31823,79 @@
       <c r="W413" s="3" t="n">
         <v>161.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>370.35</v>
+      </c>
+      <c r="D414" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="E414" t="n">
+        <v>363.64</v>
+      </c>
+      <c r="F414" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="G414" t="n">
+        <v>12115591</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>369.82</v>
+      </c>
+      <c r="K414" t="n">
+        <v>353.89</v>
+      </c>
+      <c r="L414" t="n">
+        <v>377.85</v>
+      </c>
+      <c r="M414" t="n">
+        <v>387.27</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="O414" t="n">
+        <v>28</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31839,25 +31839,25 @@
         <v>370.35</v>
       </c>
       <c r="D414" t="n">
-        <v>376.24</v>
+        <v>377.59</v>
       </c>
       <c r="E414" t="n">
         <v>363.64</v>
       </c>
       <c r="F414" t="n">
-        <v>375.78</v>
+        <v>375.76</v>
       </c>
       <c r="G414" t="n">
-        <v>12115591</v>
+        <v>23488850</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>369.82</v>
+        <v>369.81</v>
       </c>
       <c r="K414" t="n">
         <v>353.89</v>
@@ -31869,10 +31869,10 @@
         <v>387.27</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>61.69</v>
+        <v>61.68</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31886,13 +31886,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -8843,7 +8843,7 @@
         <v>7.3</v>
       </c>
       <c r="J110" t="n">
-        <v>316.34</v>
+        <v>316.35</v>
       </c>
       <c r="K110" t="n">
         <v>324.08</v>
@@ -11326,7 +11326,7 @@
         <v>7.3</v>
       </c>
       <c r="J143" t="n">
-        <v>371.06</v>
+        <v>371.05</v>
       </c>
       <c r="K143" t="n">
         <v>336.97</v>
@@ -30117,7 +30117,7 @@
         <v>377.81</v>
       </c>
       <c r="M391" t="n">
-        <v>397.65</v>
+        <v>397.66</v>
       </c>
       <c r="N391" s="2" t="n">
         <v>54.8</v>
@@ -31773,7 +31773,7 @@
         <v>368.06</v>
       </c>
       <c r="G413" t="n">
-        <v>38741900</v>
+        <v>38817900</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>3.76</v>
@@ -31836,7 +31836,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>370.35</v>
+        <v>370.28</v>
       </c>
       <c r="D414" t="n">
         <v>377.59</v>
@@ -31845,31 +31845,31 @@
         <v>363.64</v>
       </c>
       <c r="F414" t="n">
-        <v>375.76</v>
+        <v>373.71</v>
       </c>
       <c r="G414" t="n">
-        <v>23488850</v>
+        <v>30761382</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>2.09</v>
+        <v>1.54</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>369.81</v>
+        <v>369.71</v>
       </c>
       <c r="K414" t="n">
-        <v>353.89</v>
+        <v>353.85</v>
       </c>
       <c r="L414" t="n">
-        <v>377.85</v>
+        <v>377.83</v>
       </c>
       <c r="M414" t="n">
-        <v>387.27</v>
+        <v>387.26</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>61.68</v>
+        <v>60.79</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31889,13 +31889,15 @@
         <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31797,7 +31797,7 @@
         <v>60.79</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31797,7 +31797,7 @@
         <v>60.79</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31823,6 +31823,77 @@
       <c r="W413" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="D414" t="n">
+        <v>386.68</v>
+      </c>
+      <c r="E414" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="F414" t="n">
+        <v>382.89</v>
+      </c>
+      <c r="G414" t="n">
+        <v>5115462</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>369.85</v>
+      </c>
+      <c r="K414" t="n">
+        <v>355.11</v>
+      </c>
+      <c r="L414" t="n">
+        <v>377.84</v>
+      </c>
+      <c r="M414" t="n">
+        <v>386.92</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>64.97</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="U414" s="3" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31797,7 +31797,7 @@
         <v>60.79</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31839,40 +31839,40 @@
         <v>381.51</v>
       </c>
       <c r="D414" t="n">
-        <v>386.68</v>
+        <v>388.84</v>
       </c>
       <c r="E414" t="n">
-        <v>381.4</v>
+        <v>380.51</v>
       </c>
       <c r="F414" t="n">
-        <v>382.89</v>
+        <v>386.91</v>
       </c>
       <c r="G414" t="n">
-        <v>5115462</v>
+        <v>29841080</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>2.46</v>
+        <v>3.53</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>369.85</v>
+        <v>370.05</v>
       </c>
       <c r="K414" t="n">
-        <v>355.11</v>
+        <v>355.18</v>
       </c>
       <c r="L414" t="n">
-        <v>377.84</v>
+        <v>377.88</v>
       </c>
       <c r="M414" t="n">
-        <v>386.92</v>
+        <v>386.94</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>64.97</v>
+        <v>66.38</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31886,12 +31886,14 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U414" s="3" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="3" t="inlineStr"/>
     </row>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -8310,7 +8310,7 @@
         <v>7.3</v>
       </c>
       <c r="J103" t="n">
-        <v>314.94</v>
+        <v>314.95</v>
       </c>
       <c r="K103" t="n">
         <v>321</v>
@@ -20175,7 +20175,7 @@
         <v>431.45</v>
       </c>
       <c r="L260" t="n">
-        <v>433.68</v>
+        <v>433.69</v>
       </c>
       <c r="M260" t="n">
         <v>393.31</v>
@@ -31773,7 +31773,7 @@
         <v>373.71</v>
       </c>
       <c r="G413" t="n">
-        <v>31662400</v>
+        <v>32123300</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>1.54</v>
@@ -31845,34 +31845,34 @@
         <v>380.51</v>
       </c>
       <c r="F414" t="n">
-        <v>386.91</v>
+        <v>386.47</v>
       </c>
       <c r="G414" t="n">
-        <v>29841080</v>
+        <v>44779790</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>3.53</v>
+        <v>3.41</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>370.05</v>
+        <v>370.03</v>
       </c>
       <c r="K414" t="n">
-        <v>355.18</v>
+        <v>355.17</v>
       </c>
       <c r="L414" t="n">
-        <v>377.88</v>
+        <v>377.87</v>
       </c>
       <c r="M414" t="n">
         <v>386.94</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>66.38</v>
+        <v>66.23</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31886,16 +31886,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>150.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31835,41 +31835,25 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>381.51</v>
-      </c>
-      <c r="D414" t="n">
-        <v>388.84</v>
-      </c>
-      <c r="E414" t="n">
-        <v>380.51</v>
-      </c>
-      <c r="F414" t="n">
-        <v>386.47</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>44779790</v>
       </c>
-      <c r="H414" s="2" t="n">
-        <v>3.41</v>
+      <c r="H414" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
-      <c r="J414" t="n">
-        <v>370.03</v>
-      </c>
-      <c r="K414" t="n">
-        <v>355.17</v>
-      </c>
-      <c r="L414" t="n">
-        <v>377.87</v>
-      </c>
-      <c r="M414" t="n">
-        <v>386.94</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="3" t="n">
-        <v>66.23</v>
+        <v>61.27</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31835,28 +31835,44 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="D414" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="E414" t="n">
+        <v>380.51</v>
+      </c>
+      <c r="F414" t="n">
+        <v>386.47</v>
+      </c>
       <c r="G414" t="n">
-        <v>44779790</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0</v>
+        <v>47651600</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>3.41</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>370.03</v>
+      </c>
+      <c r="K414" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="L414" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="M414" t="n">
+        <v>386.94</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>61.27</v>
+        <v>66.23</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31872,7 +31872,7 @@
         <v>66.23</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31898,6 +31898,81 @@
       <c r="W414" s="3" t="n">
         <v>150.4</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>374.03</v>
+      </c>
+      <c r="D415" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="E415" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="F415" t="n">
+        <v>375.35</v>
+      </c>
+      <c r="G415" t="n">
+        <v>5776786</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="I415" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="K415" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="L415" t="n">
+        <v>377.74</v>
+      </c>
+      <c r="M415" t="n">
+        <v>386.65</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="O415" t="n">
+        <v>28</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U415" s="3" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31872,7 +31872,7 @@
         <v>66.23</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31914,63 +31914,61 @@
         <v>374.03</v>
       </c>
       <c r="D415" t="n">
-        <v>378.75</v>
+        <v>388.86</v>
       </c>
       <c r="E415" t="n">
         <v>373.71</v>
       </c>
       <c r="F415" t="n">
-        <v>375.35</v>
+        <v>378.58</v>
       </c>
       <c r="G415" t="n">
-        <v>5776786</v>
+        <v>38283615</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-2.88</v>
+        <v>-2.04</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
       <c r="J415" t="n">
-        <v>369.9</v>
+        <v>370.06</v>
       </c>
       <c r="K415" t="n">
-        <v>356.45</v>
+        <v>356.51</v>
       </c>
       <c r="L415" t="n">
-        <v>377.74</v>
+        <v>377.77</v>
       </c>
       <c r="M415" t="n">
-        <v>386.65</v>
+        <v>386.66</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>52.52</v>
+        <v>54.39</v>
       </c>
       <c r="O415" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>2x BUY</t>
-        </is>
-      </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>3rd: MA120, 50% cash, 5d</t>
-        </is>
-      </c>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U415" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="U415" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="3" t="inlineStr"/>
     </row>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31848,7 +31848,7 @@
         <v>386.47</v>
       </c>
       <c r="G414" t="n">
-        <v>47651600</v>
+        <v>48875800</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>3.41</v>
@@ -31920,34 +31920,34 @@
         <v>373.71</v>
       </c>
       <c r="F415" t="n">
-        <v>378.58</v>
+        <v>374.58</v>
       </c>
       <c r="G415" t="n">
-        <v>38283615</v>
+        <v>51339690</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-2.04</v>
+        <v>-3.08</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
       <c r="J415" t="n">
-        <v>370.06</v>
+        <v>369.86</v>
       </c>
       <c r="K415" t="n">
-        <v>356.51</v>
+        <v>356.44</v>
       </c>
       <c r="L415" t="n">
-        <v>377.77</v>
+        <v>377.74</v>
       </c>
       <c r="M415" t="n">
-        <v>386.66</v>
+        <v>386.64</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>54.39</v>
+        <v>52.1</v>
       </c>
       <c r="O415" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31959,18 +31959,24 @@
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>4.95</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>14.7</v>
+        <v>15.2</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="inlineStr"/>
+      <c r="W415" s="3" t="n">
+        <v>152.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31910,41 +31910,25 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>374.03</v>
-      </c>
-      <c r="D415" t="n">
-        <v>388.86</v>
-      </c>
-      <c r="E415" t="n">
-        <v>373.71</v>
-      </c>
-      <c r="F415" t="n">
-        <v>374.58</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>51339690</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>-3.08</v>
+        <v>51511993</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
-      <c r="J415" t="n">
-        <v>369.86</v>
-      </c>
-      <c r="K415" t="n">
-        <v>356.44</v>
-      </c>
-      <c r="L415" t="n">
-        <v>377.74</v>
-      </c>
-      <c r="M415" t="n">
-        <v>386.64</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="3" t="n">
-        <v>52.1</v>
+        <v>59.54</v>
       </c>
       <c r="O415" t="n">
         <v>20</v>
@@ -31959,11 +31943,7 @@
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>3rd: MA120, 50% cash, 5d</t>
-        </is>
-      </c>
+      <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
         <v>4.95</v>
       </c>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31910,25 +31910,41 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>374.29</v>
+      </c>
+      <c r="D415" t="n">
+        <v>388.86</v>
+      </c>
+      <c r="E415" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="F415" t="n">
+        <v>374.58</v>
+      </c>
       <c r="G415" t="n">
-        <v>51511993</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
+        <v>51482700</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-3.08</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="K415" t="n">
+        <v>356.44</v>
+      </c>
+      <c r="L415" t="n">
+        <v>377.74</v>
+      </c>
+      <c r="M415" t="n">
+        <v>386.64</v>
+      </c>
       <c r="N415" s="3" t="n">
-        <v>59.54</v>
+        <v>52.1</v>
       </c>
       <c r="O415" t="n">
         <v>20</v>
@@ -31943,7 +31959,11 @@
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>4.95</v>
       </c>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31947,7 +31947,7 @@
         <v>52.1</v>
       </c>
       <c r="O415" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31947,7 +31947,7 @@
         <v>52.1</v>
       </c>
       <c r="O415" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31977,6 +31977,79 @@
       <c r="W415" s="3" t="n">
         <v>152.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="D416" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="E416" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="F416" t="n">
+        <v>371.6</v>
+      </c>
+      <c r="G416" t="n">
+        <v>27033339</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I416" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J416" t="n">
+        <v>369.84</v>
+      </c>
+      <c r="K416" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="L416" t="n">
+        <v>377.56</v>
+      </c>
+      <c r="M416" t="n">
+        <v>386.34</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="O416" t="n">
+        <v>20</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T416" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U416" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31923,7 +31923,7 @@
         <v>374.58</v>
       </c>
       <c r="G415" t="n">
-        <v>51482700</v>
+        <v>51610900</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-3.08</v>
@@ -31999,34 +31999,34 @@
         <v>365.27</v>
       </c>
       <c r="F416" t="n">
-        <v>371.6</v>
+        <v>372.22</v>
       </c>
       <c r="G416" t="n">
-        <v>27033339</v>
+        <v>34615357</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-0.8</v>
+        <v>-0.63</v>
       </c>
       <c r="I416" t="n">
         <v>7.3</v>
       </c>
       <c r="J416" t="n">
-        <v>369.84</v>
+        <v>369.87</v>
       </c>
       <c r="K416" t="n">
-        <v>357.49</v>
+        <v>357.5</v>
       </c>
       <c r="L416" t="n">
-        <v>377.56</v>
+        <v>377.57</v>
       </c>
       <c r="M416" t="n">
-        <v>386.34</v>
+        <v>386.35</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>46.04</v>
+        <v>46.36</v>
       </c>
       <c r="O416" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -32040,16 +32040,18 @@
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="T416" s="3" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="U416" s="3" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="3" t="inlineStr"/>
+      <c r="W416" s="3" t="n">
+        <v>151.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31914,25 +31914,41 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="D415" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="E415" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="F415" t="n">
+        <v>372.22</v>
+      </c>
       <c r="G415" t="n">
-        <v>34615357</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>34689700</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-0.63</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>369.87</v>
+      </c>
+      <c r="K415" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="L415" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="M415" t="n">
+        <v>386.35</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>47.61</v>
+        <v>46.36</v>
       </c>
       <c r="O415" t="n">
         <v>21</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -19950,7 +19950,7 @@
         <v>431.45</v>
       </c>
       <c r="L257" t="n">
-        <v>433.69</v>
+        <v>433.68</v>
       </c>
       <c r="M257" t="n">
         <v>393.31</v>
@@ -31801,7 +31801,7 @@
         <v>46.36</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31827,6 +31827,79 @@
       <c r="W413" s="3" t="n">
         <v>151.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>383.97</v>
+      </c>
+      <c r="D414" t="n">
+        <v>396.96</v>
+      </c>
+      <c r="E414" t="n">
+        <v>383.84</v>
+      </c>
+      <c r="F414" t="n">
+        <v>395.28</v>
+      </c>
+      <c r="G414" t="n">
+        <v>31949707</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>371.76</v>
+      </c>
+      <c r="K414" t="n">
+        <v>358.9</v>
+      </c>
+      <c r="L414" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="M414" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31843,37 +31843,37 @@
         <v>383.97</v>
       </c>
       <c r="D414" t="n">
-        <v>396.96</v>
+        <v>397.27</v>
       </c>
       <c r="E414" t="n">
         <v>383.84</v>
       </c>
       <c r="F414" t="n">
-        <v>395.28</v>
+        <v>391.62</v>
       </c>
       <c r="G414" t="n">
-        <v>31949707</v>
+        <v>52860669</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>6.2</v>
+        <v>5.21</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>371.76</v>
+        <v>371.58</v>
       </c>
       <c r="K414" t="n">
-        <v>358.9</v>
+        <v>358.84</v>
       </c>
       <c r="L414" t="n">
-        <v>377.62</v>
+        <v>377.59</v>
       </c>
       <c r="M414" t="n">
-        <v>386.14</v>
+        <v>386.13</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>56.61</v>
+        <v>55.12</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31890,16 +31890,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31698,7 +31698,7 @@
         <v>372.22</v>
       </c>
       <c r="G412" t="n">
-        <v>34689700</v>
+        <v>34763000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.63</v>
@@ -31760,28 +31760,44 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>383.83</v>
+      </c>
+      <c r="D413" t="n">
+        <v>397.27</v>
+      </c>
+      <c r="E413" t="n">
+        <v>383.73</v>
+      </c>
+      <c r="F413" t="n">
+        <v>391.62</v>
+      </c>
       <c r="G413" t="n">
-        <v>52860669</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0</v>
+        <v>52957700</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>5.21</v>
       </c>
       <c r="I413" t="n">
         <v>7.3</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>371.58</v>
+      </c>
+      <c r="K413" t="n">
+        <v>358.84</v>
+      </c>
+      <c r="L413" t="n">
+        <v>377.59</v>
+      </c>
+      <c r="M413" t="n">
+        <v>386.13</v>
+      </c>
       <c r="N413" s="3" t="n">
-        <v>45.16</v>
+        <v>55.12</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31797,7 +31797,7 @@
         <v>55.12</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31823,6 +31823,79 @@
       <c r="W413" s="3" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="D414" t="n">
+        <v>404</v>
+      </c>
+      <c r="E414" t="n">
+        <v>395.25</v>
+      </c>
+      <c r="F414" t="n">
+        <v>401.98</v>
+      </c>
+      <c r="G414" t="n">
+        <v>12786100</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>374.03</v>
+      </c>
+      <c r="K414" t="n">
+        <v>360.17</v>
+      </c>
+      <c r="L414" t="n">
+        <v>377.61</v>
+      </c>
+      <c r="M414" t="n">
+        <v>385.91</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="O414" t="n">
+        <v>32</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31773,7 +31773,7 @@
         <v>391.62</v>
       </c>
       <c r="G413" t="n">
-        <v>52957700</v>
+        <v>53090200</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>5.21</v>
@@ -31839,40 +31839,40 @@
         <v>397.8</v>
       </c>
       <c r="D414" t="n">
-        <v>404</v>
+        <v>408.45</v>
       </c>
       <c r="E414" t="n">
         <v>395.25</v>
       </c>
       <c r="F414" t="n">
-        <v>401.98</v>
+        <v>407.08</v>
       </c>
       <c r="G414" t="n">
-        <v>12786100</v>
+        <v>39389122</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>2.65</v>
+        <v>3.95</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>374.03</v>
+        <v>374.29</v>
       </c>
       <c r="K414" t="n">
-        <v>360.17</v>
+        <v>360.25</v>
       </c>
       <c r="L414" t="n">
-        <v>377.61</v>
+        <v>377.66</v>
       </c>
       <c r="M414" t="n">
-        <v>385.91</v>
+        <v>385.94</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>60.58</v>
+        <v>62.26</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31886,13 +31886,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="3" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -29511,7 +29511,7 @@
         <v>54.13</v>
       </c>
       <c r="O383" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P383" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>52.58</v>
       </c>
       <c r="O384" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>54.8</v>
       </c>
       <c r="O386" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>56.77</v>
       </c>
       <c r="O387" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>61.73</v>
       </c>
       <c r="O390" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>50.97</v>
       </c>
       <c r="O391" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>41.81</v>
       </c>
       <c r="O393" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P393" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>39.26</v>
       </c>
       <c r="O394" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>57.62</v>
       </c>
       <c r="O397" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>63.51</v>
       </c>
       <c r="O398" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>57.52</v>
       </c>
       <c r="O400" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>56.87</v>
       </c>
       <c r="O401" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -30960,11 +30960,11 @@
         <v>54.95</v>
       </c>
       <c r="O402" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
@@ -31035,7 +31035,7 @@
         <v>49.43</v>
       </c>
       <c r="O403" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -31114,11 +31114,11 @@
         <v>46.84</v>
       </c>
       <c r="O404" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
@@ -31189,7 +31189,7 @@
         <v>43.53</v>
       </c>
       <c r="O405" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P405" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44.11</v>
       </c>
       <c r="O406" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>48.19</v>
       </c>
       <c r="O407" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>59.07</v>
       </c>
       <c r="O408" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P408" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>60.79</v>
       </c>
       <c r="O409" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P409" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>66.23</v>
       </c>
       <c r="O410" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P410" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>52.1</v>
       </c>
       <c r="O411" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P411" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>46.36</v>
       </c>
       <c r="O412" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>55.12</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31845,22 +31845,22 @@
         <v>395.25</v>
       </c>
       <c r="F414" t="n">
-        <v>407.08</v>
+        <v>407.46</v>
       </c>
       <c r="G414" t="n">
-        <v>39389122</v>
+        <v>45019044</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>374.29</v>
+        <v>374.31</v>
       </c>
       <c r="K414" t="n">
-        <v>360.25</v>
+        <v>360.26</v>
       </c>
       <c r="L414" t="n">
         <v>377.66</v>
@@ -31869,10 +31869,10 @@
         <v>385.94</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>62.26</v>
+        <v>62.38</v>
       </c>
       <c r="O414" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31895,7 +31895,9 @@
         <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31793,7 +31793,7 @@
         <v>62.38</v>
       </c>
       <c r="O413" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31819,6 +31819,79 @@
       <c r="W413" s="6" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>410.21</v>
+      </c>
+      <c r="D414" t="n">
+        <v>410.85</v>
+      </c>
+      <c r="E414" t="n">
+        <v>397.18</v>
+      </c>
+      <c r="F414" t="n">
+        <v>402.83</v>
+      </c>
+      <c r="G414" t="n">
+        <v>24535639</v>
+      </c>
+      <c r="H414" s="7" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="I414" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J414" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="K414" t="n">
+        <v>361.52</v>
+      </c>
+      <c r="L414" t="n">
+        <v>377.59</v>
+      </c>
+      <c r="M414" t="n">
+        <v>385.71</v>
+      </c>
+      <c r="N414" s="6" t="n">
+        <v>61.45</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T414" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31769,7 +31769,7 @@
         <v>407.46</v>
       </c>
       <c r="G413" t="n">
-        <v>45189400</v>
+        <v>45333200</v>
       </c>
       <c r="H413" s="5" t="n">
         <v>4.04</v>
@@ -31841,34 +31841,34 @@
         <v>397.18</v>
       </c>
       <c r="F414" t="n">
-        <v>402.83</v>
+        <v>404.22</v>
       </c>
       <c r="G414" t="n">
-        <v>24535639</v>
+        <v>35080523</v>
       </c>
       <c r="H414" s="7" t="n">
-        <v>-1.14</v>
+        <v>-0.8</v>
       </c>
       <c r="I414" t="n">
         <v>7.3</v>
       </c>
       <c r="J414" t="n">
-        <v>376.71</v>
+        <v>376.78</v>
       </c>
       <c r="K414" t="n">
-        <v>361.52</v>
+        <v>361.54</v>
       </c>
       <c r="L414" t="n">
-        <v>377.59</v>
+        <v>377.6</v>
       </c>
       <c r="M414" t="n">
-        <v>385.71</v>
+        <v>385.72</v>
       </c>
       <c r="N414" s="6" t="n">
-        <v>61.45</v>
+        <v>62.16</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31882,16 +31882,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="T414" s="6" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="6" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="6" t="inlineStr"/>
+      <c r="W414" s="6" t="n">
+        <v>148.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31832,7 +31832,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>410.21</v>
+        <v>410.16</v>
       </c>
       <c r="D414" t="n">
         <v>410.85</v>
@@ -31844,7 +31844,7 @@
         <v>404.22</v>
       </c>
       <c r="G414" t="n">
-        <v>35080523</v>
+        <v>35450700</v>
       </c>
       <c r="H414" s="7" t="n">
         <v>-0.8</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31868,7 +31868,7 @@
         <v>62.16</v>
       </c>
       <c r="O414" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31894,6 +31894,79 @@
       <c r="W414" s="6" t="n">
         <v>148.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>405.93</v>
+      </c>
+      <c r="D415" t="n">
+        <v>406.98</v>
+      </c>
+      <c r="E415" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="F415" t="n">
+        <v>405.45</v>
+      </c>
+      <c r="G415" t="n">
+        <v>12855410</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I415" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J415" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="K415" t="n">
+        <v>362.94</v>
+      </c>
+      <c r="L415" t="n">
+        <v>377.41</v>
+      </c>
+      <c r="M415" t="n">
+        <v>385.51</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>60.01</v>
+      </c>
+      <c r="O415" t="n">
+        <v>35</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="6" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U415" s="6" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31844,7 +31844,7 @@
         <v>404.22</v>
       </c>
       <c r="G414" t="n">
-        <v>35450700</v>
+        <v>35598800</v>
       </c>
       <c r="H414" s="7" t="n">
         <v>-0.8</v>
@@ -31916,31 +31916,31 @@
         <v>400.5</v>
       </c>
       <c r="F415" t="n">
-        <v>405.45</v>
+        <v>403.3</v>
       </c>
       <c r="G415" t="n">
-        <v>12855410</v>
-      </c>
-      <c r="H415" s="5" t="n">
-        <v>0.3</v>
+        <v>22375524</v>
+      </c>
+      <c r="H415" s="7" t="n">
+        <v>-0.23</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
       <c r="J415" t="n">
-        <v>379.34</v>
+        <v>379.24</v>
       </c>
       <c r="K415" t="n">
-        <v>362.94</v>
+        <v>362.9</v>
       </c>
       <c r="L415" t="n">
-        <v>377.41</v>
+        <v>377.39</v>
       </c>
       <c r="M415" t="n">
-        <v>385.51</v>
+        <v>385.5</v>
       </c>
       <c r="N415" s="6" t="n">
-        <v>60.01</v>
+        <v>59.08</v>
       </c>
       <c r="O415" t="n">
         <v>35</v>
@@ -31952,21 +31952,23 @@
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>BUY STOP</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T415" s="6" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="U415" s="6" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="6" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31907,7 +31907,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>405.93</v>
+        <v>405.63</v>
       </c>
       <c r="D415" t="n">
         <v>406.98</v>
@@ -31919,7 +31919,7 @@
         <v>403.3</v>
       </c>
       <c r="G415" t="n">
-        <v>22375524</v>
+        <v>22602100</v>
       </c>
       <c r="H415" s="7" t="n">
         <v>-0.23</v>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31943,7 +31943,7 @@
         <v>59.08</v>
       </c>
       <c r="O415" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31943,7 +31943,7 @@
         <v>59.08</v>
       </c>
       <c r="O415" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31969,6 +31969,79 @@
       <c r="W415" s="6" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>393.04</v>
+      </c>
+      <c r="D416" t="n">
+        <v>404.2</v>
+      </c>
+      <c r="E416" t="n">
+        <v>387.52</v>
+      </c>
+      <c r="F416" t="n">
+        <v>399.6</v>
+      </c>
+      <c r="G416" t="n">
+        <v>17721935</v>
+      </c>
+      <c r="H416" s="7" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="I416" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J416" t="n">
+        <v>380.69</v>
+      </c>
+      <c r="K416" t="n">
+        <v>364.24</v>
+      </c>
+      <c r="L416" t="n">
+        <v>377.01</v>
+      </c>
+      <c r="M416" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="N416" s="6" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="O416" t="n">
+        <v>27</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T416" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U416" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31919,7 +31919,7 @@
         <v>403.3</v>
       </c>
       <c r="G415" t="n">
-        <v>22602100</v>
+        <v>22858300</v>
       </c>
       <c r="H415" s="7" t="n">
         <v>-0.23</v>
@@ -31985,25 +31985,25 @@
         <v>393.04</v>
       </c>
       <c r="D416" t="n">
-        <v>404.2</v>
+        <v>404.19</v>
       </c>
       <c r="E416" t="n">
         <v>387.52</v>
       </c>
       <c r="F416" t="n">
-        <v>399.6</v>
+        <v>399.81</v>
       </c>
       <c r="G416" t="n">
-        <v>17721935</v>
+        <v>41290047</v>
       </c>
       <c r="H416" s="7" t="n">
-        <v>-0.92</v>
+        <v>-0.87</v>
       </c>
       <c r="I416" t="n">
         <v>7.3</v>
       </c>
       <c r="J416" t="n">
-        <v>380.69</v>
+        <v>380.7</v>
       </c>
       <c r="K416" t="n">
         <v>364.24</v>
@@ -32015,10 +32015,10 @@
         <v>385.3</v>
       </c>
       <c r="N416" s="6" t="n">
-        <v>59.59</v>
+        <v>59.71</v>
       </c>
       <c r="O416" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -32032,13 +32032,13 @@
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="T416" s="6" t="n">
         <v>19.4</v>
       </c>
       <c r="U416" s="6" t="n">
-        <v>12.7</v>
+        <v>19.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="6" t="inlineStr"/>

--- a/US_stock/TESLA_table.xlsx
+++ b/US_stock/TESLA_table.xlsx
@@ -31898,25 +31898,41 @@
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>393.22</v>
+      </c>
+      <c r="D415" t="n">
+        <v>404.22</v>
+      </c>
+      <c r="E415" t="n">
+        <v>387.52</v>
+      </c>
+      <c r="F415" t="n">
+        <v>399.81</v>
+      </c>
       <c r="G415" t="n">
-        <v>41578483</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>41644400</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>-0.87</v>
       </c>
       <c r="I415" t="n">
         <v>7.3</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="K415" t="n">
+        <v>364.24</v>
+      </c>
+      <c r="L415" t="n">
+        <v>377.01</v>
+      </c>
+      <c r="M415" t="n">
+        <v>385.3</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>61.62</v>
+        <v>59.71</v>
       </c>
       <c r="O415" t="n">
         <v>26</v>
@@ -31928,7 +31944,7 @@
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>BUY STOP</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr"/>
